--- a/Dados/PRODUTIVIDADE/table_PROD_TRIM_RS_aux.xlsx
+++ b/Dados/PRODUTIVIDADE/table_PROD_TRIM_RS_aux.xlsx
@@ -7448,58 +7448,58 @@
         </is>
       </c>
       <c r="B5">
-        <v>131291241.5574411</v>
+        <v>1693657016.09099</v>
       </c>
       <c r="C5">
-        <v>2772419.18845992</v>
+        <v>35764207.53113297</v>
       </c>
       <c r="D5">
-        <v>159328000.3621346</v>
+        <v>2055331204.671537</v>
       </c>
       <c r="E5">
-        <v>7702385.468944971</v>
+        <v>99360772.54939012</v>
       </c>
       <c r="F5">
-        <v>65279932.46213016</v>
+        <v>842111128.7614791</v>
       </c>
       <c r="G5">
-        <v>235082737.4816697</v>
+        <v>3032567313.513539</v>
       </c>
       <c r="H5">
-        <v>170987099.9468098</v>
+        <v>2205733589.313847</v>
       </c>
       <c r="I5">
-        <v>52224431.83748957</v>
+        <v>673695170.7036154</v>
       </c>
       <c r="J5">
-        <v>10456921.77095584</v>
+        <v>134894290.8453303</v>
       </c>
       <c r="K5">
-        <v>12446724.00046067</v>
+        <v>160562739.6059426</v>
       </c>
       <c r="L5">
-        <v>5936208.38715127</v>
+        <v>76577088.19425139</v>
       </c>
       <c r="M5">
-        <v>215923941.6035263</v>
+        <v>2785418846.68549</v>
       </c>
       <c r="N5">
-        <v>81050861.24758258</v>
+        <v>1045556110.093815</v>
       </c>
       <c r="O5">
-        <v>549026188.7939761</v>
+        <v>7082437835.442291</v>
       </c>
       <c r="P5">
-        <v>915400167.8330868</v>
+        <v>11808662165.04682</v>
       </c>
       <c r="Q5">
-        <v>828413098.1983531</v>
+        <v>10686528966.75875</v>
       </c>
       <c r="R5">
-        <v>697121856.6409118</v>
+        <v>8992871950.667763</v>
       </c>
       <c r="S5">
-        <v>684675132.6404512</v>
+        <v>8832309211.061821</v>
       </c>
     </row>
     <row r="6">
@@ -7509,58 +7509,58 @@
         </is>
       </c>
       <c r="B6">
-        <v>130842339.6069331</v>
+        <v>1687866180.929437</v>
       </c>
       <c r="C6">
-        <v>2873063.40556605</v>
+        <v>37062517.93180205</v>
       </c>
       <c r="D6">
-        <v>159452714.7696756</v>
+        <v>2056940020.528816</v>
       </c>
       <c r="E6">
-        <v>7684574.547880881</v>
+        <v>99131011.66766337</v>
       </c>
       <c r="F6">
-        <v>67352221.31514865</v>
+        <v>868843654.9654177</v>
       </c>
       <c r="G6">
-        <v>237362574.0382712</v>
+        <v>3061977205.093699</v>
       </c>
       <c r="H6">
-        <v>172777502.719432</v>
+        <v>2228829785.080672</v>
       </c>
       <c r="I6">
-        <v>52482654.21942319</v>
+        <v>677026239.4305592</v>
       </c>
       <c r="J6">
-        <v>10478978.21476661</v>
+        <v>135178818.9704893</v>
       </c>
       <c r="K6">
-        <v>12774069.04422191</v>
+        <v>164785490.6704626</v>
       </c>
       <c r="L6">
-        <v>6805204.03749773</v>
+        <v>87787132.08372071</v>
       </c>
       <c r="M6">
-        <v>212071608.5184864</v>
+        <v>2735723749.888475</v>
       </c>
       <c r="N6">
-        <v>83294594.84057541</v>
+        <v>1074500273.443423</v>
       </c>
       <c r="O6">
-        <v>550684611.5944033</v>
+        <v>7103831489.567802</v>
       </c>
       <c r="P6">
-        <v>918889525.2396077</v>
+        <v>11853674875.59094</v>
       </c>
       <c r="Q6">
-        <v>828789726.3615344</v>
+        <v>10691387470.06379</v>
       </c>
       <c r="R6">
-        <v>697947386.7546012</v>
+        <v>9003521289.134357</v>
       </c>
       <c r="S6">
-        <v>685173317.7103794</v>
+        <v>8838735798.463894</v>
       </c>
     </row>
     <row r="7">
@@ -7570,58 +7570,58 @@
         </is>
       </c>
       <c r="B7">
-        <v>128599433.1831076</v>
+        <v>1658932688.062088</v>
       </c>
       <c r="C7">
-        <v>2934016.79203935</v>
+        <v>37848816.61730762</v>
       </c>
       <c r="D7">
-        <v>159476451.6987268</v>
+        <v>2057246226.913576</v>
       </c>
       <c r="E7">
-        <v>8074400.66983876</v>
+        <v>104159768.64092</v>
       </c>
       <c r="F7">
-        <v>66751042.5699582</v>
+        <v>861088449.1524607</v>
       </c>
       <c r="G7">
-        <v>237235911.7305632</v>
+        <v>3060343261.324265</v>
       </c>
       <c r="H7">
-        <v>175665992.2919004</v>
+        <v>2266091300.565515</v>
       </c>
       <c r="I7">
-        <v>53098459.42127262</v>
+        <v>684970126.5344168</v>
       </c>
       <c r="J7">
-        <v>10404933.15025596</v>
+        <v>134223637.6383019</v>
       </c>
       <c r="K7">
-        <v>12890404.54884089</v>
+        <v>166286218.6800475</v>
       </c>
       <c r="L7">
-        <v>7430449.40898817</v>
+        <v>95852797.3759474</v>
       </c>
       <c r="M7">
-        <v>210223771.236254</v>
+        <v>2711886648.947677</v>
       </c>
       <c r="N7">
-        <v>85895095.55242445</v>
+        <v>1108046732.626275</v>
       </c>
       <c r="O7">
-        <v>555609105.6099365</v>
+        <v>7167357462.368181</v>
       </c>
       <c r="P7">
-        <v>921444450.5236073</v>
+        <v>11886633411.75454</v>
       </c>
       <c r="Q7">
-        <v>828118905.5621945</v>
+        <v>10682733881.75231</v>
       </c>
       <c r="R7">
-        <v>699519472.379087</v>
+        <v>9023801193.690222</v>
       </c>
       <c r="S7">
-        <v>686629067.830246</v>
+        <v>8857514975.010174</v>
       </c>
     </row>
     <row r="8">
@@ -7631,58 +7631,58 @@
         </is>
       </c>
       <c r="B8">
-        <v>127690767.3229534</v>
+        <v>1647210898.466098</v>
       </c>
       <c r="C8">
-        <v>2845024.27391361</v>
+        <v>36700813.13348557</v>
       </c>
       <c r="D8">
-        <v>159464318.2317336</v>
+        <v>2057089705.189364</v>
       </c>
       <c r="E8">
-        <v>8317266.319347519</v>
+        <v>107292735.519583</v>
       </c>
       <c r="F8">
-        <v>68424024.14600657</v>
+        <v>882669911.4834847</v>
       </c>
       <c r="G8">
-        <v>239050632.9710014</v>
+        <v>3083753165.325917</v>
       </c>
       <c r="H8">
-        <v>178712049.4349527</v>
+        <v>2305385437.710889</v>
       </c>
       <c r="I8">
-        <v>53782784.37331786</v>
+        <v>693797918.4158003</v>
       </c>
       <c r="J8">
-        <v>10159515.13332438</v>
+        <v>131057745.2198845</v>
       </c>
       <c r="K8">
-        <v>13015613.40109401</v>
+        <v>167901412.8741127</v>
       </c>
       <c r="L8">
-        <v>7970540.04159506</v>
+        <v>102819966.5365763</v>
       </c>
       <c r="M8">
-        <v>211328646.9128817</v>
+        <v>2726139545.176174</v>
       </c>
       <c r="N8">
-        <v>87169087.60063326</v>
+        <v>1124481230.048169</v>
       </c>
       <c r="O8">
-        <v>562138236.8977989</v>
+        <v>7251583255.981606</v>
       </c>
       <c r="P8">
-        <v>928879637.1917539</v>
+        <v>11982547319.77362</v>
       </c>
       <c r="Q8">
-        <v>833740009.5495253</v>
+        <v>10755246123.18888</v>
       </c>
       <c r="R8">
-        <v>706049242.226572</v>
+        <v>9108035224.722778</v>
       </c>
       <c r="S8">
-        <v>693033628.8254778</v>
+        <v>8940133811.848665</v>
       </c>
     </row>
     <row r="9">
@@ -7692,58 +7692,58 @@
         </is>
       </c>
       <c r="B9">
-        <v>126747676.1585412</v>
+        <v>1635045022.445182</v>
       </c>
       <c r="C9">
-        <v>2831941.52387637</v>
+        <v>36532045.65800517</v>
       </c>
       <c r="D9">
-        <v>159079728.0232578</v>
+        <v>2052128491.500026</v>
       </c>
       <c r="E9">
-        <v>8093165.28177697</v>
+        <v>104401832.1349229</v>
       </c>
       <c r="F9">
-        <v>68901651.58272633</v>
+        <v>888831305.4171697</v>
       </c>
       <c r="G9">
-        <v>238906486.4116375</v>
+        <v>3081893674.710124</v>
       </c>
       <c r="H9">
-        <v>182946384.0940431</v>
+        <v>2360008354.813156</v>
       </c>
       <c r="I9">
-        <v>53016596.36730317</v>
+        <v>683914093.1382109</v>
       </c>
       <c r="J9">
-        <v>10082982.45646401</v>
+        <v>130070473.6883857</v>
       </c>
       <c r="K9">
-        <v>12931233.61574933</v>
+        <v>166812913.6431664</v>
       </c>
       <c r="L9">
-        <v>7979226.50792678</v>
+        <v>102932021.9522555</v>
       </c>
       <c r="M9">
-        <v>214995644.4833845</v>
+        <v>2773443813.83566</v>
       </c>
       <c r="N9">
-        <v>87920839.73643503</v>
+        <v>1134178832.600012</v>
       </c>
       <c r="O9">
-        <v>569872907.2613059</v>
+        <v>7351360503.670847</v>
       </c>
       <c r="P9">
-        <v>935527069.8314847</v>
+        <v>12068299200.82615</v>
       </c>
       <c r="Q9">
-        <v>839627003.5871227</v>
+        <v>10831188346.27388</v>
       </c>
       <c r="R9">
-        <v>712879327.4285816</v>
+        <v>9196143323.828703</v>
       </c>
       <c r="S9">
-        <v>699948093.8128322</v>
+        <v>9029330410.185535</v>
       </c>
     </row>
     <row r="10">
@@ -7753,58 +7753,58 @@
         </is>
       </c>
       <c r="B10">
-        <v>122213643.8443585</v>
+        <v>1576556005.592225</v>
       </c>
       <c r="C10">
-        <v>2871466.91324268</v>
+        <v>37041923.18083058</v>
       </c>
       <c r="D10">
-        <v>159331205.8513637</v>
+        <v>2055372555.482592</v>
       </c>
       <c r="E10">
-        <v>7717464.8744187</v>
+        <v>99555296.88000123</v>
       </c>
       <c r="F10">
-        <v>69005220.04053889</v>
+        <v>890167338.5229517</v>
       </c>
       <c r="G10">
-        <v>238925357.679564</v>
+        <v>3082137114.066376</v>
       </c>
       <c r="H10">
-        <v>186117638.8962763</v>
+        <v>2400917541.761965</v>
       </c>
       <c r="I10">
-        <v>52401240.97273269</v>
+        <v>675976008.5482517</v>
       </c>
       <c r="J10">
-        <v>10370341.03129575</v>
+        <v>133777399.3037152</v>
       </c>
       <c r="K10">
-        <v>12615790.00158284</v>
+        <v>162743691.0204186</v>
       </c>
       <c r="L10">
-        <v>7760537.88193722</v>
+        <v>100110938.6769901</v>
       </c>
       <c r="M10">
-        <v>218804321.4339382</v>
+        <v>2822575746.497803</v>
       </c>
       <c r="N10">
-        <v>87025889.65178877</v>
+        <v>1122633976.508075</v>
       </c>
       <c r="O10">
-        <v>575095759.8695518</v>
+        <v>7418735302.317219</v>
       </c>
       <c r="P10">
-        <v>936234761.3934743</v>
+        <v>12077428421.97582</v>
       </c>
       <c r="Q10">
-        <v>841448333.8597484</v>
+        <v>10854683506.79075</v>
       </c>
       <c r="R10">
-        <v>719234690.0153898</v>
+        <v>9278127501.198528</v>
       </c>
       <c r="S10">
-        <v>706618900.0138069</v>
+        <v>9115383810.178108</v>
       </c>
     </row>
     <row r="11">
@@ -7814,58 +7814,58 @@
         </is>
       </c>
       <c r="B11">
-        <v>119788620.4950595</v>
+        <v>1545273204.386268</v>
       </c>
       <c r="C11">
-        <v>2454260.3184503</v>
+        <v>31659958.10800887</v>
       </c>
       <c r="D11">
-        <v>158311424.0959623</v>
+        <v>2042217370.837914</v>
       </c>
       <c r="E11">
-        <v>7136406.61161709</v>
+        <v>92059645.28986046</v>
       </c>
       <c r="F11">
-        <v>68628868.33999771</v>
+        <v>885312401.5859704</v>
       </c>
       <c r="G11">
-        <v>236530959.3660274</v>
+        <v>3051249375.821754</v>
       </c>
       <c r="H11">
-        <v>186224780.8922558</v>
+        <v>2402299673.510099</v>
       </c>
       <c r="I11">
-        <v>51066866.42404594</v>
+        <v>658762576.8701925</v>
       </c>
       <c r="J11">
-        <v>10557237.68274517</v>
+        <v>136188366.1074127</v>
       </c>
       <c r="K11">
-        <v>12148177.31275648</v>
+        <v>156711487.3345586</v>
       </c>
       <c r="L11">
-        <v>7205813.89991194</v>
+        <v>92954999.30886403</v>
       </c>
       <c r="M11">
-        <v>226738160.6370859</v>
+        <v>2924922272.218408</v>
       </c>
       <c r="N11">
-        <v>85492645.40484098</v>
+        <v>1102855125.722449</v>
       </c>
       <c r="O11">
-        <v>579433682.2536421</v>
+        <v>7474694501.071983</v>
       </c>
       <c r="P11">
-        <v>935753262.1147289</v>
+        <v>12071217081.28</v>
       </c>
       <c r="Q11">
-        <v>843054802.8099761</v>
+        <v>10875406956.24869</v>
       </c>
       <c r="R11">
-        <v>723266182.3149165</v>
+        <v>9330133751.862423</v>
       </c>
       <c r="S11">
-        <v>711118005.0021601</v>
+        <v>9173422264.527866</v>
       </c>
     </row>
     <row r="12">
@@ -7875,58 +7875,58 @@
         </is>
       </c>
       <c r="B12">
-        <v>118362295.9294441</v>
+        <v>1526873617.489829</v>
       </c>
       <c r="C12">
-        <v>2380187.0020108</v>
+        <v>30704412.32593932</v>
       </c>
       <c r="D12">
-        <v>157734074.5012679</v>
+        <v>2034769561.066356</v>
       </c>
       <c r="E12">
-        <v>6796797.12018349</v>
+        <v>87678682.85036702</v>
       </c>
       <c r="F12">
-        <v>67316018.23186359</v>
+        <v>868376635.1910403</v>
       </c>
       <c r="G12">
-        <v>234227076.8553258</v>
+        <v>3021529291.433703</v>
       </c>
       <c r="H12">
-        <v>184522694.6054034</v>
+        <v>2380342760.409704</v>
       </c>
       <c r="I12">
-        <v>49415436.99431237</v>
+        <v>637459137.2266296</v>
       </c>
       <c r="J12">
-        <v>10760980.5814273</v>
+        <v>138816649.5004122</v>
       </c>
       <c r="K12">
-        <v>12047338.01818712</v>
+        <v>155410660.4346139</v>
       </c>
       <c r="L12">
-        <v>6613869.32136924</v>
+        <v>85318914.2456632</v>
       </c>
       <c r="M12">
-        <v>230733466.3505424</v>
+        <v>2976461715.921997</v>
       </c>
       <c r="N12">
-        <v>85167204.03718624</v>
+        <v>1098656932.079702</v>
       </c>
       <c r="O12">
-        <v>579260989.9084281</v>
+        <v>7472466769.818723</v>
       </c>
       <c r="P12">
-        <v>931850362.693198</v>
+        <v>12020869678.74225</v>
       </c>
       <c r="Q12">
-        <v>840069289.3346425</v>
+        <v>10836893832.41689</v>
       </c>
       <c r="R12">
-        <v>721706993.4051983</v>
+        <v>9310020214.927059</v>
       </c>
       <c r="S12">
-        <v>709659655.3870113</v>
+        <v>9154609554.492447</v>
       </c>
     </row>
     <row r="13">
@@ -7936,58 +7936,58 @@
         </is>
       </c>
       <c r="B13">
-        <v>114728008.0333817</v>
+        <v>1479991303.630624</v>
       </c>
       <c r="C13">
-        <v>2404276.61701017</v>
+        <v>31015168.3594312</v>
       </c>
       <c r="D13">
-        <v>156145567.566002</v>
+        <v>2014277821.601426</v>
       </c>
       <c r="E13">
-        <v>6753847.81383101</v>
+        <v>87124636.79842003</v>
       </c>
       <c r="F13">
-        <v>68049648.59029785</v>
+        <v>877840466.8148422</v>
       </c>
       <c r="G13">
-        <v>233353340.587141</v>
+        <v>3010258093.574119</v>
       </c>
       <c r="H13">
-        <v>181583408.0815606</v>
+        <v>2342425964.252132</v>
       </c>
       <c r="I13">
-        <v>48619747.63787924</v>
+        <v>627194744.5286422</v>
       </c>
       <c r="J13">
-        <v>10999533.12901894</v>
+        <v>141893977.3643443</v>
       </c>
       <c r="K13">
-        <v>11891758.62709886</v>
+        <v>153403686.2895753</v>
       </c>
       <c r="L13">
-        <v>6567369.293287911</v>
+        <v>84719063.88341404</v>
       </c>
       <c r="M13">
-        <v>233746081.4448139</v>
+        <v>3015324450.6381</v>
       </c>
       <c r="N13">
-        <v>85187826.40590961</v>
+        <v>1098922960.636234</v>
       </c>
       <c r="O13">
-        <v>578595724.6195692</v>
+        <v>7463884847.592443</v>
       </c>
       <c r="P13">
-        <v>926677073.2400919</v>
+        <v>11954134244.79719</v>
       </c>
       <c r="Q13">
-        <v>834921877.5408944</v>
+        <v>10770492220.27754</v>
       </c>
       <c r="R13">
-        <v>720193869.5075126</v>
+        <v>9290500916.646914</v>
       </c>
       <c r="S13">
-        <v>708302110.8804138</v>
+        <v>9137097230.357338</v>
       </c>
     </row>
     <row r="14">
@@ -7997,58 +7997,58 @@
         </is>
       </c>
       <c r="B14">
-        <v>115316439.9604184</v>
+        <v>1487582075.489397</v>
       </c>
       <c r="C14">
-        <v>2358478.67137188</v>
+        <v>30424374.86069725</v>
       </c>
       <c r="D14">
-        <v>153889817.2182038</v>
+        <v>1985178642.114829</v>
       </c>
       <c r="E14">
-        <v>7153399.90215454</v>
+        <v>92278858.73779356</v>
       </c>
       <c r="F14">
-        <v>66776504.62650644</v>
+        <v>861416909.6819332</v>
       </c>
       <c r="G14">
-        <v>230178200.4182366</v>
+        <v>2969298785.395252</v>
       </c>
       <c r="H14">
-        <v>180344306.0339225</v>
+        <v>2326441547.837601</v>
       </c>
       <c r="I14">
-        <v>47380526.05595585</v>
+        <v>611208786.1218305</v>
       </c>
       <c r="J14">
-        <v>11090974.79622965</v>
+        <v>143073574.8713625</v>
       </c>
       <c r="K14">
-        <v>12289454.58650172</v>
+        <v>158533964.1658722</v>
       </c>
       <c r="L14">
-        <v>6439282.29268258</v>
+        <v>83066741.57560529</v>
       </c>
       <c r="M14">
-        <v>237427173.5492387</v>
+        <v>3062810538.785179</v>
       </c>
       <c r="N14">
-        <v>86253248.98652954</v>
+        <v>1112666911.926231</v>
       </c>
       <c r="O14">
-        <v>581224966.3010607</v>
+        <v>7497802065.283682</v>
       </c>
       <c r="P14">
-        <v>926719606.6797156</v>
+        <v>11954682926.16833</v>
       </c>
       <c r="Q14">
-        <v>834027075.4005034</v>
+        <v>10758949272.66649</v>
       </c>
       <c r="R14">
-        <v>718710635.4400849</v>
+        <v>9271367197.177097</v>
       </c>
       <c r="S14">
-        <v>706421180.8535833</v>
+        <v>9112833233.011227</v>
       </c>
     </row>
     <row r="15">
@@ -8058,58 +8058,58 @@
         </is>
       </c>
       <c r="B15">
-        <v>114700654.2499466</v>
+        <v>1479638439.824311</v>
       </c>
       <c r="C15">
-        <v>2623491.50012125</v>
+        <v>33843040.35156413</v>
       </c>
       <c r="D15">
-        <v>150964512.0344971</v>
+        <v>1947442205.245013</v>
       </c>
       <c r="E15">
-        <v>7714746.38361426</v>
+        <v>99520228.34862395</v>
       </c>
       <c r="F15">
-        <v>66001169.26650726</v>
+        <v>851415083.5379437</v>
       </c>
       <c r="G15">
-        <v>227303919.1847399</v>
+        <v>2932220557.483144</v>
       </c>
       <c r="H15">
-        <v>180601394.7695467</v>
+        <v>2329757992.527153</v>
       </c>
       <c r="I15">
-        <v>48106341.55660678</v>
+        <v>620571806.0802275</v>
       </c>
       <c r="J15">
-        <v>11799703.45209289</v>
+        <v>152216174.5319983</v>
       </c>
       <c r="K15">
-        <v>12463731.99309433</v>
+        <v>160782142.7109169</v>
       </c>
       <c r="L15">
-        <v>6715889.28628258</v>
+        <v>86634971.79304528</v>
       </c>
       <c r="M15">
-        <v>236338012.9073372</v>
+        <v>3048760366.504649</v>
       </c>
       <c r="N15">
-        <v>86159609.90297359</v>
+        <v>1111458967.748359</v>
       </c>
       <c r="O15">
-        <v>582184683.8679341</v>
+        <v>7510182421.89635</v>
       </c>
       <c r="P15">
-        <v>924189257.3026205</v>
+        <v>11922041419.2038</v>
       </c>
       <c r="Q15">
-        <v>831313758.1133642</v>
+        <v>10723947479.6624</v>
       </c>
       <c r="R15">
-        <v>716613103.8634177</v>
+        <v>9244309039.838089</v>
       </c>
       <c r="S15">
-        <v>704149371.8703234</v>
+        <v>9083526897.127172</v>
       </c>
     </row>
     <row r="16">
@@ -8119,58 +8119,58 @@
         </is>
       </c>
       <c r="B16">
-        <v>113689126.0787627</v>
+        <v>1466589726.416039</v>
       </c>
       <c r="C16">
-        <v>2850095.59865163</v>
+        <v>36766233.22260603</v>
       </c>
       <c r="D16">
-        <v>149476144.1283943</v>
+        <v>1928242259.256286</v>
       </c>
       <c r="E16">
-        <v>8130341.34157939</v>
+        <v>104881403.3063741</v>
       </c>
       <c r="F16">
-        <v>64889302.41563528</v>
+        <v>837072001.1616951</v>
       </c>
       <c r="G16">
-        <v>225345883.4842606</v>
+        <v>2906961896.946961</v>
       </c>
       <c r="H16">
-        <v>181409966.5553397</v>
+        <v>2340188568.563882</v>
       </c>
       <c r="I16">
-        <v>48493964.97506987</v>
+        <v>625572148.1784014</v>
       </c>
       <c r="J16">
-        <v>12164286.7785398</v>
+        <v>156919299.4431634</v>
       </c>
       <c r="K16">
-        <v>12121839.57511161</v>
+        <v>156371730.5189398</v>
       </c>
       <c r="L16">
-        <v>6436857.51014862</v>
+        <v>83035461.88091719</v>
       </c>
       <c r="M16">
-        <v>233824997.7955039</v>
+        <v>3016342471.562</v>
       </c>
       <c r="N16">
-        <v>86202185.20705415</v>
+        <v>1112008189.170999</v>
       </c>
       <c r="O16">
-        <v>580654098.3967676</v>
+        <v>7490437869.318302</v>
       </c>
       <c r="P16">
-        <v>919689107.9597909</v>
+        <v>11863989492.6813</v>
       </c>
       <c r="Q16">
-        <v>827050065.242588</v>
+        <v>10668945841.62939</v>
       </c>
       <c r="R16">
-        <v>713360939.1638255</v>
+        <v>9202356115.213348</v>
       </c>
       <c r="S16">
-        <v>701239099.5887138</v>
+        <v>9045984384.694408</v>
       </c>
     </row>
     <row r="17">
@@ -8180,58 +8180,58 @@
         </is>
       </c>
       <c r="B17">
-        <v>112802241.2146832</v>
+        <v>1455148911.669414</v>
       </c>
       <c r="C17">
-        <v>2998017.77125975</v>
+        <v>38674429.24925078</v>
       </c>
       <c r="D17">
-        <v>149097043.7219423</v>
+        <v>1923351864.013055</v>
       </c>
       <c r="E17">
-        <v>8800728.55697668</v>
+        <v>113529398.3849992</v>
       </c>
       <c r="F17">
-        <v>64014306.54870287</v>
+        <v>825784554.4782671</v>
       </c>
       <c r="G17">
-        <v>224910096.5988816</v>
+        <v>2901340246.125573</v>
       </c>
       <c r="H17">
-        <v>181588066.0530292</v>
+        <v>2342486052.084077</v>
       </c>
       <c r="I17">
-        <v>49318949.92739433</v>
+        <v>636214454.0633869</v>
       </c>
       <c r="J17">
-        <v>12773569.42662237</v>
+        <v>164779045.6034286</v>
       </c>
       <c r="K17">
-        <v>12194161.2818561</v>
+        <v>157304680.5359437</v>
       </c>
       <c r="L17">
-        <v>6127873.70378429</v>
+        <v>79049570.77881734</v>
       </c>
       <c r="M17">
-        <v>231858788.0300083</v>
+        <v>2990978365.587107</v>
       </c>
       <c r="N17">
-        <v>87107866.0682894</v>
+        <v>1123691472.280933</v>
       </c>
       <c r="O17">
-        <v>580969274.490984</v>
+        <v>7494503640.933694</v>
       </c>
       <c r="P17">
-        <v>918681612.3045487</v>
+        <v>11850992798.72868</v>
       </c>
       <c r="Q17">
-        <v>825445872.532475</v>
+        <v>10648251755.66893</v>
       </c>
       <c r="R17">
-        <v>712643631.3177919</v>
+        <v>9193102843.999516</v>
       </c>
       <c r="S17">
-        <v>700449470.0359358</v>
+        <v>9035798163.463572</v>
       </c>
     </row>
     <row r="18">
@@ -8241,58 +8241,58 @@
         </is>
       </c>
       <c r="B18">
-        <v>113143221.537675</v>
+        <v>1459547557.836007</v>
       </c>
       <c r="C18">
-        <v>2983935.16133585</v>
+        <v>38492763.58123247</v>
       </c>
       <c r="D18">
-        <v>147894805.3591982</v>
+        <v>1907842989.133657</v>
       </c>
       <c r="E18">
-        <v>9012976.11112245</v>
+        <v>116267391.8334796</v>
       </c>
       <c r="F18">
-        <v>65064494.88462498</v>
+        <v>839331984.0116622</v>
       </c>
       <c r="G18">
-        <v>224956211.5162815</v>
+        <v>2901935128.560031</v>
       </c>
       <c r="H18">
-        <v>179603401.4679316</v>
+        <v>2316883878.936318</v>
       </c>
       <c r="I18">
-        <v>50848117.55736561</v>
+        <v>655940716.4900163</v>
       </c>
       <c r="J18">
-        <v>11899703.7636502</v>
+        <v>153506178.5510876</v>
       </c>
       <c r="K18">
-        <v>11966453.7497945</v>
+        <v>154367253.3723491</v>
       </c>
       <c r="L18">
-        <v>5962268.36218708</v>
+        <v>76913261.87221333</v>
       </c>
       <c r="M18">
-        <v>230230312.9152077</v>
+        <v>2969971036.60618</v>
       </c>
       <c r="N18">
-        <v>87092172.01120235</v>
+        <v>1123489018.94451</v>
       </c>
       <c r="O18">
-        <v>577602429.8273392</v>
+        <v>7451071344.772675</v>
       </c>
       <c r="P18">
-        <v>915701862.8812957</v>
+        <v>11812554031.16871</v>
       </c>
       <c r="Q18">
-        <v>822647422.5079061</v>
+        <v>10612151750.35199</v>
       </c>
       <c r="R18">
-        <v>709504200.9702312</v>
+        <v>9152604192.515984</v>
       </c>
       <c r="S18">
-        <v>697537747.2204367</v>
+        <v>8998236939.143633</v>
       </c>
     </row>
     <row r="19">
@@ -8302,58 +8302,58 @@
         </is>
       </c>
       <c r="B19">
-        <v>113562546.9965351</v>
+        <v>1464956856.255302</v>
       </c>
       <c r="C19">
-        <v>2846279.43761497</v>
+        <v>36717004.74523311</v>
       </c>
       <c r="D19">
-        <v>146509295.4166858</v>
+        <v>1889969910.875247</v>
       </c>
       <c r="E19">
-        <v>8821688.770045839</v>
+        <v>113799785.1335913</v>
       </c>
       <c r="F19">
-        <v>66562312.21128404</v>
+        <v>858653827.5255641</v>
       </c>
       <c r="G19">
-        <v>224739575.8356307</v>
+        <v>2899140528.279636</v>
       </c>
       <c r="H19">
-        <v>176876916.2451909</v>
+        <v>2281712219.562963</v>
       </c>
       <c r="I19">
-        <v>50758316.7208659</v>
+        <v>654782285.6991701</v>
       </c>
       <c r="J19">
-        <v>11333894.63183914</v>
+        <v>146207240.7507249</v>
       </c>
       <c r="K19">
-        <v>12233897.69772909</v>
+        <v>157817280.3007053</v>
       </c>
       <c r="L19">
-        <v>5682191.73274824</v>
+        <v>73300273.35245229</v>
       </c>
       <c r="M19">
-        <v>228788875.6370167</v>
+        <v>2951376495.717516</v>
       </c>
       <c r="N19">
-        <v>88353061.72935081</v>
+        <v>1139754496.308625</v>
       </c>
       <c r="O19">
-        <v>574027154.3947408</v>
+        <v>7404950291.692157</v>
       </c>
       <c r="P19">
-        <v>912329277.2269068</v>
+        <v>11769047676.2271</v>
       </c>
       <c r="Q19">
-        <v>818294023.7648075</v>
+        <v>10555992906.56602</v>
       </c>
       <c r="R19">
-        <v>704731476.7682724</v>
+        <v>9091036050.310715</v>
       </c>
       <c r="S19">
-        <v>692497579.0705434</v>
+        <v>8933218770.01001</v>
       </c>
     </row>
     <row r="20">
@@ -8363,58 +8363,58 @@
         </is>
       </c>
       <c r="B20">
-        <v>114491553.6225518</v>
+        <v>1476941041.730919</v>
       </c>
       <c r="C20">
-        <v>2885893.72605731</v>
+        <v>37228029.0661393</v>
       </c>
       <c r="D20">
-        <v>144337087.3132343</v>
+        <v>1861948426.340722</v>
       </c>
       <c r="E20">
-        <v>8475288.34554583</v>
+        <v>109331219.6575412</v>
       </c>
       <c r="F20">
-        <v>67830730.05123428</v>
+        <v>875016417.6609221</v>
       </c>
       <c r="G20">
-        <v>223528999.4360717</v>
+        <v>2883524092.725325</v>
       </c>
       <c r="H20">
-        <v>175661196.1317103</v>
+        <v>2266029430.099063</v>
       </c>
       <c r="I20">
-        <v>49918033.71628334</v>
+        <v>643942634.9400551</v>
       </c>
       <c r="J20">
-        <v>10812045.93124696</v>
+        <v>139475392.5130858</v>
       </c>
       <c r="K20">
-        <v>12869368.9060445</v>
+        <v>166014858.8879741</v>
       </c>
       <c r="L20">
-        <v>5787071.15795433</v>
+        <v>74653217.93761086</v>
       </c>
       <c r="M20">
-        <v>230433104.2686709</v>
+        <v>2972587045.065854</v>
       </c>
       <c r="N20">
-        <v>89576526.88641888</v>
+        <v>1155537196.834804</v>
       </c>
       <c r="O20">
-        <v>575057346.9983292</v>
+        <v>7418239776.278447</v>
       </c>
       <c r="P20">
-        <v>913077900.056953</v>
+        <v>11778704910.73469</v>
       </c>
       <c r="Q20">
-        <v>817714302.0125794</v>
+        <v>10548514495.96227</v>
       </c>
       <c r="R20">
-        <v>703222748.3900276</v>
+        <v>9071573454.231358</v>
       </c>
       <c r="S20">
-        <v>690353379.4839833</v>
+        <v>8905558595.343384</v>
       </c>
     </row>
     <row r="21">
@@ -8424,58 +8424,58 @@
         </is>
       </c>
       <c r="B21">
-        <v>115784658.7293149</v>
+        <v>1493622097.608162</v>
       </c>
       <c r="C21">
-        <v>2566911.96781719</v>
+        <v>33113164.38484175</v>
       </c>
       <c r="D21">
-        <v>142687222.9929281</v>
+        <v>1840665176.608773</v>
       </c>
       <c r="E21">
-        <v>8316950.12687548</v>
+        <v>107288656.6366937</v>
       </c>
       <c r="F21">
-        <v>67780130.87459789</v>
+        <v>874363688.2823129</v>
       </c>
       <c r="G21">
-        <v>221351215.9622187</v>
+        <v>2855430685.912621</v>
       </c>
       <c r="H21">
-        <v>172924484.9099412</v>
+        <v>2230725855.338242</v>
       </c>
       <c r="I21">
-        <v>48541413.37105655</v>
+        <v>626184232.4866295</v>
       </c>
       <c r="J21">
-        <v>9854570.61171177</v>
+        <v>127123960.8910818</v>
       </c>
       <c r="K21">
-        <v>13308509.74990273</v>
+        <v>171679775.7737452</v>
       </c>
       <c r="L21">
-        <v>6247077.91004685</v>
+        <v>80587305.03960437</v>
       </c>
       <c r="M21">
-        <v>231932944.4611817</v>
+        <v>2991934983.549244</v>
       </c>
       <c r="N21">
-        <v>88436460.9407063</v>
+        <v>1140830346.135111</v>
       </c>
       <c r="O21">
-        <v>571245461.9545472</v>
+        <v>7369066459.213657</v>
       </c>
       <c r="P21">
-        <v>908381336.646081</v>
+        <v>11718119242.73444</v>
       </c>
       <c r="Q21">
-        <v>813697797.7953277</v>
+        <v>10496701591.55973</v>
       </c>
       <c r="R21">
-        <v>697913139.0660126</v>
+        <v>9003079493.951563</v>
       </c>
       <c r="S21">
-        <v>684604629.31611</v>
+        <v>8831399718.177818</v>
       </c>
     </row>
     <row r="22">
@@ -8485,58 +8485,58 @@
         </is>
       </c>
       <c r="B22">
-        <v>114424898.9423222</v>
+        <v>1476081196.355957</v>
       </c>
       <c r="C22">
-        <v>2300902.77122159</v>
+        <v>29681645.74875851</v>
       </c>
       <c r="D22">
-        <v>140818249.1053465</v>
+        <v>1816555413.45897</v>
       </c>
       <c r="E22">
-        <v>8109670.85362098</v>
+        <v>104614754.0117106</v>
       </c>
       <c r="F22">
-        <v>66230443.52542068</v>
+        <v>854372721.4779267</v>
       </c>
       <c r="G22">
-        <v>217459266.2556098</v>
+        <v>2805224534.697367</v>
       </c>
       <c r="H22">
-        <v>172974613.0155523</v>
+        <v>2231372507.900624</v>
       </c>
       <c r="I22">
-        <v>47426936.85080473</v>
+        <v>611807485.375381</v>
       </c>
       <c r="J22">
-        <v>10365038.56937487</v>
+        <v>133708997.5449358</v>
       </c>
       <c r="K22">
-        <v>13407020.83229467</v>
+        <v>172950568.7366013</v>
       </c>
       <c r="L22">
-        <v>6404580.30916718</v>
+        <v>82619085.98825663</v>
       </c>
       <c r="M22">
-        <v>233398215.6783957</v>
+        <v>3010836982.251306</v>
       </c>
       <c r="N22">
-        <v>87793305.34109657</v>
+        <v>1132533638.900146</v>
       </c>
       <c r="O22">
-        <v>571769710.596686</v>
+        <v>7375829266.697249</v>
       </c>
       <c r="P22">
-        <v>903653875.7946181</v>
+        <v>11657134997.75057</v>
       </c>
       <c r="Q22">
-        <v>809455990.1443543</v>
+        <v>10441982272.86217</v>
       </c>
       <c r="R22">
-        <v>695031091.202032</v>
+        <v>8965901076.506214</v>
       </c>
       <c r="S22">
-        <v>681624070.3697375</v>
+        <v>8792950507.769613</v>
       </c>
     </row>
     <row r="23">
@@ -8546,58 +8546,58 @@
         </is>
       </c>
       <c r="B23">
-        <v>114348221.5362875</v>
+        <v>1475092057.81811</v>
       </c>
       <c r="C23">
-        <v>2338055.39525967</v>
+        <v>30160914.59884974</v>
       </c>
       <c r="D23">
-        <v>139483887.3776954</v>
+        <v>1799342147.172271</v>
       </c>
       <c r="E23">
-        <v>8400247.931504721</v>
+        <v>108363198.3164109</v>
       </c>
       <c r="F23">
-        <v>63228857.80683273</v>
+        <v>815652265.7081423</v>
       </c>
       <c r="G23">
-        <v>213451048.5112926</v>
+        <v>2753518525.795674</v>
       </c>
       <c r="H23">
-        <v>174744235.4071059</v>
+        <v>2254200636.751667</v>
       </c>
       <c r="I23">
-        <v>47846944.59101686</v>
+        <v>617225585.2241175</v>
       </c>
       <c r="J23">
-        <v>10270757.80635806</v>
+        <v>132492775.702019</v>
       </c>
       <c r="K23">
-        <v>12987177.74643875</v>
+        <v>167534592.9290599</v>
       </c>
       <c r="L23">
-        <v>7012944.61557954</v>
+        <v>90466985.54097608</v>
       </c>
       <c r="M23">
-        <v>235220715.0938912</v>
+        <v>3034347224.711197</v>
       </c>
       <c r="N23">
-        <v>87099058.33764438</v>
+        <v>1123577852.555613</v>
       </c>
       <c r="O23">
-        <v>575181833.5980347</v>
+        <v>7419845653.414648</v>
       </c>
       <c r="P23">
-        <v>902981103.645615</v>
+        <v>11648456237.02843</v>
       </c>
       <c r="Q23">
-        <v>808869100.6923909</v>
+        <v>10434411398.93184</v>
       </c>
       <c r="R23">
-        <v>694520879.1561033</v>
+        <v>8959319341.113733</v>
       </c>
       <c r="S23">
-        <v>681533701.4096646</v>
+        <v>8791784748.184673</v>
       </c>
     </row>
     <row r="24">
@@ -8607,58 +8607,58 @@
         </is>
       </c>
       <c r="B24">
-        <v>114348126.9598527</v>
+        <v>1475090837.782099</v>
       </c>
       <c r="C24">
-        <v>2020115.33816233</v>
+        <v>26059487.86229406</v>
       </c>
       <c r="D24">
-        <v>138817291.5690255</v>
+        <v>1790743061.240429</v>
       </c>
       <c r="E24">
-        <v>9101487.660672201</v>
+        <v>117409190.8226714</v>
       </c>
       <c r="F24">
-        <v>61844456.82129007</v>
+        <v>797793492.9946419</v>
       </c>
       <c r="G24">
-        <v>211783351.3891501</v>
+        <v>2732005232.920036</v>
       </c>
       <c r="H24">
-        <v>174277895.9105458</v>
+        <v>2248184857.24604</v>
       </c>
       <c r="I24">
-        <v>48635759.81330234</v>
+        <v>627401301.5916002</v>
       </c>
       <c r="J24">
-        <v>10271339.67317983</v>
+        <v>132500281.7840198</v>
       </c>
       <c r="K24">
-        <v>12637055.48730254</v>
+        <v>163018015.7862028</v>
       </c>
       <c r="L24">
-        <v>7367591.56871484</v>
+        <v>95041931.23642144</v>
       </c>
       <c r="M24">
-        <v>236111138.0965558</v>
+        <v>3045833681.44557</v>
       </c>
       <c r="N24">
-        <v>85969274.80828685</v>
+        <v>1109003645.0269</v>
       </c>
       <c r="O24">
-        <v>575270055.357888</v>
+        <v>7420983714.116755</v>
       </c>
       <c r="P24">
-        <v>901401533.7068908</v>
+        <v>11628079784.81889</v>
       </c>
       <c r="Q24">
-        <v>808064667.3298891</v>
+        <v>10424034208.55557</v>
       </c>
       <c r="R24">
-        <v>693716540.3700362</v>
+        <v>8948943370.773468</v>
       </c>
       <c r="S24">
-        <v>681079484.8827338</v>
+        <v>8785925354.987267</v>
       </c>
     </row>
     <row r="25">
@@ -8668,58 +8668,58 @@
         </is>
       </c>
       <c r="B25">
-        <v>112896306.474921</v>
+        <v>1456362353.52648</v>
       </c>
       <c r="C25">
-        <v>2126578.24333975</v>
+        <v>27432859.33908277</v>
       </c>
       <c r="D25">
-        <v>137196397.486758</v>
+        <v>1769833527.579178</v>
       </c>
       <c r="E25">
-        <v>9436832.604774071</v>
+        <v>121735140.6015855</v>
       </c>
       <c r="F25">
-        <v>60726700.29445508</v>
+        <v>783374433.7984705</v>
       </c>
       <c r="G25">
-        <v>209486508.6293269</v>
+        <v>2702375961.318317</v>
       </c>
       <c r="H25">
-        <v>174948346.0802983</v>
+        <v>2256833664.435848</v>
       </c>
       <c r="I25">
-        <v>49916178.12191322</v>
+        <v>643918697.7726805</v>
       </c>
       <c r="J25">
-        <v>10339258.05417783</v>
+        <v>133376428.898894</v>
       </c>
       <c r="K25">
-        <v>12351692.41531259</v>
+        <v>159336832.1575324</v>
       </c>
       <c r="L25">
-        <v>7032752.10883475</v>
+        <v>90722502.20396829</v>
       </c>
       <c r="M25">
-        <v>236279136.5547456</v>
+        <v>3048000861.556219</v>
       </c>
       <c r="N25">
-        <v>87275129.62505549</v>
+        <v>1125849172.163216</v>
       </c>
       <c r="O25">
-        <v>578142492.9603379</v>
+        <v>7458038159.188359</v>
       </c>
       <c r="P25">
-        <v>900525308.0645857</v>
+        <v>11616776474.03316</v>
       </c>
       <c r="Q25">
-        <v>806217426.3306954</v>
+        <v>10400204799.66597</v>
       </c>
       <c r="R25">
-        <v>693321119.8557744</v>
+        <v>8943842446.13949</v>
       </c>
       <c r="S25">
-        <v>680969427.4404619</v>
+        <v>8784505613.981958</v>
       </c>
     </row>
     <row r="26">
@@ -8729,58 +8729,58 @@
         </is>
       </c>
       <c r="B26">
-        <v>110496018.8090051</v>
+        <v>1425398642.636167</v>
       </c>
       <c r="C26">
-        <v>2355279.50155069</v>
+        <v>30383105.5700039</v>
       </c>
       <c r="D26">
-        <v>136323467.3933719</v>
+        <v>1758572729.374497</v>
       </c>
       <c r="E26">
-        <v>9678573.51300345</v>
+        <v>124853598.3177445</v>
       </c>
       <c r="F26">
-        <v>61607127.0480085</v>
+        <v>794731938.9193096</v>
       </c>
       <c r="G26">
-        <v>209964447.4559345</v>
+        <v>2708541372.181556</v>
       </c>
       <c r="H26">
-        <v>174880483.0332644</v>
+        <v>2255958231.129111</v>
       </c>
       <c r="I26">
-        <v>50556649.21254985</v>
+        <v>652180774.8418931</v>
       </c>
       <c r="J26">
-        <v>10377646.38528724</v>
+        <v>133871638.3702054</v>
       </c>
       <c r="K26">
-        <v>11816831.18339524</v>
+        <v>152437122.2657986</v>
       </c>
       <c r="L26">
-        <v>7064980.418437241</v>
+        <v>91138247.39784041</v>
       </c>
       <c r="M26">
-        <v>234861965.412983</v>
+        <v>3029719353.82748</v>
       </c>
       <c r="N26">
-        <v>87256365.91759133</v>
+        <v>1125607120.336928</v>
       </c>
       <c r="O26">
-        <v>576814921.5635084</v>
+        <v>7440912488.169259</v>
       </c>
       <c r="P26">
-        <v>897275387.8284481</v>
+        <v>11574852502.98698</v>
       </c>
       <c r="Q26">
-        <v>802954041.4924194</v>
+        <v>10358107135.25221</v>
       </c>
       <c r="R26">
-        <v>692458022.6834142</v>
+        <v>8932708492.616043</v>
       </c>
       <c r="S26">
-        <v>680641191.500019</v>
+        <v>8780271370.350246</v>
       </c>
     </row>
     <row r="27">
@@ -8790,58 +8790,58 @@
         </is>
       </c>
       <c r="B27">
-        <v>108627224.8262284</v>
+        <v>1401291200.258347</v>
       </c>
       <c r="C27">
-        <v>2329961.89880614</v>
+        <v>30056508.49459921</v>
       </c>
       <c r="D27">
-        <v>137487929.8205998</v>
+        <v>1773594294.685737</v>
       </c>
       <c r="E27">
-        <v>9724677.15892981</v>
+        <v>125448335.3501946</v>
       </c>
       <c r="F27">
-        <v>62916801.17709159</v>
+        <v>811626735.1844815</v>
       </c>
       <c r="G27">
-        <v>212459370.0554273</v>
+        <v>2740725873.715013</v>
       </c>
       <c r="H27">
-        <v>173052633.3183087</v>
+        <v>2232378969.806181</v>
       </c>
       <c r="I27">
-        <v>50178497.7255197</v>
+        <v>647302620.6592042</v>
       </c>
       <c r="J27">
-        <v>10754215.02394495</v>
+        <v>138729373.8088899</v>
       </c>
       <c r="K27">
-        <v>11884578.27388365</v>
+        <v>153311059.7330991</v>
       </c>
       <c r="L27">
-        <v>6661552.244671401</v>
+        <v>85934023.95626107</v>
       </c>
       <c r="M27">
-        <v>233303875.2168273</v>
+        <v>3009619990.297072</v>
       </c>
       <c r="N27">
-        <v>87265468.28968883</v>
+        <v>1125724540.936986</v>
       </c>
       <c r="O27">
-        <v>573100820.0928446</v>
+        <v>7393000579.197696</v>
       </c>
       <c r="P27">
-        <v>894187414.9745002</v>
+        <v>11535017653.17105</v>
       </c>
       <c r="Q27">
-        <v>800260394.44014</v>
+        <v>10323359088.27781</v>
       </c>
       <c r="R27">
-        <v>691633169.6139115</v>
+        <v>8922067888.019459</v>
       </c>
       <c r="S27">
-        <v>679748591.3400279</v>
+        <v>8768756828.28636</v>
       </c>
     </row>
     <row r="28">
@@ -8851,58 +8851,58 @@
         </is>
       </c>
       <c r="B28">
-        <v>106545630.679455</v>
+        <v>1374438635.76497</v>
       </c>
       <c r="C28">
-        <v>2159825.6727266</v>
+        <v>27861751.17817314</v>
       </c>
       <c r="D28">
-        <v>137483949.041438</v>
+        <v>1773542942.63455</v>
       </c>
       <c r="E28">
-        <v>9648275.1321858</v>
+        <v>124462749.2051968</v>
       </c>
       <c r="F28">
-        <v>63918844.47439402</v>
+        <v>824553093.7196828</v>
       </c>
       <c r="G28">
-        <v>213210894.3207445</v>
+        <v>2750420536.737603</v>
       </c>
       <c r="H28">
-        <v>171589638.4000911</v>
+        <v>2213506335.361175</v>
       </c>
       <c r="I28">
-        <v>50022807.53459712</v>
+        <v>645294217.1963029</v>
       </c>
       <c r="J28">
-        <v>11076873.03460792</v>
+        <v>142891662.1464422</v>
       </c>
       <c r="K28">
-        <v>11452895.91085452</v>
+        <v>147742357.2500233</v>
       </c>
       <c r="L28">
-        <v>6452523.773295891</v>
+        <v>83237556.67551698</v>
       </c>
       <c r="M28">
-        <v>232295850.5536499</v>
+        <v>2996616472.142084</v>
       </c>
       <c r="N28">
-        <v>88087574.63319461</v>
+        <v>1136329712.76821</v>
       </c>
       <c r="O28">
-        <v>570978163.840291</v>
+        <v>7365618313.539755</v>
       </c>
       <c r="P28">
-        <v>890734688.8404906</v>
+        <v>11490477486.04233</v>
       </c>
       <c r="Q28">
-        <v>796194590.434</v>
+        <v>10270910216.5986</v>
       </c>
       <c r="R28">
-        <v>689648959.754545</v>
+        <v>8896471580.833632</v>
       </c>
       <c r="S28">
-        <v>678196063.8436904</v>
+        <v>8748729223.583607</v>
       </c>
     </row>
     <row r="29">
@@ -8912,58 +8912,58 @@
         </is>
       </c>
       <c r="B29">
-        <v>106373844.9442034</v>
+        <v>1372222599.780224</v>
       </c>
       <c r="C29">
-        <v>1792667.68822664</v>
+        <v>23125413.17812366</v>
       </c>
       <c r="D29">
-        <v>137904452.8013743</v>
+        <v>1778967441.137728</v>
       </c>
       <c r="E29">
-        <v>9400314.64948778</v>
+        <v>121264058.9783924</v>
       </c>
       <c r="F29">
-        <v>64397423.44545153</v>
+        <v>830726762.4463247</v>
       </c>
       <c r="G29">
-        <v>213494858.5845402</v>
+        <v>2754083675.740569</v>
       </c>
       <c r="H29">
-        <v>171051140.6046569</v>
+        <v>2206559713.800075</v>
       </c>
       <c r="I29">
-        <v>49395769.49286105</v>
+        <v>637205426.4579077</v>
       </c>
       <c r="J29">
-        <v>11663850.02641414</v>
+        <v>150463665.3407424</v>
       </c>
       <c r="K29">
-        <v>10899373.07652639</v>
+        <v>140601912.6871904</v>
       </c>
       <c r="L29">
-        <v>6693785.8440784</v>
+        <v>86349837.38861136</v>
       </c>
       <c r="M29">
-        <v>235177518.4010169</v>
+        <v>3033789987.373118</v>
       </c>
       <c r="N29">
-        <v>88162288.07967918</v>
+        <v>1137293516.227861</v>
       </c>
       <c r="O29">
-        <v>573043725.525233</v>
+        <v>7392264059.275506</v>
       </c>
       <c r="P29">
-        <v>892912429.0539767</v>
+        <v>11518570334.7963</v>
       </c>
       <c r="Q29">
-        <v>798056355.130219</v>
+        <v>10294926981.17982</v>
       </c>
       <c r="R29">
-        <v>691682510.1860157</v>
+        <v>8922704381.399603</v>
       </c>
       <c r="S29">
-        <v>680783137.1094892</v>
+        <v>8782102468.712412</v>
       </c>
     </row>
     <row r="30">
@@ -8973,58 +8973,58 @@
         </is>
       </c>
       <c r="B30">
-        <v>107545185.7254146</v>
+        <v>1387332895.857848</v>
       </c>
       <c r="C30">
-        <v>1495306.56783962</v>
+        <v>19289454.7251311</v>
       </c>
       <c r="D30">
-        <v>137666707.8525163</v>
+        <v>1775900531.29746</v>
       </c>
       <c r="E30">
-        <v>9307525.861461161</v>
+        <v>120067083.612849</v>
       </c>
       <c r="F30">
-        <v>63607933.57977176</v>
+        <v>820542343.1790557</v>
       </c>
       <c r="G30">
-        <v>212077473.8615888</v>
+        <v>2735799412.814496</v>
       </c>
       <c r="H30">
-        <v>170833703.4158289</v>
+        <v>2203754774.064194</v>
       </c>
       <c r="I30">
-        <v>48979631.75045358</v>
+        <v>631837249.5808513</v>
       </c>
       <c r="J30">
-        <v>12578577.33174207</v>
+        <v>162263647.5794727</v>
       </c>
       <c r="K30">
-        <v>10791470.96186999</v>
+        <v>139209975.4081229</v>
       </c>
       <c r="L30">
-        <v>6768427.1103237</v>
+        <v>87312709.72317573</v>
       </c>
       <c r="M30">
-        <v>239513726.1490352</v>
+        <v>3089727067.322554</v>
       </c>
       <c r="N30">
-        <v>89033440.18136261</v>
+        <v>1148531378.339578</v>
       </c>
       <c r="O30">
-        <v>578498976.9006159</v>
+        <v>7462636802.017946</v>
       </c>
       <c r="P30">
-        <v>898121636.4876194</v>
+        <v>11585769110.69029</v>
       </c>
       <c r="Q30">
-        <v>802319769.1959331</v>
+        <v>10349925022.62754</v>
       </c>
       <c r="R30">
-        <v>694774583.4705186</v>
+        <v>8962592126.76969</v>
       </c>
       <c r="S30">
-        <v>683983112.5086486</v>
+        <v>8823382151.361567</v>
       </c>
     </row>
     <row r="31">
@@ -9034,58 +9034,58 @@
         </is>
       </c>
       <c r="B31">
-        <v>109089587.4427743</v>
+        <v>1407255678.011788</v>
       </c>
       <c r="C31">
-        <v>1472968.93347926</v>
+        <v>19001299.24188245</v>
       </c>
       <c r="D31">
-        <v>136129275.052359</v>
+        <v>1756067648.175431</v>
       </c>
       <c r="E31">
-        <v>9094699.27955913</v>
+        <v>117321620.7063128</v>
       </c>
       <c r="F31">
-        <v>63991214.89283669</v>
+        <v>825486672.1175933</v>
       </c>
       <c r="G31">
-        <v>210688158.1582341</v>
+        <v>2717877240.24122</v>
       </c>
       <c r="H31">
-        <v>172029047.3744988</v>
+        <v>2219174711.131035</v>
       </c>
       <c r="I31">
-        <v>50226062.00426456</v>
+        <v>647916199.8550129</v>
       </c>
       <c r="J31">
-        <v>13453658.33060616</v>
+        <v>173552192.4648195</v>
       </c>
       <c r="K31">
-        <v>10554774.89145235</v>
+        <v>136156596.0997353</v>
       </c>
       <c r="L31">
-        <v>6746172.37927295</v>
+        <v>87025623.69262105</v>
       </c>
       <c r="M31">
-        <v>242866500.4644023</v>
+        <v>3132977855.99079</v>
       </c>
       <c r="N31">
-        <v>90356553.4648536</v>
+        <v>1165599539.696611</v>
       </c>
       <c r="O31">
-        <v>586232768.9093506</v>
+        <v>7562402718.930624</v>
       </c>
       <c r="P31">
-        <v>906010514.5103593</v>
+        <v>11687535637.18363</v>
       </c>
       <c r="Q31">
-        <v>808907788.6662326</v>
+        <v>10434910473.7944</v>
       </c>
       <c r="R31">
-        <v>699818201.2234584</v>
+        <v>9027654795.782614</v>
       </c>
       <c r="S31">
-        <v>689263426.332006</v>
+        <v>8891498199.682877</v>
       </c>
     </row>
     <row r="32">
@@ -9095,58 +9095,58 @@
         </is>
       </c>
       <c r="B32">
-        <v>108688960.6978928</v>
+        <v>1402087593.002817</v>
       </c>
       <c r="C32">
-        <v>1624430.31590017</v>
+        <v>20955151.07511219</v>
       </c>
       <c r="D32">
-        <v>136065558.5789517</v>
+        <v>1755245705.668476</v>
       </c>
       <c r="E32">
-        <v>8535893.116765959</v>
+        <v>110113021.2062809</v>
       </c>
       <c r="F32">
-        <v>63499638.51671889</v>
+        <v>819145336.8656738</v>
       </c>
       <c r="G32">
-        <v>209725520.5283366</v>
+        <v>2705459214.815543</v>
       </c>
       <c r="H32">
-        <v>174293181.1282701</v>
+        <v>2248382036.554684</v>
       </c>
       <c r="I32">
-        <v>52359554.53441551</v>
+        <v>675438253.4939601</v>
       </c>
       <c r="J32">
-        <v>14076229.35510358</v>
+        <v>181583358.6808362</v>
       </c>
       <c r="K32">
-        <v>10597469.2283286</v>
+        <v>136707353.0454389</v>
       </c>
       <c r="L32">
-        <v>6473534.32079492</v>
+        <v>83508592.73825447</v>
       </c>
       <c r="M32">
-        <v>243183871.0991325</v>
+        <v>3137071937.178809</v>
       </c>
       <c r="N32">
-        <v>91257864.46108887</v>
+        <v>1177226451.548047</v>
       </c>
       <c r="O32">
-        <v>592241704.127134</v>
+        <v>7639917983.240028</v>
       </c>
       <c r="P32">
-        <v>910656185.3533635</v>
+        <v>11747464791.05839</v>
       </c>
       <c r="Q32">
-        <v>812924786.5714797</v>
+        <v>10486729746.77209</v>
       </c>
       <c r="R32">
-        <v>704235825.8735869</v>
+        <v>9084642153.769272</v>
       </c>
       <c r="S32">
-        <v>693638356.6452583</v>
+        <v>8947934800.723831</v>
       </c>
     </row>
     <row r="33">
@@ -9156,58 +9156,58 @@
         </is>
       </c>
       <c r="B33">
-        <v>107266796.1118822</v>
+        <v>1383741669.843281</v>
       </c>
       <c r="C33">
-        <v>1890724.95801566</v>
+        <v>24390351.95840202</v>
       </c>
       <c r="D33">
-        <v>137390539.3233927</v>
+        <v>1772337957.271767</v>
       </c>
       <c r="E33">
-        <v>7690925.122453639</v>
+        <v>99212934.07965195</v>
       </c>
       <c r="F33">
-        <v>63224005.3606239</v>
+        <v>815589669.1520483</v>
       </c>
       <c r="G33">
-        <v>210196194.764486</v>
+        <v>2711530912.461869</v>
       </c>
       <c r="H33">
-        <v>176695190.0192297</v>
+        <v>2279367951.248063</v>
       </c>
       <c r="I33">
-        <v>54224620.01302592</v>
+        <v>699497598.1680344</v>
       </c>
       <c r="J33">
-        <v>14461226.26397158</v>
+        <v>186549818.8052334</v>
       </c>
       <c r="K33">
-        <v>10302168.55997068</v>
+        <v>132897974.4236218</v>
       </c>
       <c r="L33">
-        <v>6442034.57839164</v>
+        <v>83102246.06125216</v>
       </c>
       <c r="M33">
-        <v>243838692.402527</v>
+        <v>3145519131.992598</v>
       </c>
       <c r="N33">
-        <v>91388305.897312</v>
+        <v>1178909146.075325</v>
       </c>
       <c r="O33">
-        <v>597352237.7344285</v>
+        <v>7705843866.774128</v>
       </c>
       <c r="P33">
-        <v>914815228.6107968</v>
+        <v>11801116449.07928</v>
       </c>
       <c r="Q33">
-        <v>816984888.1350931</v>
+        <v>10539105056.9427</v>
       </c>
       <c r="R33">
-        <v>709718092.0232108</v>
+        <v>9155363387.099419</v>
       </c>
       <c r="S33">
-        <v>699415923.4632401</v>
+        <v>9022465412.675797</v>
       </c>
     </row>
     <row r="34">
@@ -9217,58 +9217,58 @@
         </is>
       </c>
       <c r="B34">
-        <v>105804556.2085769</v>
+        <v>1364878775.090643</v>
       </c>
       <c r="C34">
-        <v>1919722.49822381</v>
+        <v>24764420.22708715</v>
       </c>
       <c r="D34">
-        <v>137109650.2492104</v>
+        <v>1768714488.214814</v>
       </c>
       <c r="E34">
-        <v>6848669.76334876</v>
+        <v>88347839.947199</v>
       </c>
       <c r="F34">
-        <v>63247787.84192166</v>
+        <v>815896463.1607895</v>
       </c>
       <c r="G34">
-        <v>209125830.3527046</v>
+        <v>2697723211.549889</v>
       </c>
       <c r="H34">
-        <v>175867302.6180188</v>
+        <v>2268688203.772442</v>
       </c>
       <c r="I34">
-        <v>56019934.57130156</v>
+        <v>722657155.9697902</v>
       </c>
       <c r="J34">
-        <v>14324742.38939615</v>
+        <v>184789176.8232103</v>
       </c>
       <c r="K34">
-        <v>9892365.59515018</v>
+        <v>127611516.1774373</v>
       </c>
       <c r="L34">
-        <v>6078105.33521614</v>
+        <v>78407558.8242882</v>
       </c>
       <c r="M34">
-        <v>242510665.3610689</v>
+        <v>3128387583.157789</v>
       </c>
       <c r="N34">
-        <v>92577350.68568859</v>
+        <v>1194247823.845383</v>
       </c>
       <c r="O34">
-        <v>597270466.5558404</v>
+        <v>7704789018.570341</v>
       </c>
       <c r="P34">
-        <v>912200853.1171219</v>
+        <v>11767391005.21087</v>
       </c>
       <c r="Q34">
-        <v>813545397.0962172</v>
+        <v>10494735622.5412</v>
       </c>
       <c r="R34">
-        <v>707740840.8876402</v>
+        <v>9129856847.450558</v>
       </c>
       <c r="S34">
-        <v>697848475.29249</v>
+        <v>9002245331.273121</v>
       </c>
     </row>
     <row r="35">
@@ -9278,58 +9278,58 @@
         </is>
       </c>
       <c r="B35">
-        <v>105140806.5015677</v>
+        <v>1356316403.870224</v>
       </c>
       <c r="C35">
-        <v>1719109.20421082</v>
+        <v>22176508.73431958</v>
       </c>
       <c r="D35">
-        <v>133289012.6963421</v>
+        <v>1719428263.782813</v>
       </c>
       <c r="E35">
-        <v>6767525.45114821</v>
+        <v>87301078.31981191</v>
       </c>
       <c r="F35">
-        <v>60906979.0934957</v>
+        <v>785700030.3060945</v>
       </c>
       <c r="G35">
-        <v>202682626.4451968</v>
+        <v>2614605881.143039</v>
       </c>
       <c r="H35">
-        <v>169878606.6192357</v>
+        <v>2191434025.388141</v>
       </c>
       <c r="I35">
-        <v>55011634.47921169</v>
+        <v>709650084.7818308</v>
       </c>
       <c r="J35">
-        <v>13759281.99249792</v>
+        <v>177494737.7032232</v>
       </c>
       <c r="K35">
-        <v>9441827.441094581</v>
+        <v>121799573.9901201</v>
       </c>
       <c r="L35">
-        <v>5734961.40308717</v>
+        <v>73981002.09982449</v>
       </c>
       <c r="M35">
-        <v>237572869.4076141</v>
+        <v>3064690015.358222</v>
       </c>
       <c r="N35">
-        <v>92274149.88868235</v>
+        <v>1190336533.564003</v>
       </c>
       <c r="O35">
-        <v>583673331.2314235</v>
+        <v>7529385972.885364</v>
       </c>
       <c r="P35">
-        <v>891496764.1781881</v>
+        <v>11500308257.89863</v>
       </c>
       <c r="Q35">
-        <v>793487652.8864186</v>
+        <v>10235990722.2348</v>
       </c>
       <c r="R35">
-        <v>688346846.3848507</v>
+        <v>8879674318.364574</v>
       </c>
       <c r="S35">
-        <v>678905018.9437561</v>
+        <v>8757874744.374454</v>
       </c>
     </row>
     <row r="36">
@@ -9339,58 +9339,58 @@
         </is>
       </c>
       <c r="B36">
-        <v>106789430.6172024</v>
+        <v>1377583654.961911</v>
       </c>
       <c r="C36">
-        <v>1566030.49827694</v>
+        <v>20201793.42777253</v>
       </c>
       <c r="D36">
-        <v>129486126.2439263</v>
+        <v>1670371028.546649</v>
       </c>
       <c r="E36">
-        <v>6626439.74536934</v>
+        <v>85481072.71526448</v>
       </c>
       <c r="F36">
-        <v>58231118.22742927</v>
+        <v>751181425.1338376</v>
       </c>
       <c r="G36">
-        <v>195909714.7150018</v>
+        <v>2527235319.823524</v>
       </c>
       <c r="H36">
-        <v>162667157.7510633</v>
+        <v>2098406334.988716</v>
       </c>
       <c r="I36">
-        <v>52069085.37076323</v>
+        <v>671691201.2828457</v>
       </c>
       <c r="J36">
-        <v>14283084.70750293</v>
+        <v>184251792.7267878</v>
       </c>
       <c r="K36">
-        <v>9967109.184215069</v>
+        <v>128575708.4763744</v>
       </c>
       <c r="L36">
-        <v>5352648.32256923</v>
+        <v>69049163.36114307</v>
       </c>
       <c r="M36">
-        <v>230339392.6893654</v>
+        <v>2971378165.692814</v>
       </c>
       <c r="N36">
-        <v>90149713.91087671</v>
+        <v>1162931309.45031</v>
       </c>
       <c r="O36">
-        <v>564828191.9363558</v>
+        <v>7286283675.978991</v>
       </c>
       <c r="P36">
-        <v>867527337.2685601</v>
+        <v>11191102650.76443</v>
       </c>
       <c r="Q36">
-        <v>772024975.035114</v>
+        <v>9959122177.952972</v>
       </c>
       <c r="R36">
-        <v>665235544.4179118</v>
+        <v>8581538522.99106</v>
       </c>
       <c r="S36">
-        <v>655268435.2336966</v>
+        <v>8452962814.514687</v>
       </c>
     </row>
     <row r="37">
@@ -9400,58 +9400,58 @@
         </is>
       </c>
       <c r="B37">
-        <v>110840131.6884345</v>
+        <v>1429837698.780805</v>
       </c>
       <c r="C37">
-        <v>1302058.07154814</v>
+        <v>16796549.12297101</v>
       </c>
       <c r="D37">
-        <v>123394936.0741042</v>
+        <v>1591794675.355944</v>
       </c>
       <c r="E37">
-        <v>7124481.97061727</v>
+        <v>91905817.42096278</v>
       </c>
       <c r="F37">
-        <v>55254024.86049213</v>
+        <v>712776920.7003485</v>
       </c>
       <c r="G37">
-        <v>187075500.9767617</v>
+        <v>2413273962.600225</v>
       </c>
       <c r="H37">
-        <v>158596834.6035907</v>
+        <v>2045899166.38632</v>
       </c>
       <c r="I37">
-        <v>49528492.64994369</v>
+        <v>638917555.1842737</v>
       </c>
       <c r="J37">
-        <v>14614048.26879882</v>
+        <v>188521222.6675048</v>
       </c>
       <c r="K37">
-        <v>11643520.23205022</v>
+        <v>150201410.9934478</v>
       </c>
       <c r="L37">
-        <v>4552345.25595348</v>
+        <v>58725253.80179989</v>
       </c>
       <c r="M37">
-        <v>222903536.7928797</v>
+        <v>2875455624.628149</v>
       </c>
       <c r="N37">
-        <v>89123158.13045299</v>
+        <v>1149688739.882844</v>
       </c>
       <c r="O37">
-        <v>550961935.9336696</v>
+        <v>7107408973.544338</v>
       </c>
       <c r="P37">
-        <v>848877568.5988659</v>
+        <v>10950520634.92537</v>
       </c>
       <c r="Q37">
-        <v>755202065.2124593</v>
+        <v>9742106641.240726</v>
       </c>
       <c r="R37">
-        <v>644361933.5240248</v>
+        <v>8312268942.45992</v>
       </c>
       <c r="S37">
-        <v>632718413.2919745</v>
+        <v>8162067531.466473</v>
       </c>
     </row>
     <row r="38">
@@ -9461,58 +9461,58 @@
         </is>
       </c>
       <c r="B38">
-        <v>113138285.7108243</v>
+        <v>1459483885.669633</v>
       </c>
       <c r="C38">
-        <v>1376701.60377926</v>
+        <v>17759450.68875245</v>
       </c>
       <c r="D38">
-        <v>119420347.1035236</v>
+        <v>1540522477.635455</v>
       </c>
       <c r="E38">
-        <v>7681686.26309181</v>
+        <v>99093752.79388435</v>
       </c>
       <c r="F38">
-        <v>52166791.19032894</v>
+        <v>672951606.3552433</v>
       </c>
       <c r="G38">
-        <v>180645526.1607236</v>
+        <v>2330327287.473335</v>
       </c>
       <c r="H38">
-        <v>157548576.6518709</v>
+        <v>2032376638.809135</v>
       </c>
       <c r="I38">
-        <v>45931164.19376144</v>
+        <v>592512018.0995226</v>
       </c>
       <c r="J38">
-        <v>15060054.51895442</v>
+        <v>194274703.294512</v>
       </c>
       <c r="K38">
-        <v>13900182.86656179</v>
+        <v>179312358.9786471</v>
       </c>
       <c r="L38">
-        <v>4228126.0265588</v>
+        <v>54542825.74260852</v>
       </c>
       <c r="M38">
-        <v>220529629.0580446</v>
+        <v>2844832214.848775</v>
       </c>
       <c r="N38">
-        <v>87283793.28393422</v>
+        <v>1125960933.362751</v>
       </c>
       <c r="O38">
-        <v>544481526.5996861</v>
+        <v>7023811693.135951</v>
       </c>
       <c r="P38">
-        <v>838265338.4712341</v>
+        <v>10813622866.27892</v>
       </c>
       <c r="Q38">
-        <v>746753419.160741</v>
+        <v>9633119107.173559</v>
       </c>
       <c r="R38">
-        <v>633615133.4499167</v>
+        <v>8173635221.503925</v>
       </c>
       <c r="S38">
-        <v>619714950.5833549</v>
+        <v>7994322862.52528</v>
       </c>
     </row>
     <row r="39">
@@ -9522,58 +9522,58 @@
         </is>
       </c>
       <c r="B39">
-        <v>117682106.8178985</v>
+        <v>1518099177.95089</v>
       </c>
       <c r="C39">
-        <v>1562111.68050538</v>
+        <v>20151240.6785194</v>
       </c>
       <c r="D39">
-        <v>119542859.5283919</v>
+        <v>1542102887.916256</v>
       </c>
       <c r="E39">
-        <v>7697652.14968787</v>
+        <v>99299712.73097353</v>
       </c>
       <c r="F39">
-        <v>52606508.51723989</v>
+        <v>678623959.8723946</v>
       </c>
       <c r="G39">
-        <v>181409131.875825</v>
+        <v>2340177801.198143</v>
       </c>
       <c r="H39">
-        <v>163171181.975982</v>
+        <v>2104908247.490168</v>
       </c>
       <c r="I39">
-        <v>44355781.86395722</v>
+        <v>572189586.0450481</v>
       </c>
       <c r="J39">
-        <v>15955466.80048195</v>
+        <v>205825521.7262172</v>
       </c>
       <c r="K39">
-        <v>15916019.74450632</v>
+        <v>205316654.7041315</v>
       </c>
       <c r="L39">
-        <v>4075026.13293252</v>
+        <v>52567837.11482951</v>
       </c>
       <c r="M39">
-        <v>219571909.5611635</v>
+        <v>2832477633.339009</v>
       </c>
       <c r="N39">
-        <v>87088404.9572688</v>
+        <v>1123440423.948768</v>
       </c>
       <c r="O39">
-        <v>550133791.0362923</v>
+        <v>7096725904.368172</v>
       </c>
       <c r="P39">
-        <v>849225029.7300159</v>
+        <v>10955002883.51721</v>
       </c>
       <c r="Q39">
-        <v>758061598.6398145</v>
+        <v>9778994622.453606</v>
       </c>
       <c r="R39">
-        <v>640379491.821916</v>
+        <v>8260895444.502717</v>
       </c>
       <c r="S39">
-        <v>624463472.0774097</v>
+        <v>8055578789.798586</v>
       </c>
     </row>
     <row r="40">
@@ -9583,58 +9583,58 @@
         </is>
       </c>
       <c r="B40">
-        <v>120443854.4497379</v>
+        <v>1553725722.401618</v>
       </c>
       <c r="C40">
-        <v>1750033.67193863</v>
+        <v>22575434.36800833</v>
       </c>
       <c r="D40">
-        <v>119960121.3112348</v>
+        <v>1547485564.914929</v>
       </c>
       <c r="E40">
-        <v>7451481.78790153</v>
+        <v>96124115.06392974</v>
       </c>
       <c r="F40">
-        <v>53892442.47944486</v>
+        <v>695212507.9848387</v>
       </c>
       <c r="G40">
-        <v>183054079.2505199</v>
+        <v>2361397622.331706</v>
       </c>
       <c r="H40">
-        <v>169856754.595071</v>
+        <v>2191152134.276417</v>
       </c>
       <c r="I40">
-        <v>44931067.21085633</v>
+        <v>579610767.0200467</v>
       </c>
       <c r="J40">
-        <v>16257420.94084346</v>
+        <v>209720730.1368806</v>
       </c>
       <c r="K40">
-        <v>16177690.84562421</v>
+        <v>208692211.9085523</v>
       </c>
       <c r="L40">
-        <v>4339438.37596388</v>
+        <v>55978755.04993406</v>
       </c>
       <c r="M40">
-        <v>225272279.3903839</v>
+        <v>2906012404.135952</v>
       </c>
       <c r="N40">
-        <v>88920555.50245614</v>
+        <v>1147075165.981684</v>
       </c>
       <c r="O40">
-        <v>565755206.8611989</v>
+        <v>7298242168.509466</v>
       </c>
       <c r="P40">
-        <v>869253140.5614567</v>
+        <v>11213365513.24279</v>
       </c>
       <c r="Q40">
-        <v>775993146.6830366</v>
+        <v>10010311592.21117</v>
       </c>
       <c r="R40">
-        <v>655549292.2332987</v>
+        <v>8456585869.809553</v>
       </c>
       <c r="S40">
-        <v>639371601.3876746</v>
+        <v>8247893657.901002</v>
       </c>
     </row>
     <row r="41">
@@ -9644,58 +9644,58 @@
         </is>
       </c>
       <c r="B41">
-        <v>120460390.4525282</v>
+        <v>1553939036.837614</v>
       </c>
       <c r="C41">
-        <v>2049525.75774476</v>
+        <v>26438882.27490741</v>
       </c>
       <c r="D41">
-        <v>123715087.8099643</v>
+        <v>1595924632.74854</v>
       </c>
       <c r="E41">
-        <v>7186464.54145368</v>
+        <v>92705392.58475247</v>
       </c>
       <c r="F41">
-        <v>55670688.41784033</v>
+        <v>718151880.5901403</v>
       </c>
       <c r="G41">
-        <v>188621766.5270031</v>
+        <v>2433220788.19834</v>
       </c>
       <c r="H41">
-        <v>171833383.3793209</v>
+        <v>2216650645.593239</v>
       </c>
       <c r="I41">
-        <v>44015577.86427899</v>
+        <v>567800954.449199</v>
       </c>
       <c r="J41">
-        <v>15983730.38325783</v>
+        <v>206190121.944026</v>
       </c>
       <c r="K41">
-        <v>15498091.17828617</v>
+        <v>199925376.1998916</v>
       </c>
       <c r="L41">
-        <v>4891479.55115176</v>
+        <v>63100086.20985771</v>
       </c>
       <c r="M41">
-        <v>230087929.1757031</v>
+        <v>2968134286.36657</v>
       </c>
       <c r="N41">
-        <v>89817353.85847184</v>
+        <v>1158643864.774287</v>
       </c>
       <c r="O41">
-        <v>572127545.3904705</v>
+        <v>7380445335.53707</v>
       </c>
       <c r="P41">
-        <v>881209702.3700018</v>
+        <v>11367605160.57302</v>
       </c>
       <c r="Q41">
-        <v>786500868.9603782</v>
+        <v>10145861209.58888</v>
       </c>
       <c r="R41">
-        <v>666040478.5078499</v>
+        <v>8591922172.751265</v>
       </c>
       <c r="S41">
-        <v>650542387.3295639</v>
+        <v>8391996796.551373</v>
       </c>
     </row>
     <row r="42">
@@ -9705,58 +9705,58 @@
         </is>
       </c>
       <c r="B42">
-        <v>121968333.7387799</v>
+        <v>1573391505.23026</v>
       </c>
       <c r="C42">
-        <v>2135013.47037004</v>
+        <v>27541673.76777352</v>
       </c>
       <c r="D42">
-        <v>127384133.1902674</v>
+        <v>1643255318.154449</v>
       </c>
       <c r="E42">
-        <v>7195853.4701865</v>
+        <v>92826509.76540586</v>
       </c>
       <c r="F42">
-        <v>58080466.83599789</v>
+        <v>749238022.1843728</v>
       </c>
       <c r="G42">
-        <v>194795466.9668218</v>
+        <v>2512861523.872002</v>
       </c>
       <c r="H42">
-        <v>174643465.1478199</v>
+        <v>2252900700.406877</v>
       </c>
       <c r="I42">
-        <v>45903912.63512942</v>
+        <v>592160472.9931695</v>
       </c>
       <c r="J42">
-        <v>15718606.43687868</v>
+        <v>202770023.035735</v>
       </c>
       <c r="K42">
-        <v>14340881.85256191</v>
+        <v>184997375.8980486</v>
       </c>
       <c r="L42">
-        <v>6024542.92220501</v>
+        <v>77716603.69644463</v>
       </c>
       <c r="M42">
-        <v>233264350.9643304</v>
+        <v>3009110127.439862</v>
       </c>
       <c r="N42">
-        <v>90171744.22133735</v>
+        <v>1163215500.455252</v>
       </c>
       <c r="O42">
-        <v>580067504.1802626</v>
+        <v>7482870803.925388</v>
       </c>
       <c r="P42">
-        <v>896831304.8858643</v>
+        <v>11569123833.02765</v>
       </c>
       <c r="Q42">
-        <v>800635017.742322</v>
+        <v>10328191728.87595</v>
       </c>
       <c r="R42">
-        <v>678666684.0035421</v>
+        <v>8754800223.645693</v>
       </c>
       <c r="S42">
-        <v>664325802.1509802</v>
+        <v>8569802847.747644</v>
       </c>
     </row>
     <row r="43">
@@ -9766,58 +9766,58 @@
         </is>
       </c>
       <c r="B43">
-        <v>119267877.1566773</v>
+        <v>1538555615.321137</v>
       </c>
       <c r="C43">
-        <v>2100963.51916995</v>
+        <v>27102429.39729236</v>
       </c>
       <c r="D43">
-        <v>131634204.6907254</v>
+        <v>1698081240.510358</v>
       </c>
       <c r="E43">
-        <v>6830686.57921023</v>
+        <v>88115856.87181197</v>
       </c>
       <c r="F43">
-        <v>58858611.04743545</v>
+        <v>759276082.5119174</v>
       </c>
       <c r="G43">
-        <v>199424465.8365411</v>
+        <v>2572575609.29138</v>
       </c>
       <c r="H43">
-        <v>175572055.3195821</v>
+        <v>2264879513.622609</v>
       </c>
       <c r="I43">
-        <v>48452503.94879802</v>
+        <v>625037300.9394945</v>
       </c>
       <c r="J43">
-        <v>15247285.36717452</v>
+        <v>196689981.2365513</v>
       </c>
       <c r="K43">
-        <v>13431636.59006361</v>
+        <v>173268112.0118206</v>
       </c>
       <c r="L43">
-        <v>7341412.32573851</v>
+        <v>94704219.00202678</v>
       </c>
       <c r="M43">
-        <v>240705007.9936121</v>
+        <v>3105094603.117596</v>
       </c>
       <c r="N43">
-        <v>90546746.36762187</v>
+        <v>1168053028.142322</v>
       </c>
       <c r="O43">
-        <v>591296647.9125907</v>
+        <v>7627726758.07242</v>
       </c>
       <c r="P43">
-        <v>909988990.9058092</v>
+        <v>11738857982.68494</v>
       </c>
       <c r="Q43">
-        <v>812100832.2124487</v>
+        <v>10476100735.54059</v>
       </c>
       <c r="R43">
-        <v>692832955.0557714</v>
+        <v>8937545120.219452</v>
       </c>
       <c r="S43">
-        <v>679401318.4657078</v>
+        <v>8764277008.20763</v>
       </c>
     </row>
     <row r="44">
@@ -9827,58 +9827,58 @@
         </is>
       </c>
       <c r="B44">
-        <v>117799684.6996458</v>
+        <v>1519615932.625431</v>
       </c>
       <c r="C44">
-        <v>1888947.79332693</v>
+        <v>24367426.5339174</v>
       </c>
       <c r="D44">
-        <v>138034072.4399759</v>
+        <v>1780639534.475689</v>
       </c>
       <c r="E44">
-        <v>6857541.45986292</v>
+        <v>88462284.83223167</v>
       </c>
       <c r="F44">
-        <v>60451718.68625509</v>
+        <v>779827171.0526907</v>
       </c>
       <c r="G44">
-        <v>207232280.3794208</v>
+        <v>2673296416.894528</v>
       </c>
       <c r="H44">
-        <v>176634237.4195427</v>
+        <v>2278581662.712101</v>
       </c>
       <c r="I44">
-        <v>48982586.40807701</v>
+        <v>631875364.6641934</v>
       </c>
       <c r="J44">
-        <v>14790431.79059562</v>
+        <v>190796570.0986835</v>
       </c>
       <c r="K44">
-        <v>13685925.58157512</v>
+        <v>176548440.002319</v>
       </c>
       <c r="L44">
-        <v>8370842.44123296</v>
+        <v>107983867.4919052</v>
       </c>
       <c r="M44">
-        <v>246791409.0565509</v>
+        <v>3183609176.829506</v>
       </c>
       <c r="N44">
-        <v>89955780.12353906</v>
+        <v>1160429563.593654</v>
       </c>
       <c r="O44">
-        <v>599211212.8211133</v>
+        <v>7729824645.392363</v>
       </c>
       <c r="P44">
-        <v>924243177.90018</v>
+        <v>11922736994.91232</v>
       </c>
       <c r="Q44">
-        <v>825916555.335408</v>
+        <v>10654323563.82676</v>
       </c>
       <c r="R44">
-        <v>708116870.6357622</v>
+        <v>9134707631.201332</v>
       </c>
       <c r="S44">
-        <v>694430945.0541871</v>
+        <v>8958159191.199013</v>
       </c>
     </row>
     <row r="45">
@@ -9888,58 +9888,58 @@
         </is>
       </c>
       <c r="B45">
-        <v>115850904.0435487</v>
+        <v>1494476662.161779</v>
       </c>
       <c r="C45">
-        <v>1604253.59730362</v>
+        <v>20694871.4052167</v>
       </c>
       <c r="D45">
-        <v>143114597.8556399</v>
+        <v>1846178312.337755</v>
       </c>
       <c r="E45">
-        <v>6664515.79931898</v>
+        <v>85972253.81121485</v>
       </c>
       <c r="F45">
-        <v>62055650.67817909</v>
+        <v>800517893.7485102</v>
       </c>
       <c r="G45">
-        <v>213439017.9304416</v>
+        <v>2753363331.302697</v>
       </c>
       <c r="H45">
-        <v>178333589.8392365</v>
+        <v>2300503308.926151</v>
       </c>
       <c r="I45">
-        <v>50613803.21558765</v>
+        <v>652918061.4810807</v>
       </c>
       <c r="J45">
-        <v>15656960.16249319</v>
+        <v>201974786.0961621</v>
       </c>
       <c r="K45">
-        <v>14083973.97200771</v>
+        <v>181683264.2388995</v>
       </c>
       <c r="L45">
-        <v>8902060.69408715</v>
+        <v>114836582.9537242</v>
       </c>
       <c r="M45">
-        <v>249617509.9936244</v>
+        <v>3220065878.917755</v>
       </c>
       <c r="N45">
-        <v>90539733.77476734</v>
+        <v>1167962565.694499</v>
       </c>
       <c r="O45">
-        <v>607747631.651804</v>
+        <v>7839944448.30827</v>
       </c>
       <c r="P45">
-        <v>937037553.6257943</v>
+        <v>12087784441.77275</v>
       </c>
       <c r="Q45">
-        <v>837595759.1569399</v>
+        <v>10804985293.12452</v>
       </c>
       <c r="R45">
-        <v>721744855.113391</v>
+        <v>9310508630.962746</v>
       </c>
       <c r="S45">
-        <v>707660881.1413834</v>
+        <v>9128825366.723846</v>
       </c>
     </row>
     <row r="46">
@@ -9949,58 +9949,58 @@
         </is>
       </c>
       <c r="B46">
-        <v>113682736.9613001</v>
+        <v>1466507306.800771</v>
       </c>
       <c r="C46">
-        <v>1605036.88124514</v>
+        <v>20704975.76806231</v>
       </c>
       <c r="D46">
-        <v>147657732.9826351</v>
+        <v>1904784755.475992</v>
       </c>
       <c r="E46">
-        <v>6301804.58269222</v>
+        <v>81293279.11672965</v>
       </c>
       <c r="F46">
-        <v>63660256.80346587</v>
+        <v>821217312.7647097</v>
       </c>
       <c r="G46">
-        <v>219224831.2500383</v>
+        <v>2828000323.125494</v>
       </c>
       <c r="H46">
-        <v>177387867.16748</v>
+        <v>2288303486.460492</v>
       </c>
       <c r="I46">
-        <v>51064829.1724401</v>
+        <v>658736296.3244773</v>
       </c>
       <c r="J46">
-        <v>15965270.00837463</v>
+        <v>205951983.1080327</v>
       </c>
       <c r="K46">
-        <v>14675726.8795845</v>
+        <v>189316876.7466401</v>
       </c>
       <c r="L46">
-        <v>8397765.007897511</v>
+        <v>108331168.6018779</v>
       </c>
       <c r="M46">
-        <v>252903516.4707131</v>
+        <v>3262455362.472199</v>
       </c>
       <c r="N46">
-        <v>90112532.07030746</v>
+        <v>1162451663.706966</v>
       </c>
       <c r="O46">
-        <v>610507506.7767973</v>
+        <v>7875546837.420686</v>
       </c>
       <c r="P46">
-        <v>943415074.9881357</v>
+        <v>12170054467.34695</v>
       </c>
       <c r="Q46">
-        <v>844904777.9099308</v>
+        <v>10899271635.03811</v>
       </c>
       <c r="R46">
-        <v>731222040.9486306</v>
+        <v>9432764328.237335</v>
       </c>
       <c r="S46">
-        <v>716546314.0690463</v>
+        <v>9243447451.490696</v>
       </c>
     </row>
     <row r="47">
@@ -10010,58 +10010,58 @@
         </is>
       </c>
       <c r="B47">
-        <v>112617302.677504</v>
+        <v>1452763204.539802</v>
       </c>
       <c r="C47">
-        <v>1511869.99889355</v>
+        <v>19503122.9857268</v>
       </c>
       <c r="D47">
-        <v>149743169.8925543</v>
+        <v>1931686891.61395</v>
       </c>
       <c r="E47">
-        <v>6080572.7959284</v>
+        <v>78439389.06747636</v>
       </c>
       <c r="F47">
-        <v>66323260.45234922</v>
+        <v>855570059.835305</v>
       </c>
       <c r="G47">
-        <v>223658873.1397254</v>
+        <v>2885199463.502459</v>
       </c>
       <c r="H47">
-        <v>176844761.4012975</v>
+        <v>2281297422.076737</v>
       </c>
       <c r="I47">
-        <v>49650510.61765517</v>
+        <v>640491586.9677517</v>
       </c>
       <c r="J47">
-        <v>16805527.32385777</v>
+        <v>216791302.4777652</v>
       </c>
       <c r="K47">
-        <v>15382545.02799236</v>
+        <v>198434830.8611014</v>
       </c>
       <c r="L47">
-        <v>7963862.60182195</v>
+        <v>102733827.5635032</v>
       </c>
       <c r="M47">
-        <v>255107937.5930636</v>
+        <v>3290892394.950521</v>
       </c>
       <c r="N47">
-        <v>89131497.92277481</v>
+        <v>1149796323.203795</v>
       </c>
       <c r="O47">
-        <v>610886642.4884632</v>
+        <v>7880437688.101174</v>
       </c>
       <c r="P47">
-        <v>947162818.3056927</v>
+        <v>12218400356.14344</v>
       </c>
       <c r="Q47">
-        <v>850067457.781096</v>
+        <v>10965870205.37614</v>
       </c>
       <c r="R47">
-        <v>737450155.1035918</v>
+        <v>9513107000.836334</v>
       </c>
       <c r="S47">
-        <v>722067610.0755996</v>
+        <v>9314672169.975235</v>
       </c>
     </row>
     <row r="48">
@@ -10071,58 +10071,58 @@
         </is>
       </c>
       <c r="B48">
-        <v>109510674.4859377</v>
+        <v>1412687700.868596</v>
       </c>
       <c r="C48">
-        <v>1699532.43124115</v>
+        <v>21923968.36301084</v>
       </c>
       <c r="D48">
-        <v>148087452.5589838</v>
+        <v>1910328138.010891</v>
       </c>
       <c r="E48">
-        <v>6269648.260560339</v>
+        <v>80878462.56122839</v>
       </c>
       <c r="F48">
-        <v>66185800.0387266</v>
+        <v>853796820.4995732</v>
       </c>
       <c r="G48">
-        <v>222242433.2895119</v>
+        <v>2866927389.434704</v>
       </c>
       <c r="H48">
-        <v>174488017.1568014</v>
+        <v>2250895421.322738</v>
       </c>
       <c r="I48">
-        <v>48752234.87839459</v>
+        <v>628903829.9312903</v>
       </c>
       <c r="J48">
-        <v>17267311.92930195</v>
+        <v>222748323.8879952</v>
       </c>
       <c r="K48">
-        <v>15703377.3941196</v>
+        <v>202573568.3841428</v>
       </c>
       <c r="L48">
-        <v>7734834.15864661</v>
+        <v>99779360.64654127</v>
       </c>
       <c r="M48">
-        <v>258170082.8666706</v>
+        <v>3330394068.980051</v>
       </c>
       <c r="N48">
-        <v>88325946.18725909</v>
+        <v>1139404705.815642</v>
       </c>
       <c r="O48">
-        <v>610441804.5711938</v>
+        <v>7874699278.968401</v>
       </c>
       <c r="P48">
-        <v>942194912.3466434</v>
+        <v>12154314369.2717</v>
       </c>
       <c r="Q48">
-        <v>846134132.0007378</v>
+        <v>10915130302.80952</v>
       </c>
       <c r="R48">
-        <v>736623457.5148001</v>
+        <v>9502442601.940922</v>
       </c>
       <c r="S48">
-        <v>720920080.1206805</v>
+        <v>9299869033.556778</v>
       </c>
     </row>
     <row r="49">
@@ -10132,58 +10132,58 @@
         </is>
       </c>
       <c r="B49">
-        <v>106347309.2702644</v>
+        <v>1371880289.586411</v>
       </c>
       <c r="C49">
-        <v>1839764.98149414</v>
+        <v>23732968.26127441</v>
       </c>
       <c r="D49">
-        <v>146577838.1311935</v>
+        <v>1890854111.892395</v>
       </c>
       <c r="E49">
-        <v>6366897.21113095</v>
+        <v>82132974.02358925</v>
       </c>
       <c r="F49">
-        <v>66585847.84051295</v>
+        <v>858957437.142617</v>
       </c>
       <c r="G49">
-        <v>221370348.1643315</v>
+        <v>2855677491.319876</v>
       </c>
       <c r="H49">
-        <v>173142359.3369261</v>
+        <v>2233536435.446346</v>
       </c>
       <c r="I49">
-        <v>48963570.87133363</v>
+        <v>631630064.2402039</v>
       </c>
       <c r="J49">
-        <v>17038652.88101723</v>
+        <v>219798622.1651223</v>
       </c>
       <c r="K49">
-        <v>16464147.18444061</v>
+        <v>212387498.6792839</v>
       </c>
       <c r="L49">
-        <v>7737078.731912971</v>
+        <v>99808315.64167732</v>
       </c>
       <c r="M49">
-        <v>261330172.6182146</v>
+        <v>3371159226.774969</v>
       </c>
       <c r="N49">
-        <v>87884655.77141634</v>
+        <v>1133712059.451271</v>
       </c>
       <c r="O49">
-        <v>612560637.3952615</v>
+        <v>7902032222.398873</v>
       </c>
       <c r="P49">
-        <v>940278294.8298573</v>
+        <v>12129590003.30516</v>
       </c>
       <c r="Q49">
-        <v>844656560.3265281</v>
+        <v>10896069628.21221</v>
       </c>
       <c r="R49">
-        <v>738309251.0562637</v>
+        <v>9524189338.625801</v>
       </c>
       <c r="S49">
-        <v>721845103.871823</v>
+        <v>9311801839.946516</v>
       </c>
     </row>
     <row r="50">
@@ -10193,58 +10193,58 @@
         </is>
       </c>
       <c r="B50">
-        <v>102197046.8474496</v>
+        <v>1318341904.3321</v>
       </c>
       <c r="C50">
-        <v>1806674.63666498</v>
+        <v>23306102.81297824</v>
       </c>
       <c r="D50">
-        <v>145108316.747228</v>
+        <v>1871897286.039241</v>
       </c>
       <c r="E50">
-        <v>6294748.654971329</v>
+        <v>81202257.64913017</v>
       </c>
       <c r="F50">
-        <v>66839747.53912728</v>
+        <v>862232743.2547418</v>
       </c>
       <c r="G50">
-        <v>220049487.5779916</v>
+        <v>2838638389.756092</v>
       </c>
       <c r="H50">
-        <v>175690920.9617805</v>
+        <v>2266412880.406969</v>
       </c>
       <c r="I50">
-        <v>48575040.39809107</v>
+        <v>626618021.1353748</v>
       </c>
       <c r="J50">
-        <v>17711468.88890891</v>
+        <v>228477948.666925</v>
       </c>
       <c r="K50">
-        <v>15934941.9737899</v>
+        <v>205560751.4618897</v>
       </c>
       <c r="L50">
-        <v>8208445.15312647</v>
+        <v>105888942.4753315</v>
       </c>
       <c r="M50">
-        <v>263745588.2730121</v>
+        <v>3402318088.721856</v>
       </c>
       <c r="N50">
-        <v>88069200.32121944</v>
+        <v>1136092684.143731</v>
       </c>
       <c r="O50">
-        <v>617935605.9699285</v>
+        <v>7971369317.012078</v>
       </c>
       <c r="P50">
-        <v>940182140.3953696</v>
+        <v>12128349611.10027</v>
       </c>
       <c r="Q50">
-        <v>843904494.9210237</v>
+        <v>10886367984.48121</v>
       </c>
       <c r="R50">
-        <v>741707448.0735741</v>
+        <v>9568026080.149107</v>
       </c>
       <c r="S50">
-        <v>725772506.0997841</v>
+        <v>9362465328.687216</v>
       </c>
     </row>
     <row r="51">
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="B51">
-        <v>98180546.52761659</v>
+        <v>1266529050.206254</v>
       </c>
       <c r="C51">
-        <v>1719558.0505405</v>
+        <v>22182298.85197245</v>
       </c>
       <c r="D51">
-        <v>145235751.6182343</v>
+        <v>1873541195.875222</v>
       </c>
       <c r="E51">
-        <v>6258001.596026611</v>
+        <v>80728220.58874327</v>
       </c>
       <c r="F51">
-        <v>65683845.38688876</v>
+        <v>847321605.490865</v>
       </c>
       <c r="G51">
-        <v>218897156.6516902</v>
+        <v>2823773320.806803</v>
       </c>
       <c r="H51">
-        <v>177357021.2451864</v>
+        <v>2287905574.062905</v>
       </c>
       <c r="I51">
-        <v>50150599.45189427</v>
+        <v>646942732.9294361</v>
       </c>
       <c r="J51">
-        <v>17226114.6284619</v>
+        <v>222216878.7071585</v>
       </c>
       <c r="K51">
-        <v>14963413.46430151</v>
+        <v>193028033.6894895</v>
       </c>
       <c r="L51">
-        <v>8569077.43540192</v>
+        <v>110541098.9166848</v>
       </c>
       <c r="M51">
-        <v>264640287.9514348</v>
+        <v>3413859714.573509</v>
       </c>
       <c r="N51">
-        <v>88888606.90382937</v>
+        <v>1146663029.059399</v>
       </c>
       <c r="O51">
-        <v>621795121.0805104</v>
+        <v>8021157061.938585</v>
       </c>
       <c r="P51">
-        <v>938872824.2598169</v>
+        <v>12111459432.95164</v>
       </c>
       <c r="Q51">
-        <v>841415139.9205858</v>
+        <v>10854255304.97556</v>
       </c>
       <c r="R51">
-        <v>743234593.3929691</v>
+        <v>9587726254.769302</v>
       </c>
       <c r="S51">
-        <v>728271179.9286677</v>
+        <v>9394698221.079813</v>
       </c>
     </row>
     <row r="52">
@@ -10315,58 +10315,58 @@
         </is>
       </c>
       <c r="B52">
-        <v>96457448.94747166</v>
+        <v>1244301091.422385</v>
       </c>
       <c r="C52">
-        <v>1517548.89660274</v>
+        <v>19576380.76617535</v>
       </c>
       <c r="D52">
-        <v>146236568.785339</v>
+        <v>1886451737.330873</v>
       </c>
       <c r="E52">
-        <v>6056579.54508561</v>
+        <v>78129876.13160437</v>
       </c>
       <c r="F52">
-        <v>66301387.93513554</v>
+        <v>855287904.3632485</v>
       </c>
       <c r="G52">
-        <v>220112085.1621629</v>
+        <v>2839445898.591902</v>
       </c>
       <c r="H52">
-        <v>182297603.796678</v>
+        <v>2351639088.977147</v>
       </c>
       <c r="I52">
-        <v>52258149.44417402</v>
+        <v>674130127.8298448</v>
       </c>
       <c r="J52">
-        <v>16884598.60364906</v>
+        <v>217811321.9870729</v>
       </c>
       <c r="K52">
-        <v>14447011.33631765</v>
+        <v>186366446.2384977</v>
       </c>
       <c r="L52">
-        <v>8673507.70892</v>
+        <v>111888249.445068</v>
       </c>
       <c r="M52">
-        <v>263492832.7121965</v>
+        <v>3399057541.987334</v>
       </c>
       <c r="N52">
-        <v>90702960.9300601</v>
+        <v>1170068195.997775</v>
       </c>
       <c r="O52">
-        <v>628756664.5319954</v>
+        <v>8110960972.462742</v>
       </c>
       <c r="P52">
-        <v>945326198.6416298</v>
+        <v>12194707962.47702</v>
       </c>
       <c r="Q52">
-        <v>845949730.0026498</v>
+        <v>10912751517.03418</v>
       </c>
       <c r="R52">
-        <v>749492281.0551782</v>
+        <v>9668450425.611797</v>
       </c>
       <c r="S52">
-        <v>735045269.7188605</v>
+        <v>9482083979.373302</v>
       </c>
     </row>
     <row r="53">
@@ -10376,58 +10376,58 @@
         </is>
       </c>
       <c r="B53">
-        <v>95206699.03176701</v>
+        <v>1228166417.509795</v>
       </c>
       <c r="C53">
-        <v>1502631.0745112</v>
+        <v>19383940.86119448</v>
       </c>
       <c r="D53">
-        <v>148353251.509463</v>
+        <v>1913756944.472072</v>
       </c>
       <c r="E53">
-        <v>6019253.04351005</v>
+        <v>77648364.26127964</v>
       </c>
       <c r="F53">
-        <v>66412356.91279308</v>
+        <v>856719404.1750307</v>
       </c>
       <c r="G53">
-        <v>222287492.5402773</v>
+        <v>2867508653.769577</v>
       </c>
       <c r="H53">
-        <v>185018206.5391024</v>
+        <v>2386734864.354422</v>
       </c>
       <c r="I53">
-        <v>55100883.50121056</v>
+        <v>710801397.1656163</v>
       </c>
       <c r="J53">
-        <v>17001732.17050011</v>
+        <v>219322344.9994514</v>
       </c>
       <c r="K53">
-        <v>13648884.38774459</v>
+        <v>176070608.6019052</v>
       </c>
       <c r="L53">
-        <v>8993949.030413799</v>
+        <v>116021942.492338</v>
       </c>
       <c r="M53">
-        <v>264019462.6182593</v>
+        <v>3405851067.775545</v>
       </c>
       <c r="N53">
-        <v>90987815.89193994</v>
+        <v>1173742825.006025</v>
       </c>
       <c r="O53">
-        <v>634770934.1391709</v>
+        <v>8188545050.395304</v>
       </c>
       <c r="P53">
-        <v>952265125.711215</v>
+        <v>12284220121.67467</v>
       </c>
       <c r="Q53">
-        <v>852283360.7888613</v>
+        <v>10994455354.17631</v>
       </c>
       <c r="R53">
-        <v>757076661.7570943</v>
+        <v>9766288936.666515</v>
       </c>
       <c r="S53">
-        <v>743427777.3693498</v>
+        <v>9590218328.064613</v>
       </c>
     </row>
     <row r="54">
@@ -10437,58 +10437,58 @@
         </is>
       </c>
       <c r="B54">
-        <v>94144984.68467438</v>
+        <v>1214470302.4323</v>
       </c>
       <c r="C54">
-        <v>1272808.21221124</v>
+        <v>16419225.937525</v>
       </c>
       <c r="D54">
-        <v>149455322.3232227</v>
+        <v>1927973657.969573</v>
       </c>
       <c r="E54">
-        <v>5997440.378719</v>
+        <v>77366980.8854751</v>
       </c>
       <c r="F54">
-        <v>64898821.13590002</v>
+        <v>837194792.6531103</v>
       </c>
       <c r="G54">
-        <v>221624392.0500529</v>
+        <v>2858954657.445683</v>
       </c>
       <c r="H54">
-        <v>186298819.0890058</v>
+        <v>2403254766.248176</v>
       </c>
       <c r="I54">
-        <v>57428652.01543505</v>
+        <v>740829610.9991121</v>
       </c>
       <c r="J54">
-        <v>16700790.3558228</v>
+        <v>215440195.5901141</v>
       </c>
       <c r="K54">
-        <v>14219538.18495002</v>
+        <v>183432042.5858552</v>
       </c>
       <c r="L54">
-        <v>8672574.9968</v>
+        <v>111876217.45872</v>
       </c>
       <c r="M54">
-        <v>264761226.8681252</v>
+        <v>3415419826.598815</v>
       </c>
       <c r="N54">
-        <v>92651741.36788499</v>
+        <v>1195207463.645716</v>
       </c>
       <c r="O54">
-        <v>640733342.8780239</v>
+        <v>8265460123.126509</v>
       </c>
       <c r="P54">
-        <v>956502719.6127512</v>
+        <v>12338885083.00449</v>
       </c>
       <c r="Q54">
-        <v>855178403.2480662</v>
+        <v>11031801401.90005</v>
       </c>
       <c r="R54">
-        <v>761033418.5633918</v>
+        <v>9817331099.467754</v>
       </c>
       <c r="S54">
-        <v>746813880.3784419</v>
+        <v>9633899056.881901</v>
       </c>
     </row>
     <row r="55">
@@ -10498,58 +10498,58 @@
         </is>
       </c>
       <c r="B55">
-        <v>93420783.47558089</v>
+        <v>1205128106.834993</v>
       </c>
       <c r="C55">
-        <v>1110909.081836</v>
+        <v>14330727.1556844</v>
       </c>
       <c r="D55">
-        <v>149540360.5469504</v>
+        <v>1929070651.05566</v>
       </c>
       <c r="E55">
-        <v>5619396.1359349</v>
+        <v>72490210.15356021</v>
       </c>
       <c r="F55">
-        <v>63672209.89199374</v>
+        <v>821371507.6067193</v>
       </c>
       <c r="G55">
-        <v>219942875.656715</v>
+        <v>2837263095.971624</v>
       </c>
       <c r="H55">
-        <v>186951411.3979237</v>
+        <v>2411673207.033216</v>
       </c>
       <c r="I55">
-        <v>58030729.20786856</v>
+        <v>748596406.7815044</v>
       </c>
       <c r="J55">
-        <v>16528994.29107987</v>
+        <v>213224026.3549303</v>
       </c>
       <c r="K55">
-        <v>15366021.93335562</v>
+        <v>198221682.9402875</v>
       </c>
       <c r="L55">
-        <v>8243230.6136598</v>
+        <v>106337674.9162114</v>
       </c>
       <c r="M55">
-        <v>267574315.8542635</v>
+        <v>3451708674.519999</v>
       </c>
       <c r="N55">
-        <v>94393112.3777741</v>
+        <v>1217671149.673286</v>
       </c>
       <c r="O55">
-        <v>647087815.6759251</v>
+        <v>8347432822.219434</v>
       </c>
       <c r="P55">
-        <v>960451474.8082211</v>
+        <v>12389824025.02605</v>
       </c>
       <c r="Q55">
-        <v>857815131.8167871</v>
+        <v>11065815200.43655</v>
       </c>
       <c r="R55">
-        <v>764394348.3412063</v>
+        <v>9860687093.601563</v>
       </c>
       <c r="S55">
-        <v>749028326.4078507</v>
+        <v>9662465410.661274</v>
       </c>
     </row>
     <row r="56">
@@ -10559,58 +10559,58 @@
         </is>
       </c>
       <c r="B56">
-        <v>92993065.31167209</v>
+        <v>1199610542.52057</v>
       </c>
       <c r="C56">
-        <v>1051511.79002769</v>
+        <v>13564502.0913572</v>
       </c>
       <c r="D56">
-        <v>150426022.6775321</v>
+        <v>1940495692.540164</v>
       </c>
       <c r="E56">
-        <v>5381427.18135571</v>
+        <v>69420410.63948867</v>
       </c>
       <c r="F56">
-        <v>63431734.96233409</v>
+        <v>818269381.0141097</v>
       </c>
       <c r="G56">
-        <v>220290696.6112496</v>
+        <v>2841749986.28512</v>
       </c>
       <c r="H56">
-        <v>185417471.2646337</v>
+        <v>2391885379.313775</v>
       </c>
       <c r="I56">
-        <v>60066835.45716632</v>
+        <v>774862177.3974456</v>
       </c>
       <c r="J56">
-        <v>16325226.44197568</v>
+        <v>210595421.1014863</v>
       </c>
       <c r="K56">
-        <v>16677347.55189956</v>
+        <v>215137783.4195043</v>
       </c>
       <c r="L56">
-        <v>7824421.79354928</v>
+        <v>100935041.1367857</v>
       </c>
       <c r="M56">
-        <v>267290643.8043881</v>
+        <v>3448049305.076606</v>
       </c>
       <c r="N56">
-        <v>94447063.28747584</v>
+        <v>1218367116.408438</v>
       </c>
       <c r="O56">
-        <v>648049009.6010885</v>
+        <v>8359832223.854042</v>
       </c>
       <c r="P56">
-        <v>961332771.5240103</v>
+        <v>12401192752.65973</v>
       </c>
       <c r="Q56">
-        <v>859061286.4429851</v>
+        <v>11081890595.11451</v>
       </c>
       <c r="R56">
-        <v>766068221.1313131</v>
+        <v>9882280052.593941</v>
       </c>
       <c r="S56">
-        <v>749390873.5794135</v>
+        <v>9667142269.174435</v>
       </c>
     </row>
     <row r="57">
@@ -10620,58 +10620,58 @@
         </is>
       </c>
       <c r="B57">
-        <v>92635838.83552209</v>
+        <v>1195002320.978235</v>
       </c>
       <c r="C57">
-        <v>868669.32343797</v>
+        <v>11205834.27234981</v>
       </c>
       <c r="D57">
-        <v>149514329.6110119</v>
+        <v>1928734851.982053</v>
       </c>
       <c r="E57">
-        <v>5659803.19137749</v>
+        <v>73011461.16876963</v>
       </c>
       <c r="F57">
-        <v>62231652.98486844</v>
+        <v>802788323.5048029</v>
       </c>
       <c r="G57">
-        <v>218274455.1106957</v>
+        <v>2815740470.927975</v>
       </c>
       <c r="H57">
-        <v>185618212.5704331</v>
+        <v>2394474942.158587</v>
       </c>
       <c r="I57">
-        <v>59439791.89898286</v>
+        <v>766773315.4968789</v>
       </c>
       <c r="J57">
-        <v>16183195.12978009</v>
+        <v>208763217.1741632</v>
       </c>
       <c r="K57">
-        <v>17305103.67609622</v>
+        <v>223235837.4216412</v>
       </c>
       <c r="L57">
-        <v>7467073.4200087</v>
+        <v>96325247.11811224</v>
       </c>
       <c r="M57">
-        <v>267966937.9381151</v>
+        <v>3456773499.401685</v>
       </c>
       <c r="N57">
-        <v>95241290.59750664</v>
+        <v>1228612648.707836</v>
       </c>
       <c r="O57">
-        <v>649221605.2309227</v>
+        <v>8374958707.478903</v>
       </c>
       <c r="P57">
-        <v>960131899.1771406</v>
+        <v>12385701499.38511</v>
       </c>
       <c r="Q57">
-        <v>857423535.1596251</v>
+        <v>11060763603.55916</v>
       </c>
       <c r="R57">
-        <v>764787696.3241032</v>
+        <v>9865761282.580933</v>
       </c>
       <c r="S57">
-        <v>747482592.6480069</v>
+        <v>9642525445.159288</v>
       </c>
     </row>
     <row r="58">
@@ -10681,58 +10681,58 @@
         </is>
       </c>
       <c r="B58">
-        <v>93951120.40169868</v>
+        <v>1211969453.181913</v>
       </c>
       <c r="C58">
-        <v>935333.21171165</v>
+        <v>12065798.43108029</v>
       </c>
       <c r="D58">
-        <v>150058889.1609412</v>
+        <v>1935759670.176142</v>
       </c>
       <c r="E58">
-        <v>5983693.88200506</v>
+        <v>77189651.07786527</v>
       </c>
       <c r="F58">
-        <v>62623036.79017853</v>
+        <v>807837174.5933031</v>
       </c>
       <c r="G58">
-        <v>219600953.0448365</v>
+        <v>2832852294.27839</v>
       </c>
       <c r="H58">
-        <v>184089606.4119237</v>
+        <v>2374755922.713816</v>
       </c>
       <c r="I58">
-        <v>59765733.89858306</v>
+        <v>770977967.2917215</v>
       </c>
       <c r="J58">
-        <v>16194373.28206081</v>
+        <v>208907415.3385844</v>
       </c>
       <c r="K58">
-        <v>17669149.05568959</v>
+        <v>227932022.8183957</v>
       </c>
       <c r="L58">
-        <v>7705635.12526048</v>
+        <v>99402693.11586019</v>
       </c>
       <c r="M58">
-        <v>266532731.57647</v>
+        <v>3438272237.336463</v>
       </c>
       <c r="N58">
-        <v>95786776.16979736</v>
+        <v>1235649412.590386</v>
       </c>
       <c r="O58">
-        <v>647744005.519785</v>
+        <v>8355897671.205227</v>
       </c>
       <c r="P58">
-        <v>961296078.9663203</v>
+        <v>12400719418.66553</v>
       </c>
       <c r="Q58">
-        <v>857803667.6712623</v>
+        <v>11065667312.95928</v>
       </c>
       <c r="R58">
-        <v>763852547.2695637</v>
+        <v>9853697859.777372</v>
       </c>
       <c r="S58">
-        <v>746183398.2138741</v>
+        <v>9625765836.958975</v>
       </c>
     </row>
   </sheetData>
@@ -10870,58 +10870,58 @@
         </is>
       </c>
       <c r="B5">
-        <v>123955983.5851155</v>
+        <v>1599032188.247989</v>
       </c>
       <c r="C5">
-        <v>2536859.70965648</v>
+        <v>32725490.2545686</v>
       </c>
       <c r="D5">
-        <v>150166591.4156167</v>
+        <v>1937149029.261456</v>
       </c>
       <c r="E5">
-        <v>7357288.421755889</v>
+        <v>94909020.64065099</v>
       </c>
       <c r="F5">
-        <v>61164375.22664642</v>
+        <v>789020440.4237388</v>
       </c>
       <c r="G5">
-        <v>221225114.7736755</v>
+        <v>2853803980.580414</v>
       </c>
       <c r="H5">
-        <v>165401309.9180031</v>
+        <v>2133676897.94224</v>
       </c>
       <c r="I5">
-        <v>49690467.19902172</v>
+        <v>641007026.8673801</v>
       </c>
       <c r="J5">
-        <v>9910570.64738421</v>
+        <v>127846361.3512563</v>
       </c>
       <c r="K5">
-        <v>11888117.72196227</v>
+        <v>153356718.6133133</v>
       </c>
       <c r="L5">
-        <v>5608377.15193392</v>
+        <v>72348065.25994757</v>
       </c>
       <c r="M5">
-        <v>204888776.4655287</v>
+        <v>2643065216.405321</v>
       </c>
       <c r="N5">
-        <v>74624567.7718925</v>
+        <v>962656924.2574133</v>
       </c>
       <c r="O5">
-        <v>522012186.8757265</v>
+        <v>6733957210.696872</v>
       </c>
       <c r="P5">
-        <v>867193285.2345173</v>
+        <v>11186793379.52527</v>
       </c>
       <c r="Q5">
-        <v>786960340.3106911</v>
+        <v>10151788390.00792</v>
       </c>
       <c r="R5">
-        <v>663004356.7255754</v>
+        <v>8552756201.759924</v>
       </c>
       <c r="S5">
-        <v>651116239.0036132</v>
+        <v>8399399483.14661</v>
       </c>
     </row>
     <row r="6">
@@ -10931,58 +10931,58 @@
         </is>
       </c>
       <c r="B6">
-        <v>122783613.6225989</v>
+        <v>1583908615.731525</v>
       </c>
       <c r="C6">
-        <v>2579509.34408559</v>
+        <v>33275670.53870411</v>
       </c>
       <c r="D6">
-        <v>149523076.6437398</v>
+        <v>1928847688.704243</v>
       </c>
       <c r="E6">
-        <v>7218447.48516063</v>
+        <v>93117972.55857213</v>
       </c>
       <c r="F6">
-        <v>62517922.84020076</v>
+        <v>806481204.6385899</v>
       </c>
       <c r="G6">
-        <v>221838956.3131867</v>
+        <v>2861722536.440109</v>
       </c>
       <c r="H6">
-        <v>166153930.2075276</v>
+        <v>2143385699.677106</v>
       </c>
       <c r="I6">
-        <v>50008991.42100993</v>
+        <v>645115989.3310281</v>
       </c>
       <c r="J6">
-        <v>9966049.6960066</v>
+        <v>128562041.0784851</v>
       </c>
       <c r="K6">
-        <v>12117361.88675038</v>
+        <v>156313968.3390799</v>
       </c>
       <c r="L6">
-        <v>6322588.16595438</v>
+        <v>81561387.34081151</v>
       </c>
       <c r="M6">
-        <v>200694556.7824337</v>
+        <v>2588959782.493395</v>
       </c>
       <c r="N6">
-        <v>76477218.93961263</v>
+        <v>986556124.321003</v>
       </c>
       <c r="O6">
-        <v>521740697.0992953</v>
+        <v>6730454992.58091</v>
       </c>
       <c r="P6">
-        <v>866363267.0350808</v>
+        <v>11176086144.75254</v>
       </c>
       <c r="Q6">
-        <v>783563459.9295139</v>
+        <v>10107968633.09073</v>
       </c>
       <c r="R6">
-        <v>660779846.306915</v>
+        <v>8524060017.359203</v>
       </c>
       <c r="S6">
-        <v>648662484.4201646</v>
+        <v>8367746049.020124</v>
       </c>
     </row>
     <row r="7">
@@ -10992,58 +10992,58 @@
         </is>
       </c>
       <c r="B7">
-        <v>121121809.4356565</v>
+        <v>1562471341.719969</v>
       </c>
       <c r="C7">
-        <v>2723779.02405763</v>
+        <v>35136749.41034342</v>
       </c>
       <c r="D7">
-        <v>150193001.7590104</v>
+        <v>1937489722.691234</v>
       </c>
       <c r="E7">
-        <v>7558361.45797218</v>
+        <v>97502862.80784112</v>
       </c>
       <c r="F7">
-        <v>61882295.98916577</v>
+        <v>798281618.2602384</v>
       </c>
       <c r="G7">
-        <v>222357438.230206</v>
+        <v>2868410953.169657</v>
       </c>
       <c r="H7">
-        <v>168762988.8848205</v>
+        <v>2177042556.614184</v>
       </c>
       <c r="I7">
-        <v>50623341.48044666</v>
+        <v>653041105.0977619</v>
       </c>
       <c r="J7">
-        <v>9949014.098254601</v>
+        <v>128342281.8674843</v>
       </c>
       <c r="K7">
-        <v>12266563.1075802</v>
+        <v>158238664.0877846</v>
       </c>
       <c r="L7">
-        <v>6992496.90412288</v>
+        <v>90203210.06318516</v>
       </c>
       <c r="M7">
-        <v>199439190.9117477</v>
+        <v>2572765562.761546</v>
       </c>
       <c r="N7">
-        <v>79413055.33863507</v>
+        <v>1024428413.868392</v>
       </c>
       <c r="O7">
-        <v>527446650.7256077</v>
+        <v>6804061794.360339</v>
       </c>
       <c r="P7">
-        <v>870925898.3914701</v>
+        <v>11234944089.24997</v>
       </c>
       <c r="Q7">
-        <v>784520346.1487122</v>
+        <v>10120312465.31839</v>
       </c>
       <c r="R7">
-        <v>663398536.7130557</v>
+        <v>8557841123.598419</v>
       </c>
       <c r="S7">
-        <v>651131973.6054754</v>
+        <v>8399602459.510633</v>
       </c>
     </row>
     <row r="8">
@@ -11053,58 +11053,58 @@
         </is>
       </c>
       <c r="B8">
-        <v>119539560.7614953</v>
+        <v>1542060333.82329</v>
       </c>
       <c r="C8">
-        <v>2626412.15638554</v>
+        <v>33880716.81737346</v>
       </c>
       <c r="D8">
-        <v>150095956.3236329</v>
+        <v>1936237836.574864</v>
       </c>
       <c r="E8">
-        <v>7819738.77672943</v>
+        <v>100874630.2198097</v>
       </c>
       <c r="F8">
-        <v>63309982.81640461</v>
+        <v>816698778.3316195</v>
       </c>
       <c r="G8">
-        <v>223852090.0731525</v>
+        <v>2887691961.943667</v>
       </c>
       <c r="H8">
-        <v>171784651.5957881</v>
+        <v>2216022005.585666</v>
       </c>
       <c r="I8">
-        <v>51298350.40380611</v>
+        <v>661748720.2090987</v>
       </c>
       <c r="J8">
-        <v>9626240.197214879</v>
+        <v>124178498.544072</v>
       </c>
       <c r="K8">
-        <v>12469108.93642603</v>
+        <v>160851505.2798958</v>
       </c>
       <c r="L8">
-        <v>7523111.92468651</v>
+        <v>97048143.82845598</v>
       </c>
       <c r="M8">
-        <v>201082298.7017878</v>
+        <v>2593961653.253062</v>
       </c>
       <c r="N8">
-        <v>80956396.73000933</v>
+        <v>1044337517.81712</v>
       </c>
       <c r="O8">
-        <v>534740158.4897188</v>
+        <v>6898148044.517372</v>
       </c>
       <c r="P8">
-        <v>878131809.3243666</v>
+        <v>11327900340.28433</v>
       </c>
       <c r="Q8">
-        <v>789652300.6696707</v>
+        <v>10186514678.63875</v>
       </c>
       <c r="R8">
-        <v>670112739.9081753</v>
+        <v>8644454344.815462</v>
       </c>
       <c r="S8">
-        <v>657643630.9717493</v>
+        <v>8483602839.535566</v>
       </c>
     </row>
     <row r="9">
@@ -11114,58 +11114,58 @@
         </is>
       </c>
       <c r="B9">
-        <v>119307968.7389078</v>
+        <v>1539072796.73191</v>
       </c>
       <c r="C9">
-        <v>2654235.10799254</v>
+        <v>34239632.89310376</v>
       </c>
       <c r="D9">
-        <v>150118470.1996418</v>
+        <v>1936528265.575379</v>
       </c>
       <c r="E9">
-        <v>7644232.120207271</v>
+        <v>98610594.35067379</v>
       </c>
       <c r="F9">
-        <v>64234622.87065266</v>
+        <v>828626635.0314193</v>
       </c>
       <c r="G9">
-        <v>224651560.2984943</v>
+        <v>2898005127.850576</v>
       </c>
       <c r="H9">
-        <v>176275405.4072924</v>
+        <v>2273952729.754072</v>
       </c>
       <c r="I9">
-        <v>50780075.44420237</v>
+        <v>655062973.2302105</v>
       </c>
       <c r="J9">
-        <v>9636065.60022272</v>
+        <v>124305246.2428731</v>
       </c>
       <c r="K9">
-        <v>12377840.10089497</v>
+        <v>159674137.3015451</v>
       </c>
       <c r="L9">
-        <v>7565122.4649307</v>
+        <v>97590079.79760604</v>
       </c>
       <c r="M9">
-        <v>205039863.6793797</v>
+        <v>2645014241.463998</v>
       </c>
       <c r="N9">
-        <v>82068953.32912533</v>
+        <v>1058689497.945717</v>
       </c>
       <c r="O9">
-        <v>543743326.0260483</v>
+        <v>7014288905.736023</v>
       </c>
       <c r="P9">
-        <v>887702855.0634503</v>
+        <v>11451366830.31851</v>
       </c>
       <c r="Q9">
-        <v>798068779.2693942</v>
+        <v>10295087252.57519</v>
       </c>
       <c r="R9">
-        <v>678760810.5304863</v>
+        <v>8756014455.843275</v>
       </c>
       <c r="S9">
-        <v>666382970.4295915</v>
+        <v>8596340318.541731</v>
       </c>
     </row>
     <row r="10">
@@ -11175,58 +11175,58 @@
         </is>
       </c>
       <c r="B10">
-        <v>116052725.9028154</v>
+        <v>1497080164.146319</v>
       </c>
       <c r="C10">
-        <v>2659870.56856559</v>
+        <v>34312330.33449611</v>
       </c>
       <c r="D10">
-        <v>150980131.3763023</v>
+        <v>1947643694.7543</v>
       </c>
       <c r="E10">
-        <v>7294421.64229862</v>
+        <v>94098039.1856522</v>
       </c>
       <c r="F10">
-        <v>64866810.55287064</v>
+        <v>836781856.1320312</v>
       </c>
       <c r="G10">
-        <v>225801234.1400371</v>
+        <v>2912835920.406479</v>
       </c>
       <c r="H10">
-        <v>180065342.7243313</v>
+        <v>2322842921.143874</v>
       </c>
       <c r="I10">
-        <v>49965670.2811706</v>
+        <v>644557146.6271007</v>
       </c>
       <c r="J10">
-        <v>9850224.79160776</v>
+        <v>127067899.8117401</v>
       </c>
       <c r="K10">
-        <v>12181724.53765542</v>
+        <v>157144246.5357549</v>
       </c>
       <c r="L10">
-        <v>7511200.14183569</v>
+        <v>96894481.82968041</v>
       </c>
       <c r="M10">
-        <v>210007668.1613732</v>
+        <v>2709098919.281714</v>
       </c>
       <c r="N10">
-        <v>81454462.16604199</v>
+        <v>1050762561.941942</v>
       </c>
       <c r="O10">
-        <v>551036292.804016</v>
+        <v>7108368177.171806</v>
       </c>
       <c r="P10">
-        <v>892890252.8468686</v>
+        <v>11518284261.72461</v>
       </c>
       <c r="Q10">
-        <v>803924590.538991</v>
+        <v>10370627217.95298</v>
       </c>
       <c r="R10">
-        <v>687871864.6361754</v>
+        <v>8873547053.806664</v>
       </c>
       <c r="S10">
-        <v>675690140.09852</v>
+        <v>8716402807.270908</v>
       </c>
     </row>
     <row r="11">
@@ -11236,58 +11236,58 @@
         </is>
       </c>
       <c r="B11">
-        <v>113262927.3469141</v>
+        <v>1461091762.775191</v>
       </c>
       <c r="C11">
-        <v>2184032.95624178</v>
+        <v>28174025.13551896</v>
       </c>
       <c r="D11">
-        <v>148812207.7624098</v>
+        <v>1919677480.135087</v>
       </c>
       <c r="E11">
-        <v>6816964.07036263</v>
+        <v>87938836.50767793</v>
       </c>
       <c r="F11">
-        <v>64481247.02894932</v>
+        <v>831808086.6734462</v>
       </c>
       <c r="G11">
-        <v>222294451.8179635</v>
+        <v>2867598428.45173</v>
       </c>
       <c r="H11">
-        <v>180083140.3840127</v>
+        <v>2323072510.953764</v>
       </c>
       <c r="I11">
-        <v>48604871.38869966</v>
+        <v>627002840.9142256</v>
       </c>
       <c r="J11">
-        <v>10073823.96046418</v>
+        <v>129952329.0899879</v>
       </c>
       <c r="K11">
-        <v>11683280.98575103</v>
+        <v>150714324.7161883</v>
       </c>
       <c r="L11">
-        <v>6960742.18974173</v>
+        <v>89793574.24766833</v>
       </c>
       <c r="M11">
-        <v>217245196.0878552</v>
+        <v>2802463029.533333</v>
       </c>
       <c r="N11">
-        <v>79634885.92783159</v>
+        <v>1027290028.469028</v>
       </c>
       <c r="O11">
-        <v>554285940.9243562</v>
+        <v>7150288637.924195</v>
       </c>
       <c r="P11">
-        <v>889843320.0892339</v>
+        <v>11478978829.15112</v>
       </c>
       <c r="Q11">
-        <v>803247691.9716604</v>
+        <v>10361895226.43442</v>
       </c>
       <c r="R11">
-        <v>689984764.6247463</v>
+        <v>8900803463.659227</v>
       </c>
       <c r="S11">
-        <v>678301483.6389953</v>
+        <v>8750089138.943041</v>
       </c>
     </row>
     <row r="12">
@@ -11297,58 +11297,58 @@
         </is>
       </c>
       <c r="B12">
-        <v>111116945.4877574</v>
+        <v>1433408596.792071</v>
       </c>
       <c r="C12">
-        <v>2091172.30867991</v>
+        <v>26976122.78197084</v>
       </c>
       <c r="D12">
-        <v>148168314.2412637</v>
+        <v>1911371253.712301</v>
       </c>
       <c r="E12">
-        <v>6512808.99957316</v>
+        <v>84015236.09449376</v>
       </c>
       <c r="F12">
-        <v>63222604.63481815</v>
+        <v>815571599.7891542</v>
       </c>
       <c r="G12">
-        <v>219994900.1843349</v>
+        <v>2837934212.37792</v>
       </c>
       <c r="H12">
-        <v>178546433.8149293</v>
+        <v>2303248996.212587</v>
       </c>
       <c r="I12">
-        <v>47165760.17264844</v>
+        <v>608438306.2271649</v>
       </c>
       <c r="J12">
-        <v>10410273.44418898</v>
+        <v>134292527.4300378</v>
       </c>
       <c r="K12">
-        <v>11638534.32042797</v>
+        <v>150137092.7335208</v>
       </c>
       <c r="L12">
-        <v>6402451.95319142</v>
+        <v>82591630.19616932</v>
       </c>
       <c r="M12">
-        <v>220897456.1571814</v>
+        <v>2849577184.427641</v>
       </c>
       <c r="N12">
-        <v>78956207.7149881</v>
+        <v>1018535079.523346</v>
       </c>
       <c r="O12">
-        <v>554017117.5775557</v>
+        <v>7146820816.750468</v>
       </c>
       <c r="P12">
-        <v>885128963.2496479</v>
+        <v>11418163625.92046</v>
       </c>
       <c r="Q12">
-        <v>799770303.5814685</v>
+        <v>10317036916.20094</v>
       </c>
       <c r="R12">
-        <v>688653358.0937109</v>
+        <v>8883628319.408871</v>
       </c>
       <c r="S12">
-        <v>677014823.773283</v>
+        <v>8733491226.67535</v>
       </c>
     </row>
     <row r="13">
@@ -11358,58 +11358,58 @@
         </is>
       </c>
       <c r="B13">
-        <v>107803576.4472004</v>
+        <v>1390666136.168885</v>
       </c>
       <c r="C13">
-        <v>2094965.79453744</v>
+        <v>27025058.74953298</v>
       </c>
       <c r="D13">
-        <v>146276465.7570952</v>
+        <v>1886966408.266528</v>
       </c>
       <c r="E13">
-        <v>6444823.51578275</v>
+        <v>83138223.35359748</v>
       </c>
       <c r="F13">
-        <v>63771628.29850463</v>
+        <v>822654005.0507097</v>
       </c>
       <c r="G13">
-        <v>218587883.36592</v>
+        <v>2819783695.420368</v>
       </c>
       <c r="H13">
-        <v>175278416.080255</v>
+        <v>2261091567.435289</v>
       </c>
       <c r="I13">
-        <v>46126354.72334593</v>
+        <v>595029975.9311625</v>
       </c>
       <c r="J13">
-        <v>10601460.92238748</v>
+        <v>136758845.8987985</v>
       </c>
       <c r="K13">
-        <v>11526831.39233766</v>
+        <v>148696124.9611558</v>
       </c>
       <c r="L13">
-        <v>6409025.17465725</v>
+        <v>82676424.75307854</v>
       </c>
       <c r="M13">
-        <v>223717559.7329851</v>
+        <v>2885956520.555509</v>
       </c>
       <c r="N13">
-        <v>78834739.76405987</v>
+        <v>1016968142.956372</v>
       </c>
       <c r="O13">
-        <v>552494387.7900283</v>
+        <v>7127177602.491366</v>
       </c>
       <c r="P13">
-        <v>878885847.6031487</v>
+        <v>11337627434.08062</v>
       </c>
       <c r="Q13">
-        <v>793642082.6644316</v>
+        <v>10237982866.37117</v>
       </c>
       <c r="R13">
-        <v>685838506.2172312</v>
+        <v>8847316730.202282</v>
       </c>
       <c r="S13">
-        <v>674311674.8248935</v>
+        <v>8698620605.241127</v>
       </c>
     </row>
     <row r="14">
@@ -11419,58 +11419,58 @@
         </is>
       </c>
       <c r="B14">
-        <v>108220535.5503481</v>
+        <v>1396044908.599491</v>
       </c>
       <c r="C14">
-        <v>2191003.17427093</v>
+        <v>28263940.948095</v>
       </c>
       <c r="D14">
-        <v>144928076.5956818</v>
+        <v>1869572188.084295</v>
       </c>
       <c r="E14">
-        <v>6885809.23613185</v>
+        <v>88826939.14610086</v>
       </c>
       <c r="F14">
-        <v>62659130.20629372</v>
+        <v>808302779.661189</v>
       </c>
       <c r="G14">
-        <v>216664019.2123783</v>
+        <v>2794965847.83968</v>
       </c>
       <c r="H14">
-        <v>174540823.5468494</v>
+        <v>2251576623.754357</v>
       </c>
       <c r="I14">
-        <v>45340065.50735456</v>
+        <v>584886845.0448738</v>
       </c>
       <c r="J14">
-        <v>10855312.96180888</v>
+        <v>140033537.2073345</v>
       </c>
       <c r="K14">
-        <v>11850832.3994977</v>
+        <v>152875737.9535203</v>
       </c>
       <c r="L14">
-        <v>6385015.80446472</v>
+        <v>82366703.87759489</v>
       </c>
       <c r="M14">
-        <v>226910825.0372982</v>
+        <v>2927149642.981147</v>
       </c>
       <c r="N14">
-        <v>79602765.99833143</v>
+        <v>1026875681.378475</v>
       </c>
       <c r="O14">
-        <v>555485641.255605</v>
+        <v>7165764772.197305</v>
       </c>
       <c r="P14">
-        <v>880370196.0183313</v>
+        <v>11356775528.63647</v>
       </c>
       <c r="Q14">
-        <v>794382414.2155352</v>
+        <v>10247533143.3804</v>
       </c>
       <c r="R14">
-        <v>686161878.6651869</v>
+        <v>8851488234.78091</v>
       </c>
       <c r="S14">
-        <v>674311046.2656893</v>
+        <v>8698612496.827393</v>
       </c>
     </row>
     <row r="15">
@@ -11480,58 +11480,58 @@
         </is>
       </c>
       <c r="B15">
-        <v>107629145.2819052</v>
+        <v>1388415974.136577</v>
       </c>
       <c r="C15">
-        <v>2492151.50382714</v>
+        <v>32148754.39937011</v>
       </c>
       <c r="D15">
-        <v>141867052.9087834</v>
+        <v>1830084982.523306</v>
       </c>
       <c r="E15">
-        <v>7424488.79037077</v>
+        <v>95775905.39578293</v>
       </c>
       <c r="F15">
-        <v>61755244.14359539</v>
+        <v>796642649.4523805</v>
       </c>
       <c r="G15">
-        <v>213538937.3465767</v>
+        <v>2754652291.770839</v>
       </c>
       <c r="H15">
-        <v>174951712.1149791</v>
+        <v>2256877086.283231</v>
       </c>
       <c r="I15">
-        <v>46371133.45251936</v>
+        <v>598187621.5374998</v>
       </c>
       <c r="J15">
-        <v>11448380.87488418</v>
+        <v>147684113.2860059</v>
       </c>
       <c r="K15">
-        <v>11935915.43337403</v>
+        <v>153973309.090525</v>
       </c>
       <c r="L15">
-        <v>6667197.99961239</v>
+        <v>86006854.19499984</v>
       </c>
       <c r="M15">
-        <v>226069441.2796488</v>
+        <v>2916295792.50747</v>
       </c>
       <c r="N15">
-        <v>79674005.07682167</v>
+        <v>1027794665.491</v>
       </c>
       <c r="O15">
-        <v>557117786.2318398</v>
+        <v>7186819442.390734</v>
       </c>
       <c r="P15">
-        <v>878285868.8603215</v>
+        <v>11329887708.29815</v>
       </c>
       <c r="Q15">
-        <v>791944665.7838875</v>
+        <v>10216086188.61215</v>
       </c>
       <c r="R15">
-        <v>684315520.5019822</v>
+        <v>8827670214.475571</v>
       </c>
       <c r="S15">
-        <v>672379605.0686083</v>
+        <v>8673696905.385046</v>
       </c>
     </row>
     <row r="16">
@@ -11541,58 +11541,58 @@
         </is>
       </c>
       <c r="B16">
-        <v>106777040.4979495</v>
+        <v>1377423822.423549</v>
       </c>
       <c r="C16">
-        <v>2768126.81424195</v>
+        <v>35708835.90372115</v>
       </c>
       <c r="D16">
-        <v>140142595.0558865</v>
+        <v>1807839476.220936</v>
       </c>
       <c r="E16">
-        <v>7766179.35107514</v>
+        <v>100183713.6288693</v>
       </c>
       <c r="F16">
-        <v>60160503.01358151</v>
+        <v>776070488.8752015</v>
       </c>
       <c r="G16">
-        <v>210837404.2347851</v>
+        <v>2719802514.628728</v>
       </c>
       <c r="H16">
-        <v>175498008.4103935</v>
+        <v>2263924308.494076</v>
       </c>
       <c r="I16">
-        <v>46450287.77255129</v>
+        <v>599208712.2659116</v>
       </c>
       <c r="J16">
-        <v>11693605.80730686</v>
+        <v>150847514.9142585</v>
       </c>
       <c r="K16">
-        <v>11530194.1887926</v>
+        <v>148739505.0354245</v>
       </c>
       <c r="L16">
-        <v>6298296.77127961</v>
+        <v>81248028.34950697</v>
       </c>
       <c r="M16">
-        <v>223149765.0512092</v>
+        <v>2878631969.160598</v>
       </c>
       <c r="N16">
-        <v>79842182.91785458</v>
+        <v>1029964159.640324</v>
       </c>
       <c r="O16">
-        <v>554462340.9193877</v>
+        <v>7152564197.860102</v>
       </c>
       <c r="P16">
-        <v>872076785.6521223</v>
+        <v>11249790534.91238</v>
       </c>
       <c r="Q16">
-        <v>785936305.962988</v>
+        <v>10138578346.92255</v>
       </c>
       <c r="R16">
-        <v>679159265.4650385</v>
+        <v>8761154524.498997</v>
       </c>
       <c r="S16">
-        <v>667629071.276246</v>
+        <v>8612415019.463573</v>
       </c>
     </row>
     <row r="17">
@@ -11602,58 +11602,58 @@
         </is>
       </c>
       <c r="B17">
-        <v>106241997.9040006</v>
+        <v>1370521772.961607</v>
       </c>
       <c r="C17">
-        <v>2925029.03406839</v>
+        <v>37732874.53948224</v>
       </c>
       <c r="D17">
-        <v>140284741.0859932</v>
+        <v>1809673160.009313</v>
       </c>
       <c r="E17">
-        <v>8409641.705129759</v>
+        <v>108484377.9961739</v>
       </c>
       <c r="F17">
-        <v>59331843.12890658</v>
+        <v>765380776.3628949</v>
       </c>
       <c r="G17">
-        <v>210951254.954098</v>
+        <v>2721271188.907864</v>
       </c>
       <c r="H17">
-        <v>175671725.2439413</v>
+        <v>2266165255.646843</v>
       </c>
       <c r="I17">
-        <v>47148433.38450993</v>
+        <v>608214790.6601781</v>
       </c>
       <c r="J17">
-        <v>12219613.64185119</v>
+        <v>157633015.9798803</v>
       </c>
       <c r="K17">
-        <v>11545378.2102926</v>
+        <v>148935378.9127746</v>
       </c>
       <c r="L17">
-        <v>5898249.76362544</v>
+        <v>76087421.95076817</v>
       </c>
       <c r="M17">
-        <v>222036346.148135</v>
+        <v>2864268865.310942</v>
       </c>
       <c r="N17">
-        <v>80904045.34727392</v>
+        <v>1043662184.979833</v>
       </c>
       <c r="O17">
-        <v>555423791.7396295</v>
+        <v>7164966913.441221</v>
       </c>
       <c r="P17">
-        <v>872617044.5977279</v>
+        <v>11256759875.31069</v>
       </c>
       <c r="Q17">
-        <v>785814749.4868286</v>
+        <v>10137010268.38009</v>
       </c>
       <c r="R17">
-        <v>679572751.5828279</v>
+        <v>8766488495.41848</v>
       </c>
       <c r="S17">
-        <v>668027373.3725355</v>
+        <v>8617553116.505707</v>
       </c>
     </row>
     <row r="18">
@@ -11663,58 +11663,58 @@
         </is>
       </c>
       <c r="B18">
-        <v>106947489.2113899</v>
+        <v>1379622610.82693</v>
       </c>
       <c r="C18">
-        <v>2913353.5516346</v>
+        <v>37582260.81608634</v>
       </c>
       <c r="D18">
-        <v>138585859.951144</v>
+        <v>1787757593.369757</v>
       </c>
       <c r="E18">
-        <v>8632936.48106852</v>
+        <v>111364880.6057839</v>
       </c>
       <c r="F18">
-        <v>60265473.36897302</v>
+        <v>777424606.459752</v>
       </c>
       <c r="G18">
-        <v>210397623.3528201</v>
+        <v>2714129341.251379</v>
       </c>
       <c r="H18">
-        <v>172781546.1209413</v>
+        <v>2228881944.960144</v>
       </c>
       <c r="I18">
-        <v>48354444.84704691</v>
+        <v>623772338.5269052</v>
       </c>
       <c r="J18">
-        <v>11332146.88679635</v>
+        <v>146184694.8396729</v>
       </c>
       <c r="K18">
-        <v>11225994.54412336</v>
+        <v>144815329.6191913</v>
       </c>
       <c r="L18">
-        <v>5578907.09359861</v>
+        <v>71967901.50742207</v>
       </c>
       <c r="M18">
-        <v>220966457.9684491</v>
+        <v>2850467307.792994</v>
       </c>
       <c r="N18">
-        <v>81337289.40148686</v>
+        <v>1049251033.279181</v>
       </c>
       <c r="O18">
-        <v>551576786.8624426</v>
+        <v>7115340550.52551</v>
       </c>
       <c r="P18">
-        <v>868921899.4266527</v>
+        <v>11209092502.60382</v>
       </c>
       <c r="Q18">
-        <v>782005702.931567</v>
+        <v>10087873567.81721</v>
       </c>
       <c r="R18">
-        <v>675058213.7201772</v>
+        <v>8708250956.990286</v>
       </c>
       <c r="S18">
-        <v>663832219.1760538</v>
+        <v>8563435627.371095</v>
       </c>
     </row>
     <row r="19">
@@ -11724,58 +11724,58 @@
         </is>
       </c>
       <c r="B19">
-        <v>108363534.5793526</v>
+        <v>1397889596.073648</v>
       </c>
       <c r="C19">
-        <v>2743627.2052527</v>
+        <v>35392790.94775983</v>
       </c>
       <c r="D19">
-        <v>138633683.7358944</v>
+        <v>1788374520.193037</v>
       </c>
       <c r="E19">
-        <v>8465589.33478749</v>
+        <v>109206102.4187586</v>
       </c>
       <c r="F19">
-        <v>62172328.17870998</v>
+        <v>802023033.5053587</v>
       </c>
       <c r="G19">
-        <v>212015228.4546445</v>
+        <v>2734996447.064915</v>
       </c>
       <c r="H19">
-        <v>170147197.7374087</v>
+        <v>2194898850.812572</v>
       </c>
       <c r="I19">
-        <v>48157669.2434855</v>
+        <v>621233933.240963</v>
       </c>
       <c r="J19">
-        <v>10927491.13363655</v>
+        <v>140964635.6239115</v>
       </c>
       <c r="K19">
-        <v>11505016.12153364</v>
+        <v>148414707.967784</v>
       </c>
       <c r="L19">
-        <v>5279272.6508048</v>
+        <v>68102617.19538192</v>
       </c>
       <c r="M19">
-        <v>219575396.9317811</v>
+        <v>2832522620.419975</v>
       </c>
       <c r="N19">
-        <v>82714493.73824999</v>
+        <v>1067016969.223425</v>
       </c>
       <c r="O19">
-        <v>548306537.5569003</v>
+        <v>7073154334.484013</v>
       </c>
       <c r="P19">
-        <v>868685300.5908974</v>
+        <v>11206040377.62258</v>
       </c>
       <c r="Q19">
-        <v>780691534.2018425</v>
+        <v>10070920791.20377</v>
       </c>
       <c r="R19">
-        <v>672327999.6224899</v>
+        <v>8673031195.130119</v>
       </c>
       <c r="S19">
-        <v>660822983.5009563</v>
+        <v>8524616487.162336</v>
       </c>
     </row>
     <row r="20">
@@ -11785,58 +11785,58 @@
         </is>
       </c>
       <c r="B20">
-        <v>110036300.552118</v>
+        <v>1419468277.122323</v>
       </c>
       <c r="C20">
-        <v>2759541.65919375</v>
+        <v>35598087.40359937</v>
       </c>
       <c r="D20">
-        <v>136848731.4493778</v>
+        <v>1765348635.696974</v>
       </c>
       <c r="E20">
-        <v>8170999.497239321</v>
+        <v>105405893.5143872</v>
       </c>
       <c r="F20">
-        <v>63726832.65050225</v>
+        <v>822076141.191479</v>
       </c>
       <c r="G20">
-        <v>211506105.2563131</v>
+        <v>2728428757.806439</v>
       </c>
       <c r="H20">
-        <v>168512030.0741868</v>
+        <v>2173805187.95701</v>
       </c>
       <c r="I20">
-        <v>47349755.81359189</v>
+        <v>610811849.9953353</v>
       </c>
       <c r="J20">
-        <v>10456463.87219037</v>
+        <v>134888383.9512558</v>
       </c>
       <c r="K20">
-        <v>11975337.8301194</v>
+        <v>154481858.0085403</v>
       </c>
       <c r="L20">
-        <v>5457562.71406961</v>
+        <v>70402559.01149797</v>
       </c>
       <c r="M20">
-        <v>220899085.9360948</v>
+        <v>2849598208.575623</v>
       </c>
       <c r="N20">
-        <v>83699215.49778605</v>
+        <v>1079719879.92144</v>
       </c>
       <c r="O20">
-        <v>548349451.7380389</v>
+        <v>7073707927.420702</v>
       </c>
       <c r="P20">
-        <v>869891857.5464702</v>
+        <v>11221604962.34947</v>
       </c>
       <c r="Q20">
-        <v>780735079.3346144</v>
+        <v>10071482523.41653</v>
       </c>
       <c r="R20">
-        <v>670698778.7824962</v>
+        <v>8652014246.294203</v>
       </c>
       <c r="S20">
-        <v>658723440.952377</v>
+        <v>8497532388.285664</v>
       </c>
     </row>
     <row r="21">
@@ -11846,58 +11846,58 @@
         </is>
       </c>
       <c r="B21">
-        <v>111562229.2255841</v>
+        <v>1439152757.010035</v>
       </c>
       <c r="C21">
-        <v>2398440.77359463</v>
+        <v>30939885.97937073</v>
       </c>
       <c r="D21">
-        <v>135462747.5476158</v>
+        <v>1747469443.364243</v>
       </c>
       <c r="E21">
-        <v>7968708.775547121</v>
+        <v>102796343.2045579</v>
       </c>
       <c r="F21">
-        <v>63744065.93993428</v>
+        <v>822298450.6251522</v>
       </c>
       <c r="G21">
-        <v>209573963.0366918</v>
+        <v>2703504123.173324</v>
       </c>
       <c r="H21">
-        <v>165744423.9735495</v>
+        <v>2138103069.258788</v>
       </c>
       <c r="I21">
-        <v>46039164.94207455</v>
+        <v>593905227.7527617</v>
       </c>
       <c r="J21">
-        <v>9548249.23890375</v>
+        <v>123172415.1818584</v>
       </c>
       <c r="K21">
-        <v>12380682.81279047</v>
+        <v>159710808.284997</v>
       </c>
       <c r="L21">
-        <v>5975048.28787524</v>
+        <v>77078122.9135906</v>
       </c>
       <c r="M21">
-        <v>221453905.9955592</v>
+        <v>2856755387.342714</v>
       </c>
       <c r="N21">
-        <v>82328150.50178765</v>
+        <v>1062033141.473061</v>
       </c>
       <c r="O21">
-        <v>543469625.7525403</v>
+        <v>7010758172.20777</v>
       </c>
       <c r="P21">
-        <v>864605818.0148163</v>
+        <v>11153415052.39113</v>
       </c>
       <c r="Q21">
-        <v>776302619.2251533</v>
+        <v>10014303788.00448</v>
       </c>
       <c r="R21">
-        <v>664740389.9995692</v>
+        <v>8575151030.994442</v>
       </c>
       <c r="S21">
-        <v>652359707.1867788</v>
+        <v>8415440222.709447</v>
       </c>
     </row>
     <row r="22">
@@ -11907,58 +11907,58 @@
         </is>
       </c>
       <c r="B22">
-        <v>109905853.3666501</v>
+        <v>1417785508.429786</v>
       </c>
       <c r="C22">
-        <v>2134948.23101694</v>
+        <v>27540832.18011853</v>
       </c>
       <c r="D22">
-        <v>134058161.8587424</v>
+        <v>1729350287.977777</v>
       </c>
       <c r="E22">
-        <v>7787606.19256746</v>
+        <v>100460119.8841202</v>
       </c>
       <c r="F22">
-        <v>62208831.94475479</v>
+        <v>802493932.0873369</v>
       </c>
       <c r="G22">
-        <v>206189548.2270817</v>
+        <v>2659845172.129353</v>
       </c>
       <c r="H22">
-        <v>166395965.7464876</v>
+        <v>2146507958.12969</v>
       </c>
       <c r="I22">
-        <v>45317324.72894306</v>
+        <v>584593489.0033655</v>
       </c>
       <c r="J22">
-        <v>10014506.33949913</v>
+        <v>129187131.7795388</v>
       </c>
       <c r="K22">
-        <v>12543066.38177477</v>
+        <v>161805556.3248945</v>
       </c>
       <c r="L22">
-        <v>6177204.72765898</v>
+        <v>79685940.98680083</v>
       </c>
       <c r="M22">
-        <v>222590194.1170782</v>
+        <v>2871413504.110309</v>
       </c>
       <c r="N22">
-        <v>81773410.00111589</v>
+        <v>1054876989.014395</v>
       </c>
       <c r="O22">
-        <v>544811672.0425576</v>
+        <v>7028070569.348993</v>
       </c>
       <c r="P22">
-        <v>860907073.6362894</v>
+        <v>11105701249.90813</v>
       </c>
       <c r="Q22">
-        <v>772956458.9075145</v>
+        <v>9971138319.906937</v>
       </c>
       <c r="R22">
-        <v>663050605.5408643</v>
+        <v>8553352811.477151</v>
       </c>
       <c r="S22">
-        <v>650507539.1590896</v>
+        <v>8391547255.152256</v>
       </c>
     </row>
     <row r="23">
@@ -11968,58 +11968,58 @@
         </is>
       </c>
       <c r="B23">
-        <v>109109674.8581512</v>
+        <v>1407514805.670151</v>
       </c>
       <c r="C23">
-        <v>2193254.48617129</v>
+        <v>28292982.87160964</v>
       </c>
       <c r="D23">
-        <v>131886725.666456</v>
+        <v>1701338761.097282</v>
       </c>
       <c r="E23">
-        <v>7927609.10069648</v>
+        <v>102266157.3989846</v>
       </c>
       <c r="F23">
-        <v>58927944.86598135</v>
+        <v>760170488.7711594</v>
       </c>
       <c r="G23">
-        <v>200935534.1193051</v>
+        <v>2592068390.139036</v>
       </c>
       <c r="H23">
-        <v>167382195.2988973</v>
+        <v>2159230319.355776</v>
       </c>
       <c r="I23">
-        <v>45733415.38684289</v>
+        <v>589961058.4902732</v>
       </c>
       <c r="J23">
-        <v>9822400.27607627</v>
+        <v>126708963.5613839</v>
       </c>
       <c r="K23">
-        <v>12116352.8722035</v>
+        <v>156300952.0514252</v>
       </c>
       <c r="L23">
-        <v>6795085.24840055</v>
+        <v>87656599.7043671</v>
       </c>
       <c r="M23">
-        <v>223496510.4052218</v>
+        <v>2883104984.227362</v>
       </c>
       <c r="N23">
-        <v>80415861.32939427</v>
+        <v>1037364611.149186</v>
       </c>
       <c r="O23">
-        <v>545761820.8170366</v>
+        <v>7040327488.539772</v>
       </c>
       <c r="P23">
-        <v>855807029.7944928</v>
+        <v>11039910684.34896</v>
       </c>
       <c r="Q23">
-        <v>768596083.2166982</v>
+        <v>9914889473.495405</v>
       </c>
       <c r="R23">
-        <v>659486408.3585467</v>
+        <v>8507374667.825253</v>
       </c>
       <c r="S23">
-        <v>647370055.4863434</v>
+        <v>8351073715.773829</v>
       </c>
     </row>
     <row r="24">
@@ -12029,58 +12029,58 @@
         </is>
       </c>
       <c r="B24">
-        <v>108964535.0586959</v>
+        <v>1405642502.257177</v>
       </c>
       <c r="C24">
-        <v>1911314.55896017</v>
+        <v>24655957.81058619</v>
       </c>
       <c r="D24">
-        <v>130954408.6309637</v>
+        <v>1689311871.339432</v>
       </c>
       <c r="E24">
-        <v>8602606.195020579</v>
+        <v>110973619.9157655</v>
       </c>
       <c r="F24">
-        <v>57709959.46864699</v>
+        <v>744458477.1455462</v>
       </c>
       <c r="G24">
-        <v>199178288.8535914</v>
+        <v>2569399926.211329</v>
       </c>
       <c r="H24">
-        <v>167058291.6963988</v>
+        <v>2155051962.883544</v>
       </c>
       <c r="I24">
-        <v>46672927.3340468</v>
+        <v>602080762.6092037</v>
       </c>
       <c r="J24">
-        <v>9881560.115742229</v>
+        <v>127472125.4930748</v>
       </c>
       <c r="K24">
-        <v>11896599.7808952</v>
+        <v>153466137.1735481</v>
       </c>
       <c r="L24">
-        <v>7131071.48502055</v>
+        <v>91990822.1567651</v>
       </c>
       <c r="M24">
-        <v>224572035.3985901</v>
+        <v>2896979256.641812</v>
       </c>
       <c r="N24">
-        <v>79095000.33998445</v>
+        <v>1020325504.385799</v>
       </c>
       <c r="O24">
-        <v>546307486.1506782</v>
+        <v>7047366571.343748</v>
       </c>
       <c r="P24">
-        <v>854450310.0629653</v>
+        <v>11022408999.81225</v>
       </c>
       <c r="Q24">
-        <v>768224238.2379605</v>
+        <v>9910092673.26969</v>
       </c>
       <c r="R24">
-        <v>659259703.1792645</v>
+        <v>8504450171.012512</v>
       </c>
       <c r="S24">
-        <v>647363103.3983692</v>
+        <v>8350984033.838964</v>
       </c>
     </row>
     <row r="25">
@@ -12090,58 +12090,58 @@
         </is>
       </c>
       <c r="B25">
-        <v>107471043.9631148</v>
+        <v>1386376467.124181</v>
       </c>
       <c r="C25">
-        <v>2059672.53042558</v>
+        <v>26569775.64248998</v>
       </c>
       <c r="D25">
-        <v>129123410.2155039</v>
+        <v>1665691991.78</v>
       </c>
       <c r="E25">
-        <v>8932991.96283791</v>
+        <v>115235596.320609</v>
       </c>
       <c r="F25">
-        <v>56362863.38754957</v>
+        <v>727080937.6993895</v>
       </c>
       <c r="G25">
-        <v>196478938.0963169</v>
+        <v>2534578301.442489</v>
       </c>
       <c r="H25">
-        <v>167668583.1154553</v>
+        <v>2162924722.189374</v>
       </c>
       <c r="I25">
-        <v>47830714.091943</v>
+        <v>617016211.7860647</v>
       </c>
       <c r="J25">
-        <v>9955540.13521996</v>
+        <v>128426467.7443375</v>
       </c>
       <c r="K25">
-        <v>11604917.06263672</v>
+        <v>149703430.1080137</v>
       </c>
       <c r="L25">
-        <v>6593360.5354663</v>
+        <v>85054350.90751527</v>
       </c>
       <c r="M25">
-        <v>224855588.7050794</v>
+        <v>2900637094.295525</v>
       </c>
       <c r="N25">
-        <v>80247208.43999436</v>
+        <v>1035188988.875927</v>
       </c>
       <c r="O25">
-        <v>548755912.0857952</v>
+        <v>7078951265.906758</v>
       </c>
       <c r="P25">
-        <v>852705894.145227</v>
+        <v>10999906034.47343</v>
       </c>
       <c r="Q25">
-        <v>765865325.1697663</v>
+        <v>9879662694.689985</v>
       </c>
       <c r="R25">
-        <v>658394281.2066514</v>
+        <v>8493286227.565804</v>
       </c>
       <c r="S25">
-        <v>646789364.1440146</v>
+        <v>8343582797.457788</v>
       </c>
     </row>
     <row r="26">
@@ -12151,58 +12151,58 @@
         </is>
       </c>
       <c r="B26">
-        <v>104924228.6749098</v>
+        <v>1353522549.906337</v>
       </c>
       <c r="C26">
-        <v>2274397.38329936</v>
+        <v>29339726.24456174</v>
       </c>
       <c r="D26">
-        <v>127952414.4355274</v>
+        <v>1650586146.218303</v>
       </c>
       <c r="E26">
-        <v>9196656.96240589</v>
+        <v>118636874.815036</v>
       </c>
       <c r="F26">
-        <v>56940485.87766919</v>
+        <v>734532267.8219326</v>
       </c>
       <c r="G26">
-        <v>196363954.6589018</v>
+        <v>2533095015.099833</v>
       </c>
       <c r="H26">
-        <v>167819785.8727574</v>
+        <v>2164875237.75857</v>
       </c>
       <c r="I26">
-        <v>48237681.81656202</v>
+        <v>622266095.43365</v>
       </c>
       <c r="J26">
-        <v>9949737.303325329</v>
+        <v>128351611.2128968</v>
       </c>
       <c r="K26">
-        <v>11073579.37014346</v>
+        <v>142849173.8748506</v>
       </c>
       <c r="L26">
-        <v>6537601.18862066</v>
+        <v>84335055.33320652</v>
       </c>
       <c r="M26">
-        <v>223696309.8635307</v>
+        <v>2885682397.239546</v>
       </c>
       <c r="N26">
-        <v>80057727.80844738</v>
+        <v>1032744688.728971</v>
       </c>
       <c r="O26">
-        <v>547372423.223387</v>
+        <v>7061104259.581693</v>
       </c>
       <c r="P26">
-        <v>848660606.5571985</v>
+        <v>10947721824.58786</v>
       </c>
       <c r="Q26">
-        <v>762065277.5601306</v>
+        <v>9830642080.525684</v>
       </c>
       <c r="R26">
-        <v>657141048.8852206</v>
+        <v>8477119530.619347</v>
       </c>
       <c r="S26">
-        <v>646067469.5150771</v>
+        <v>8334270356.744495</v>
       </c>
     </row>
     <row r="27">
@@ -12212,58 +12212,58 @@
         </is>
       </c>
       <c r="B27">
-        <v>103776721.763821</v>
+        <v>1338719710.753291</v>
       </c>
       <c r="C27">
-        <v>2244131.46985639</v>
+        <v>28949295.96114743</v>
       </c>
       <c r="D27">
-        <v>129774724.985132</v>
+        <v>1674093952.308203</v>
       </c>
       <c r="E27">
-        <v>9437637.62110571</v>
+        <v>121745525.3122637</v>
       </c>
       <c r="F27">
-        <v>58283414.0389191</v>
+        <v>751856041.1020564</v>
       </c>
       <c r="G27">
-        <v>199739908.1150132</v>
+        <v>2576644814.683671</v>
       </c>
       <c r="H27">
-        <v>166624531.9974817</v>
+        <v>2149456462.767515</v>
       </c>
       <c r="I27">
-        <v>47756389.72110062</v>
+        <v>616057427.4021981</v>
       </c>
       <c r="J27">
-        <v>10403558.56246967</v>
+        <v>134205905.4558588</v>
       </c>
       <c r="K27">
-        <v>11234707.92068244</v>
+        <v>144927732.1768035</v>
       </c>
       <c r="L27">
-        <v>6123357.79714013</v>
+        <v>78991315.58310768</v>
       </c>
       <c r="M27">
-        <v>223334599.3062505</v>
+        <v>2881016331.050631</v>
       </c>
       <c r="N27">
-        <v>80739007.95744172</v>
+        <v>1041533202.650998</v>
       </c>
       <c r="O27">
-        <v>546216153.2625668</v>
+        <v>7046188377.087112</v>
       </c>
       <c r="P27">
-        <v>849732783.1414011</v>
+        <v>10961552902.52407</v>
       </c>
       <c r="Q27">
-        <v>762870417.3868191</v>
+        <v>9841028384.289967</v>
       </c>
       <c r="R27">
-        <v>659093695.6229981</v>
+        <v>8502308673.536676</v>
       </c>
       <c r="S27">
-        <v>647858987.7023156</v>
+        <v>8357380941.359871</v>
       </c>
     </row>
     <row r="28">
@@ -12273,58 +12273,58 @@
         </is>
       </c>
       <c r="B28">
-        <v>101910651.0676199</v>
+        <v>1314647398.772297</v>
       </c>
       <c r="C28">
-        <v>2059131.09132358</v>
+        <v>26562791.07807418</v>
       </c>
       <c r="D28">
-        <v>129586228.6363</v>
+        <v>1671662349.40827</v>
       </c>
       <c r="E28">
-        <v>9363141.12224862</v>
+        <v>120784520.4770072</v>
       </c>
       <c r="F28">
-        <v>59001379.89830228</v>
+        <v>761117800.6880994</v>
       </c>
       <c r="G28">
-        <v>200009880.7481745</v>
+        <v>2580127461.651451</v>
       </c>
       <c r="H28">
-        <v>165117631.8725399</v>
+        <v>2130017451.155765</v>
       </c>
       <c r="I28">
-        <v>47648133.14227971</v>
+        <v>614660917.5354083</v>
       </c>
       <c r="J28">
-        <v>10731143.23222517</v>
+        <v>138431747.6957047</v>
       </c>
       <c r="K28">
-        <v>10748704.81672443</v>
+        <v>138658292.1357452</v>
       </c>
       <c r="L28">
-        <v>5910335.998211</v>
+        <v>76243334.37692189</v>
       </c>
       <c r="M28">
-        <v>222239425.9463666</v>
+        <v>2866888594.708129</v>
       </c>
       <c r="N28">
-        <v>81587467.9396773</v>
+        <v>1052478336.421837</v>
       </c>
       <c r="O28">
-        <v>543982842.9480242</v>
+        <v>7017378674.029511</v>
       </c>
       <c r="P28">
-        <v>845903374.7638184</v>
+        <v>10912153534.45326</v>
       </c>
       <c r="Q28">
-        <v>758405570.8259301</v>
+        <v>9783431863.654499</v>
       </c>
       <c r="R28">
-        <v>656494919.7583102</v>
+        <v>8468784464.882202</v>
       </c>
       <c r="S28">
-        <v>645746214.9415858</v>
+        <v>8330126172.746456</v>
       </c>
     </row>
     <row r="29">
@@ -12334,58 +12334,58 @@
         </is>
       </c>
       <c r="B29">
-        <v>101483215.2847061</v>
+        <v>1309133477.172709</v>
       </c>
       <c r="C29">
-        <v>1711294.47999551</v>
+        <v>22075698.79194208</v>
       </c>
       <c r="D29">
-        <v>130165045.3317423</v>
+        <v>1679129084.779476</v>
       </c>
       <c r="E29">
-        <v>9220802.48524021</v>
+        <v>118948352.0595987</v>
       </c>
       <c r="F29">
-        <v>59636761.68778625</v>
+        <v>769314225.7724427</v>
       </c>
       <c r="G29">
-        <v>200733903.9847643</v>
+        <v>2589467361.403459</v>
       </c>
       <c r="H29">
-        <v>164397264.7647878</v>
+        <v>2120724715.465763</v>
       </c>
       <c r="I29">
-        <v>47298827.80496597</v>
+        <v>610154878.6840611</v>
       </c>
       <c r="J29">
-        <v>11301403.40359877</v>
+        <v>145788103.9064241</v>
       </c>
       <c r="K29">
-        <v>10325322.7629485</v>
+        <v>133196663.6420356</v>
       </c>
       <c r="L29">
-        <v>6273108.21835709</v>
+        <v>80923096.01680645</v>
       </c>
       <c r="M29">
-        <v>224864530.3208174</v>
+        <v>2900752441.138545</v>
       </c>
       <c r="N29">
-        <v>81825254.13815367</v>
+        <v>1055545778.382182</v>
       </c>
       <c r="O29">
-        <v>546285711.4136292</v>
+        <v>7047085677.235817</v>
       </c>
       <c r="P29">
-        <v>848502830.6830995</v>
+        <v>10945686515.81198</v>
       </c>
       <c r="Q29">
-        <v>760404468.3265889</v>
+        <v>9809217641.412996</v>
       </c>
       <c r="R29">
-        <v>658921253.0418828</v>
+        <v>8500084164.240287</v>
       </c>
       <c r="S29">
-        <v>648595930.2789342</v>
+        <v>8366887500.598251</v>
       </c>
     </row>
     <row r="30">
@@ -12395,58 +12395,58 @@
         </is>
       </c>
       <c r="B30">
-        <v>102986434.3729228</v>
+        <v>1328525003.410704</v>
       </c>
       <c r="C30">
-        <v>1426003.83653441</v>
+        <v>18395449.49129389</v>
       </c>
       <c r="D30">
-        <v>130410167.9866703</v>
+        <v>1682291167.028047</v>
       </c>
       <c r="E30">
-        <v>9170314.144099571</v>
+        <v>118297052.4588845</v>
       </c>
       <c r="F30">
-        <v>59234120.35059723</v>
+        <v>764120152.5227044</v>
       </c>
       <c r="G30">
-        <v>200240606.3179016</v>
+        <v>2583103821.50093</v>
       </c>
       <c r="H30">
-        <v>163564338.7448695</v>
+        <v>2109979969.808816</v>
       </c>
       <c r="I30">
-        <v>47118667.39124201</v>
+        <v>607830809.3470219</v>
       </c>
       <c r="J30">
-        <v>12141906.64042575</v>
+        <v>156630595.6614922</v>
       </c>
       <c r="K30">
-        <v>10352893.89558903</v>
+        <v>133552331.2530985</v>
       </c>
       <c r="L30">
-        <v>6488989.614457469</v>
+        <v>83707966.02650136</v>
       </c>
       <c r="M30">
-        <v>228916847.149009</v>
+        <v>2953027328.222217</v>
       </c>
       <c r="N30">
-        <v>82501263.72655508</v>
+        <v>1064266302.072561</v>
       </c>
       <c r="O30">
-        <v>551084907.1621478</v>
+        <v>7108995302.391706</v>
       </c>
       <c r="P30">
-        <v>854311947.8529721</v>
+        <v>11020624127.30334</v>
       </c>
       <c r="Q30">
-        <v>765321694.5119597</v>
+        <v>9872649859.204281</v>
       </c>
       <c r="R30">
-        <v>662335260.1390369</v>
+        <v>8544124855.793576</v>
       </c>
       <c r="S30">
-        <v>651982366.2434478</v>
+        <v>8410572524.540477</v>
       </c>
     </row>
     <row r="31">
@@ -12456,58 +12456,58 @@
         </is>
       </c>
       <c r="B31">
-        <v>104034540.4397832</v>
+        <v>1342045571.673204</v>
       </c>
       <c r="C31">
-        <v>1410173.04231299</v>
+        <v>18191232.24583757</v>
       </c>
       <c r="D31">
-        <v>128985075.738232</v>
+        <v>1663907477.023193</v>
       </c>
       <c r="E31">
-        <v>8896863.41900355</v>
+        <v>114769538.1051458</v>
       </c>
       <c r="F31">
-        <v>59522290.14339885</v>
+        <v>767837542.8498452</v>
       </c>
       <c r="G31">
-        <v>198814402.3429474</v>
+        <v>2564705790.224022</v>
       </c>
       <c r="H31">
-        <v>164787589.3460307</v>
+        <v>2125759902.563796</v>
       </c>
       <c r="I31">
-        <v>48549038.88398785</v>
+        <v>626282601.6034433</v>
       </c>
       <c r="J31">
-        <v>12877759.12543562</v>
+        <v>166123092.7181195</v>
       </c>
       <c r="K31">
-        <v>10071702.03025938</v>
+        <v>129924956.190346</v>
       </c>
       <c r="L31">
-        <v>6480926.29925403</v>
+        <v>83603949.26037699</v>
       </c>
       <c r="M31">
-        <v>231456821.9751945</v>
+        <v>2985793003.480008</v>
       </c>
       <c r="N31">
-        <v>83836183.35564686</v>
+        <v>1081486765.287844</v>
       </c>
       <c r="O31">
-        <v>558060021.0158088</v>
+        <v>7198974271.103933</v>
       </c>
       <c r="P31">
-        <v>860908963.7985394</v>
+        <v>11105725633.00116</v>
       </c>
       <c r="Q31">
-        <v>770591854.1436387</v>
+        <v>9940634918.45294</v>
       </c>
       <c r="R31">
-        <v>666557313.7038554</v>
+        <v>8598589346.779736</v>
       </c>
       <c r="S31">
-        <v>656485611.673596</v>
+        <v>8468664390.589389</v>
       </c>
     </row>
     <row r="32">
@@ -12517,58 +12517,58 @@
         </is>
       </c>
       <c r="B32">
-        <v>104110257.0352691</v>
+        <v>1343022315.754972</v>
       </c>
       <c r="C32">
-        <v>1568953.82261277</v>
+        <v>20239504.31170473</v>
       </c>
       <c r="D32">
-        <v>129486080.2556366</v>
+        <v>1670370435.297712</v>
       </c>
       <c r="E32">
-        <v>8374794.40724212</v>
+        <v>108034847.8534234</v>
       </c>
       <c r="F32">
-        <v>59206754.58259921</v>
+        <v>763767134.1155299</v>
       </c>
       <c r="G32">
-        <v>198636583.0680907</v>
+        <v>2562411921.57837</v>
       </c>
       <c r="H32">
-        <v>167714270.2083758</v>
+        <v>2163514085.688048</v>
       </c>
       <c r="I32">
-        <v>50774691.27736341</v>
+        <v>654993517.477988</v>
       </c>
       <c r="J32">
-        <v>13383830.51749098</v>
+        <v>172651413.6756336</v>
       </c>
       <c r="K32">
-        <v>10172863.73383144</v>
+        <v>131229942.1664256</v>
       </c>
       <c r="L32">
-        <v>6227575.12825842</v>
+        <v>80335719.15453362</v>
       </c>
       <c r="M32">
-        <v>232588199.7258682</v>
+        <v>3000387776.463699</v>
       </c>
       <c r="N32">
-        <v>85293541.26838894</v>
+        <v>1100286682.362217</v>
       </c>
       <c r="O32">
-        <v>566154971.8595772</v>
+        <v>7303399136.988546</v>
       </c>
       <c r="P32">
-        <v>868901811.962937</v>
+        <v>11208833374.32189</v>
       </c>
       <c r="Q32">
-        <v>777380695.5662897</v>
+        <v>10028210972.80514</v>
       </c>
       <c r="R32">
-        <v>673270438.5310206</v>
+        <v>8685188657.050167</v>
       </c>
       <c r="S32">
-        <v>663097574.7971891</v>
+        <v>8553958714.883739</v>
       </c>
     </row>
     <row r="33">
@@ -12578,58 +12578,58 @@
         </is>
       </c>
       <c r="B33">
-        <v>102174440.3740937</v>
+        <v>1318050280.825809</v>
       </c>
       <c r="C33">
-        <v>1811356.12278338</v>
+        <v>23366493.9839056</v>
       </c>
       <c r="D33">
-        <v>131168470.2508268</v>
+        <v>1692073266.235665</v>
       </c>
       <c r="E33">
-        <v>7512417.35486259</v>
+        <v>96910183.87772742</v>
       </c>
       <c r="F33">
-        <v>58743569.76124892</v>
+        <v>757792049.9201111</v>
       </c>
       <c r="G33">
-        <v>199235813.4897217</v>
+        <v>2570141994.017409</v>
       </c>
       <c r="H33">
-        <v>170339162.2363604</v>
+        <v>2197375192.849049</v>
       </c>
       <c r="I33">
-        <v>52557272.04183592</v>
+        <v>677988809.3396834</v>
       </c>
       <c r="J33">
-        <v>13829104.17144683</v>
+        <v>178395443.8116641</v>
       </c>
       <c r="K33">
-        <v>9850144.51235736</v>
+        <v>127066864.20941</v>
       </c>
       <c r="L33">
-        <v>6213106.39543472</v>
+        <v>80149072.50110789</v>
       </c>
       <c r="M33">
-        <v>233476536.448547</v>
+        <v>3011847320.186256</v>
       </c>
       <c r="N33">
-        <v>85422984.42458972</v>
+        <v>1101956499.077208</v>
       </c>
       <c r="O33">
-        <v>571688310.230572</v>
+        <v>7374779201.974379</v>
       </c>
       <c r="P33">
-        <v>873098564.0943873</v>
+        <v>11262971476.8176</v>
       </c>
       <c r="Q33">
-        <v>781462473.2743629</v>
+        <v>10080865905.23928</v>
       </c>
       <c r="R33">
-        <v>679288032.9002692</v>
+        <v>8762815624.413471</v>
       </c>
       <c r="S33">
-        <v>669437888.3879118</v>
+        <v>8635748760.204062</v>
       </c>
     </row>
     <row r="34">
@@ -12639,58 +12639,58 @@
         </is>
       </c>
       <c r="B34">
-        <v>99999430.61942062</v>
+        <v>1289992654.990526</v>
       </c>
       <c r="C34">
-        <v>1817183.90657845</v>
+        <v>23441672.394862</v>
       </c>
       <c r="D34">
-        <v>129113015.4858677</v>
+        <v>1665557899.767694</v>
       </c>
       <c r="E34">
-        <v>6579951.29956717</v>
+        <v>84881371.76441649</v>
       </c>
       <c r="F34">
-        <v>58145042.13504493</v>
+        <v>750071043.5420796</v>
       </c>
       <c r="G34">
-        <v>195655192.8270583</v>
+        <v>2523951987.469052</v>
       </c>
       <c r="H34">
-        <v>168040895.2108716</v>
+        <v>2167727548.220243</v>
       </c>
       <c r="I34">
-        <v>53334994.68481916</v>
+        <v>688021431.4341671</v>
       </c>
       <c r="J34">
-        <v>13771365.50034828</v>
+        <v>177650614.9544928</v>
       </c>
       <c r="K34">
-        <v>9334809.68114181</v>
+        <v>120419044.8867294</v>
       </c>
       <c r="L34">
-        <v>5653186.42342324</v>
+        <v>72926104.86215979</v>
       </c>
       <c r="M34">
-        <v>228337330.7340472</v>
+        <v>2945551566.469209</v>
       </c>
       <c r="N34">
-        <v>85200517.14303488</v>
+        <v>1099086671.14515</v>
       </c>
       <c r="O34">
-        <v>563673099.3776863</v>
+        <v>7271382981.972153</v>
       </c>
       <c r="P34">
-        <v>859327722.824165</v>
+        <v>11085327624.43173</v>
       </c>
       <c r="Q34">
-        <v>768474019.2577069</v>
+        <v>9913314848.424419</v>
       </c>
       <c r="R34">
-        <v>668474588.6382862</v>
+        <v>8623322193.433891</v>
       </c>
       <c r="S34">
-        <v>659139778.9571445</v>
+        <v>8502903148.547165</v>
       </c>
     </row>
     <row r="35">
@@ -12700,58 +12700,58 @@
         </is>
       </c>
       <c r="B35">
-        <v>99091464.80526732</v>
+        <v>1278279895.987948</v>
       </c>
       <c r="C35">
-        <v>1598323.91400222</v>
+        <v>20618378.49062864</v>
       </c>
       <c r="D35">
-        <v>121042233.7597784</v>
+        <v>1561444815.501142</v>
       </c>
       <c r="E35">
-        <v>6294267.93440672</v>
+        <v>81196056.3538467</v>
       </c>
       <c r="F35">
-        <v>53355549.54581177</v>
+        <v>688286589.1409718</v>
       </c>
       <c r="G35">
-        <v>182290375.1539991</v>
+        <v>2351545839.486589</v>
       </c>
       <c r="H35">
-        <v>156846683.978973</v>
+        <v>2023322223.328751</v>
       </c>
       <c r="I35">
-        <v>50466482.05939038</v>
+        <v>651017618.5661359</v>
       </c>
       <c r="J35">
-        <v>12962439.50323378</v>
+        <v>167215469.5917158</v>
       </c>
       <c r="K35">
-        <v>8881558.60113031</v>
+        <v>114572105.954581</v>
       </c>
       <c r="L35">
-        <v>5205025.38669357</v>
+        <v>67144827.48834705</v>
       </c>
       <c r="M35">
-        <v>212248961.5057303</v>
+        <v>2738011603.423921</v>
       </c>
       <c r="N35">
-        <v>80949187.54161273</v>
+        <v>1044244519.286804</v>
       </c>
       <c r="O35">
-        <v>527560338.5767641</v>
+        <v>6805528367.640257</v>
       </c>
       <c r="P35">
-        <v>808942178.5360305</v>
+        <v>10435354103.11479</v>
       </c>
       <c r="Q35">
-        <v>722787965.6077242</v>
+        <v>9323964756.339643</v>
       </c>
       <c r="R35">
-        <v>623696500.8024569</v>
+        <v>8045684860.351692</v>
       </c>
       <c r="S35">
-        <v>614814942.2013266</v>
+        <v>7931112754.397114</v>
       </c>
     </row>
     <row r="36">
@@ -12761,58 +12761,58 @@
         </is>
       </c>
       <c r="B36">
-        <v>100716176.8491455</v>
+        <v>1299238681.353977</v>
       </c>
       <c r="C36">
-        <v>1378372.0441091</v>
+        <v>17780999.36900739</v>
       </c>
       <c r="D36">
-        <v>115696160.2030079</v>
+        <v>1492480466.618802</v>
       </c>
       <c r="E36">
-        <v>6076426.75757784</v>
+        <v>78385905.17275414</v>
       </c>
       <c r="F36">
-        <v>50263857.02235265</v>
+        <v>648403755.5883491</v>
       </c>
       <c r="G36">
-        <v>173414816.0270475</v>
+        <v>2237051126.748913</v>
       </c>
       <c r="H36">
-        <v>147477841.9754297</v>
+        <v>1902464161.483042</v>
       </c>
       <c r="I36">
-        <v>46691595.90375389</v>
+        <v>602321587.1584252</v>
       </c>
       <c r="J36">
-        <v>13317117.22349673</v>
+        <v>171790812.1831078</v>
       </c>
       <c r="K36">
-        <v>9421451.898424011</v>
+        <v>121536729.4896697</v>
       </c>
       <c r="L36">
-        <v>4792397.44094577</v>
+        <v>61821926.98820043</v>
       </c>
       <c r="M36">
-        <v>200890167.1881531</v>
+        <v>2591483156.727175</v>
       </c>
       <c r="N36">
-        <v>77353337.50914007</v>
+        <v>997858053.867907</v>
       </c>
       <c r="O36">
-        <v>499943909.1393433</v>
+        <v>6449276427.897529</v>
       </c>
       <c r="P36">
-        <v>774074902.0155362</v>
+        <v>9985566236.000416</v>
       </c>
       <c r="Q36">
-        <v>691929167.0654504</v>
+        <v>8925886255.14431</v>
       </c>
       <c r="R36">
-        <v>591212990.2163048</v>
+        <v>7626647573.790332</v>
       </c>
       <c r="S36">
-        <v>581791538.3178809</v>
+        <v>7505110844.300664</v>
       </c>
     </row>
     <row r="37">
@@ -12822,58 +12822,58 @@
         </is>
       </c>
       <c r="B37">
-        <v>105388150.4148267</v>
+        <v>1359507140.351265</v>
       </c>
       <c r="C37">
-        <v>1044690.57002966</v>
+        <v>13476508.35338261</v>
       </c>
       <c r="D37">
-        <v>109510145.4264954</v>
+        <v>1412680876.001791</v>
       </c>
       <c r="E37">
-        <v>6563294.43358545</v>
+        <v>84666498.19325231</v>
       </c>
       <c r="F37">
-        <v>47582219.2199963</v>
+        <v>613810627.9379524</v>
       </c>
       <c r="G37">
-        <v>164700349.6501068</v>
+        <v>2124634510.486378</v>
       </c>
       <c r="H37">
-        <v>143411488.5275888</v>
+        <v>1850008202.005896</v>
       </c>
       <c r="I37">
-        <v>43954198.69267925</v>
+        <v>567009163.1355623</v>
       </c>
       <c r="J37">
-        <v>13595620.02225798</v>
+        <v>175383498.287128</v>
       </c>
       <c r="K37">
-        <v>10959663.21340922</v>
+        <v>141379655.4529789</v>
       </c>
       <c r="L37">
-        <v>4030365.29133395</v>
+        <v>51991712.25820795</v>
       </c>
       <c r="M37">
-        <v>192470010.1773918</v>
+        <v>2482863131.288355</v>
       </c>
       <c r="N37">
-        <v>75809332.18979894</v>
+        <v>977940385.2484063</v>
       </c>
       <c r="O37">
-        <v>484230678.1144601</v>
+        <v>6246575747.676536</v>
       </c>
       <c r="P37">
-        <v>754319178.1793935</v>
+        <v>9730717398.514177</v>
       </c>
       <c r="Q37">
-        <v>674479480.6982608</v>
+        <v>8700785301.007565</v>
       </c>
       <c r="R37">
-        <v>569091330.2834339</v>
+        <v>7341278160.656298</v>
       </c>
       <c r="S37">
-        <v>558131667.0700247</v>
+        <v>7199898505.20332</v>
       </c>
     </row>
     <row r="38">
@@ -12883,58 +12883,58 @@
         </is>
       </c>
       <c r="B38">
-        <v>108585712.8715441</v>
+        <v>1400755696.042918</v>
       </c>
       <c r="C38">
-        <v>1096402.51431606</v>
+        <v>14143592.43467717</v>
       </c>
       <c r="D38">
-        <v>108106527.1192248</v>
+        <v>1394574199.838001</v>
       </c>
       <c r="E38">
-        <v>6956504.70140314</v>
+        <v>89738910.64810051</v>
       </c>
       <c r="F38">
-        <v>45309014.54112862</v>
+        <v>584486287.5805591</v>
       </c>
       <c r="G38">
-        <v>161468448.8760726</v>
+        <v>2082942990.501337</v>
       </c>
       <c r="H38">
-        <v>144401384.3808429</v>
+        <v>1862777858.512873</v>
       </c>
       <c r="I38">
-        <v>41367629.44867035</v>
+        <v>533642419.8878475</v>
       </c>
       <c r="J38">
-        <v>14127378.52868355</v>
+        <v>182243183.0200178</v>
       </c>
       <c r="K38">
-        <v>13254288.85316651</v>
+        <v>170980326.205848</v>
       </c>
       <c r="L38">
-        <v>3906845.20731221</v>
+        <v>50398303.17432751</v>
       </c>
       <c r="M38">
-        <v>192837389.1800238</v>
+        <v>2487602320.422307</v>
       </c>
       <c r="N38">
-        <v>76221742.13099863</v>
+        <v>983260473.4898822</v>
       </c>
       <c r="O38">
-        <v>486116657.729698</v>
+        <v>6270904884.713104</v>
       </c>
       <c r="P38">
-        <v>756170819.4773147</v>
+        <v>9754603571.25736</v>
       </c>
       <c r="Q38">
-        <v>676042232.1390039</v>
+        <v>8720944794.593151</v>
       </c>
       <c r="R38">
-        <v>567456519.2674599</v>
+        <v>7320189098.550232</v>
       </c>
       <c r="S38">
-        <v>554202230.4142933</v>
+        <v>7149208772.344383</v>
       </c>
     </row>
     <row r="39">
@@ -12944,58 +12944,58 @@
         </is>
       </c>
       <c r="B39">
-        <v>113962330.3634845</v>
+        <v>1470114061.68895</v>
       </c>
       <c r="C39">
-        <v>1321469.31731694</v>
+        <v>17046954.19338853</v>
       </c>
       <c r="D39">
-        <v>112267866.4167982</v>
+        <v>1448255476.776697</v>
       </c>
       <c r="E39">
-        <v>7181043.06833449</v>
+        <v>92635455.58151492</v>
       </c>
       <c r="F39">
-        <v>48039383.23743252</v>
+        <v>619708043.7628795</v>
       </c>
       <c r="G39">
-        <v>168809762.0398821</v>
+        <v>2177645930.314479</v>
       </c>
       <c r="H39">
-        <v>155220843.7193559</v>
+        <v>2002348883.979692</v>
       </c>
       <c r="I39">
-        <v>41677989.76412698</v>
+        <v>537646067.9572381</v>
       </c>
       <c r="J39">
-        <v>15348879.63025953</v>
+        <v>198000547.2303479</v>
       </c>
       <c r="K39">
-        <v>15323141.89937581</v>
+        <v>197668530.501948</v>
       </c>
       <c r="L39">
-        <v>3880494.91447237</v>
+        <v>50058384.39669357</v>
       </c>
       <c r="M39">
-        <v>203181506.8191523</v>
+        <v>2621041437.967065</v>
       </c>
       <c r="N39">
-        <v>80026490.37172601</v>
+        <v>1032341725.795265</v>
       </c>
       <c r="O39">
-        <v>514659347.118469</v>
+        <v>6639105577.82825</v>
       </c>
       <c r="P39">
-        <v>797431439.5218357</v>
+        <v>10286865569.83168</v>
       </c>
       <c r="Q39">
-        <v>713524454.2356373</v>
+        <v>9204465459.639721</v>
       </c>
       <c r="R39">
-        <v>599562123.8721528</v>
+        <v>7734351397.950771</v>
       </c>
       <c r="S39">
-        <v>584238981.9727769</v>
+        <v>7536682867.448822</v>
       </c>
     </row>
     <row r="40">
@@ -13005,58 +13005,58 @@
         </is>
       </c>
       <c r="B40">
-        <v>117260220.1777914</v>
+        <v>1512656840.293509</v>
       </c>
       <c r="C40">
-        <v>1591023.37491123</v>
+        <v>20524201.53635487</v>
       </c>
       <c r="D40">
-        <v>114227878.7479122</v>
+        <v>1473539635.848068</v>
       </c>
       <c r="E40">
-        <v>7035243.785143221</v>
+        <v>90754644.82834755</v>
       </c>
       <c r="F40">
-        <v>50188604.42490945</v>
+        <v>647432997.081332</v>
       </c>
       <c r="G40">
-        <v>173042750.3328761</v>
+        <v>2232251479.294102</v>
       </c>
       <c r="H40">
-        <v>163937573.3929534</v>
+        <v>2114794696.769099</v>
       </c>
       <c r="I40">
-        <v>42709573.62341871</v>
+        <v>550953499.7421013</v>
       </c>
       <c r="J40">
-        <v>15891678.72734587</v>
+        <v>205002655.5827617</v>
       </c>
       <c r="K40">
-        <v>15564470.20061247</v>
+        <v>200781665.5879009</v>
       </c>
       <c r="L40">
-        <v>4200105.81644046</v>
+        <v>54181365.03208193</v>
       </c>
       <c r="M40">
-        <v>212617176.0716491</v>
+        <v>2742761571.324274</v>
       </c>
       <c r="N40">
-        <v>83301778.89108524</v>
+        <v>1074592947.694999</v>
       </c>
       <c r="O40">
-        <v>538222356.7235053</v>
+        <v>6943068401.733218</v>
       </c>
       <c r="P40">
-        <v>828525327.2341729</v>
+        <v>10687976721.32083</v>
       </c>
       <c r="Q40">
-        <v>741023442.5266472</v>
+        <v>9559202408.59375</v>
       </c>
       <c r="R40">
-        <v>623763222.3488557</v>
+        <v>8046545568.300239</v>
       </c>
       <c r="S40">
-        <v>608198752.1482432</v>
+        <v>7845763902.712337</v>
       </c>
     </row>
     <row r="41">
@@ -13066,58 +13066,58 @@
         </is>
       </c>
       <c r="B41">
-        <v>117216207.3829644</v>
+        <v>1512089075.24024</v>
       </c>
       <c r="C41">
-        <v>1995959.98510548</v>
+        <v>25747883.80786069</v>
       </c>
       <c r="D41">
-        <v>118215022.9276762</v>
+        <v>1524973795.767023</v>
       </c>
       <c r="E41">
-        <v>6798712.21836064</v>
+        <v>87703387.61685225</v>
       </c>
       <c r="F41">
-        <v>52220070.84534126</v>
+        <v>673638913.9049022</v>
       </c>
       <c r="G41">
-        <v>179229765.9764835</v>
+        <v>2312063981.096638</v>
       </c>
       <c r="H41">
-        <v>166548843.7284903</v>
+        <v>2148480084.097525</v>
       </c>
       <c r="I41">
-        <v>42064200.89369909</v>
+        <v>542628191.5287182</v>
       </c>
       <c r="J41">
-        <v>15636595.83295449</v>
+        <v>201712086.2451129</v>
       </c>
       <c r="K41">
-        <v>15039784.4520351</v>
+        <v>194013219.4312528</v>
       </c>
       <c r="L41">
-        <v>4759919.46806754</v>
+        <v>61402961.13807127</v>
       </c>
       <c r="M41">
-        <v>219454358.5063266</v>
+        <v>2830961224.731613</v>
       </c>
       <c r="N41">
-        <v>85309950.39902771</v>
+        <v>1100498360.147457</v>
       </c>
       <c r="O41">
-        <v>548813653.2806008</v>
+        <v>7079696127.31975</v>
       </c>
       <c r="P41">
-        <v>845259626.6400487</v>
+        <v>10903849183.65663</v>
       </c>
       <c r="Q41">
-        <v>755189756.7729536</v>
+        <v>9741947862.371101</v>
       </c>
       <c r="R41">
-        <v>637973549.3899891</v>
+        <v>8229858787.130859</v>
       </c>
       <c r="S41">
-        <v>622933764.9379539</v>
+        <v>8035845567.699606</v>
       </c>
     </row>
     <row r="42">
@@ -13127,58 +13127,58 @@
         </is>
       </c>
       <c r="B42">
-        <v>118045196.1464588</v>
+        <v>1522783030.289318</v>
       </c>
       <c r="C42">
-        <v>2100355.32195764</v>
+        <v>27094583.65325356</v>
       </c>
       <c r="D42">
-        <v>121453897.1000887</v>
+        <v>1566755272.591145</v>
       </c>
       <c r="E42">
-        <v>6924268.507121691</v>
+        <v>89323063.74186981</v>
       </c>
       <c r="F42">
-        <v>54338642.73559266</v>
+        <v>700968491.2891454</v>
       </c>
       <c r="G42">
-        <v>184817163.6647607</v>
+        <v>2384141411.275414</v>
       </c>
       <c r="H42">
-        <v>168899665.6921781</v>
+        <v>2178805687.429097</v>
       </c>
       <c r="I42">
-        <v>43779650.36513062</v>
+        <v>564757489.7101851</v>
       </c>
       <c r="J42">
-        <v>15277106.65800659</v>
+        <v>197074675.888285</v>
       </c>
       <c r="K42">
-        <v>13792720.55954587</v>
+        <v>177926095.2181417</v>
       </c>
       <c r="L42">
-        <v>5887631.12224602</v>
+        <v>75950441.47697365</v>
       </c>
       <c r="M42">
-        <v>223522244.1728119</v>
+        <v>2883436949.829274</v>
       </c>
       <c r="N42">
-        <v>85277911.94596818</v>
+        <v>1100085064.10299</v>
       </c>
       <c r="O42">
-        <v>556436930.5158873</v>
+        <v>7178036403.654946</v>
       </c>
       <c r="P42">
-        <v>859299290.3271068</v>
+        <v>11084960845.21968</v>
       </c>
       <c r="Q42">
-        <v>768133747.2588927</v>
+        <v>9908925339.639715</v>
       </c>
       <c r="R42">
-        <v>650088551.1124337</v>
+        <v>8386142309.350395</v>
       </c>
       <c r="S42">
-        <v>636295830.5528879</v>
+        <v>8208216214.132254</v>
       </c>
     </row>
     <row r="43">
@@ -13188,58 +13188,58 @@
         </is>
       </c>
       <c r="B43">
-        <v>114330406.02468</v>
+        <v>1474862237.718371</v>
       </c>
       <c r="C43">
-        <v>2078923.86889499</v>
+        <v>26818117.90874537</v>
       </c>
       <c r="D43">
-        <v>126011986.9239318</v>
+        <v>1625554631.31872</v>
       </c>
       <c r="E43">
-        <v>6568026.30076395</v>
+        <v>84727539.27985495</v>
       </c>
       <c r="F43">
-        <v>55503097.70171221</v>
+        <v>715989960.3520875</v>
       </c>
       <c r="G43">
-        <v>190162034.7953029</v>
+        <v>2453090248.859408</v>
       </c>
       <c r="H43">
-        <v>169908064.3047049</v>
+        <v>2191814029.530693</v>
       </c>
       <c r="I43">
-        <v>46024660.65596671</v>
+        <v>593718122.4619706</v>
       </c>
       <c r="J43">
-        <v>14843924.16901571</v>
+        <v>191486621.7803026</v>
       </c>
       <c r="K43">
-        <v>12897662.35263471</v>
+        <v>166379844.3489878</v>
       </c>
       <c r="L43">
-        <v>7099699.4278555</v>
+        <v>91586122.61933595</v>
       </c>
       <c r="M43">
-        <v>231305940.2280366</v>
+        <v>2983846628.941671</v>
       </c>
       <c r="N43">
-        <v>85735052.0572792</v>
+        <v>1105982171.538902</v>
       </c>
       <c r="O43">
-        <v>567815003.1954932</v>
+        <v>7324813541.221864</v>
       </c>
       <c r="P43">
-        <v>872307444.0154762</v>
+        <v>11252766027.79964</v>
       </c>
       <c r="Q43">
-        <v>779472692.5303415</v>
+        <v>10055197733.64141</v>
       </c>
       <c r="R43">
-        <v>665142286.5056614</v>
+        <v>8580335495.923033</v>
       </c>
       <c r="S43">
-        <v>652244624.1530268</v>
+        <v>8413955651.574046</v>
       </c>
     </row>
     <row r="44">
@@ -13249,58 +13249,58 @@
         </is>
       </c>
       <c r="B44">
-        <v>112514740.9017548</v>
+        <v>1451440157.632637</v>
       </c>
       <c r="C44">
-        <v>1859693.99542457</v>
+        <v>23990052.54097695</v>
       </c>
       <c r="D44">
-        <v>132394416.6482952</v>
+        <v>1707887974.763008</v>
       </c>
       <c r="E44">
-        <v>6429676.75540098</v>
+        <v>82942830.14467265</v>
       </c>
       <c r="F44">
-        <v>56927076.89107473</v>
+        <v>734359291.8948641</v>
       </c>
       <c r="G44">
-        <v>197610864.2901955</v>
+        <v>2549180149.343522</v>
       </c>
       <c r="H44">
-        <v>170665583.2977157</v>
+        <v>2201586024.540533</v>
       </c>
       <c r="I44">
-        <v>46638604.90960732</v>
+        <v>601638003.3339344</v>
       </c>
       <c r="J44">
-        <v>14349545.84180682</v>
+        <v>185109141.359308</v>
       </c>
       <c r="K44">
-        <v>13179663.59918512</v>
+        <v>170017660.4294881</v>
       </c>
       <c r="L44">
-        <v>8059986.701129301</v>
+        <v>103973828.444568</v>
       </c>
       <c r="M44">
-        <v>237543805.8429666</v>
+        <v>3064315095.374269</v>
       </c>
       <c r="N44">
-        <v>85003355.4090547</v>
+        <v>1096543284.776805</v>
       </c>
       <c r="O44">
-        <v>575440545.6014656</v>
+        <v>7423183038.258906</v>
       </c>
       <c r="P44">
-        <v>885566150.7934159</v>
+        <v>11423803345.23507</v>
       </c>
       <c r="Q44">
-        <v>792502808.6832319</v>
+        <v>10223286232.01369</v>
       </c>
       <c r="R44">
-        <v>679988067.781477</v>
+        <v>8771846074.381054</v>
       </c>
       <c r="S44">
-        <v>666808404.1822919</v>
+        <v>8601828413.951565</v>
       </c>
     </row>
     <row r="45">
@@ -13310,58 +13310,58 @@
         </is>
       </c>
       <c r="B45">
-        <v>110931033.9294276</v>
+        <v>1431010337.689616</v>
       </c>
       <c r="C45">
-        <v>1565335.39477898</v>
+        <v>20192826.59264884</v>
       </c>
       <c r="D45">
-        <v>135899681.1588426</v>
+        <v>1753105886.949069</v>
       </c>
       <c r="E45">
-        <v>6199268.08714078</v>
+        <v>79970558.32411607</v>
       </c>
       <c r="F45">
-        <v>58303627.9557162</v>
+        <v>752116800.628739</v>
       </c>
       <c r="G45">
-        <v>201967912.5964785</v>
+        <v>2605386072.494573</v>
       </c>
       <c r="H45">
-        <v>171859458.049183</v>
+        <v>2216987008.834461</v>
       </c>
       <c r="I45">
-        <v>48180048.18184682</v>
+        <v>621522621.5458241</v>
       </c>
       <c r="J45">
-        <v>15100045.29375353</v>
+        <v>194790584.2894205</v>
       </c>
       <c r="K45">
-        <v>13439221.9891518</v>
+        <v>173365963.6600582</v>
       </c>
       <c r="L45">
-        <v>8566042.37414965</v>
+        <v>110501946.6265305</v>
       </c>
       <c r="M45">
-        <v>239521297.0699035</v>
+        <v>3089824732.201756</v>
       </c>
       <c r="N45">
-        <v>84864166.90661129</v>
+        <v>1094747753.095286</v>
       </c>
       <c r="O45">
-        <v>581530279.8645997</v>
+        <v>7501740610.253336</v>
       </c>
       <c r="P45">
-        <v>894429226.3905058</v>
+        <v>11538137020.43752</v>
       </c>
       <c r="Q45">
-        <v>800999017.1097448</v>
+        <v>10332887320.71571</v>
       </c>
       <c r="R45">
-        <v>690067983.1803172</v>
+        <v>8901876983.026091</v>
       </c>
       <c r="S45">
-        <v>676628761.1911653</v>
+        <v>8728511019.366034</v>
       </c>
     </row>
     <row r="46">
@@ -13371,58 +13371,58 @@
         </is>
       </c>
       <c r="B46">
-        <v>109189013.5770964</v>
+        <v>1408538275.144544</v>
       </c>
       <c r="C46">
-        <v>1562724.00892522</v>
+        <v>20159139.71513534</v>
       </c>
       <c r="D46">
-        <v>140259997.1231121</v>
+        <v>1809353962.888146</v>
       </c>
       <c r="E46">
-        <v>5778672.28486983</v>
+        <v>74544872.47482081</v>
       </c>
       <c r="F46">
-        <v>60318869.66003827</v>
+        <v>778113418.6144937</v>
       </c>
       <c r="G46">
-        <v>207920263.0769454</v>
+        <v>2682171393.692596</v>
       </c>
       <c r="H46">
-        <v>171693320.6547418</v>
+        <v>2214843836.446169</v>
       </c>
       <c r="I46">
-        <v>48813730.93405096</v>
+        <v>629697129.0492574</v>
       </c>
       <c r="J46">
-        <v>15321878.08012383</v>
+        <v>197652227.2335974</v>
       </c>
       <c r="K46">
-        <v>14131051.22077407</v>
+        <v>182290560.7479855</v>
       </c>
       <c r="L46">
-        <v>8040334.677491331</v>
+        <v>103720317.3396382</v>
       </c>
       <c r="M46">
-        <v>242966651.9002832</v>
+        <v>3134269809.513653</v>
       </c>
       <c r="N46">
-        <v>84339594.50703517</v>
+        <v>1087980769.140754</v>
       </c>
       <c r="O46">
-        <v>585306561.9745004</v>
+        <v>7550454649.471055</v>
       </c>
       <c r="P46">
-        <v>902415838.6285422</v>
+        <v>11641164318.3082</v>
       </c>
       <c r="Q46">
-        <v>810035909.4440157</v>
+        <v>10449463231.8278</v>
       </c>
       <c r="R46">
-        <v>700846895.8669192</v>
+        <v>9040924956.683258</v>
       </c>
       <c r="S46">
-        <v>686715844.6461451</v>
+        <v>8858634395.935272</v>
       </c>
     </row>
     <row r="47">
@@ -13432,58 +13432,58 @@
         </is>
       </c>
       <c r="B47">
-        <v>108778050.4849942</v>
+        <v>1403236851.256426</v>
       </c>
       <c r="C47">
-        <v>1497574.02509251</v>
+        <v>19318704.92369338</v>
       </c>
       <c r="D47">
-        <v>142025632.788865</v>
+        <v>1832130662.976359</v>
       </c>
       <c r="E47">
-        <v>5548155.977966189</v>
+        <v>71571212.11576384</v>
       </c>
       <c r="F47">
-        <v>63119850.45051857</v>
+        <v>814246070.8116896</v>
       </c>
       <c r="G47">
-        <v>212191213.2424423</v>
+        <v>2737266650.827506</v>
       </c>
       <c r="H47">
-        <v>171258206.9705544</v>
+        <v>2209230869.920152</v>
       </c>
       <c r="I47">
-        <v>47463140.73893731</v>
+        <v>612274515.5322913</v>
       </c>
       <c r="J47">
-        <v>16108686.43490673</v>
+        <v>207802055.0102968</v>
       </c>
       <c r="K47">
-        <v>14701882.80642715</v>
+        <v>189654288.2029102</v>
       </c>
       <c r="L47">
-        <v>7669434.07596168</v>
+        <v>98935699.57990569</v>
       </c>
       <c r="M47">
-        <v>244789999.6433815</v>
+        <v>3157790995.399621</v>
       </c>
       <c r="N47">
-        <v>83437258.11664303</v>
+        <v>1076340629.704695</v>
       </c>
       <c r="O47">
-        <v>585428608.7868118</v>
+        <v>7552029053.349874</v>
       </c>
       <c r="P47">
-        <v>906397872.5142484</v>
+        <v>11692532555.43381</v>
       </c>
       <c r="Q47">
-        <v>815291180.3216437</v>
+        <v>10517256226.1492</v>
       </c>
       <c r="R47">
-        <v>706513129.8366494</v>
+        <v>9114019374.892776</v>
       </c>
       <c r="S47">
-        <v>691811247.0302222</v>
+        <v>8924365086.689867</v>
       </c>
     </row>
     <row r="48">
@@ -13493,58 +13493,58 @@
         </is>
       </c>
       <c r="B48">
-        <v>105088759.984763</v>
+        <v>1355645003.803443</v>
       </c>
       <c r="C48">
-        <v>1685236.45744011</v>
+        <v>21739550.30097742</v>
       </c>
       <c r="D48">
-        <v>139961063.1148366</v>
+        <v>1805497714.181393</v>
       </c>
       <c r="E48">
-        <v>5849935.19966031</v>
+        <v>75464164.075618</v>
       </c>
       <c r="F48">
-        <v>62522486.29208908</v>
+        <v>806540073.1679492</v>
       </c>
       <c r="G48">
-        <v>210018721.0640261</v>
+        <v>2709241501.725937</v>
       </c>
       <c r="H48">
-        <v>168830099.0263767</v>
+        <v>2177908277.440259</v>
       </c>
       <c r="I48">
-        <v>46702465.91139103</v>
+        <v>602461810.2569443</v>
       </c>
       <c r="J48">
-        <v>16620568.09036647</v>
+        <v>214405328.3657275</v>
       </c>
       <c r="K48">
-        <v>15046340.08497226</v>
+        <v>194097787.0961422</v>
       </c>
       <c r="L48">
-        <v>7492074.414216541</v>
+        <v>96647759.94339338</v>
       </c>
       <c r="M48">
-        <v>246907272.0923196</v>
+        <v>3185103809.990923</v>
       </c>
       <c r="N48">
-        <v>82495061.61816111</v>
+        <v>1064186294.874278</v>
       </c>
       <c r="O48">
-        <v>584093881.2378037</v>
+        <v>7534811067.967668</v>
       </c>
       <c r="P48">
-        <v>899201362.2865928</v>
+        <v>11599697573.49705</v>
       </c>
       <c r="Q48">
-        <v>809214226.2542152</v>
+        <v>10438863518.67938</v>
       </c>
       <c r="R48">
-        <v>704125466.2694521</v>
+        <v>9083218514.875933</v>
       </c>
       <c r="S48">
-        <v>689079126.18448</v>
+        <v>8889120727.779791</v>
       </c>
     </row>
     <row r="49">
@@ -13554,58 +13554,58 @@
         </is>
       </c>
       <c r="B49">
-        <v>101232233.0742725</v>
+        <v>1305895806.658115</v>
       </c>
       <c r="C49">
-        <v>1823381.57093886</v>
+        <v>23521622.2651113</v>
       </c>
       <c r="D49">
-        <v>138366017.424576</v>
+        <v>1784921624.77703</v>
       </c>
       <c r="E49">
-        <v>5968273.89187655</v>
+        <v>76990733.2052075</v>
       </c>
       <c r="F49">
-        <v>62722455.30576183</v>
+        <v>809119673.4443276</v>
       </c>
       <c r="G49">
-        <v>208880128.1931532</v>
+        <v>2694553653.691677</v>
       </c>
       <c r="H49">
-        <v>167562378.3046069</v>
+        <v>2161554680.129429</v>
       </c>
       <c r="I49">
-        <v>46928694.08071259</v>
+        <v>605380153.6411924</v>
       </c>
       <c r="J49">
-        <v>16406969.09450738</v>
+        <v>211649901.3191452</v>
       </c>
       <c r="K49">
-        <v>15863638.11379067</v>
+        <v>204640931.6678997</v>
       </c>
       <c r="L49">
-        <v>7481811.3575117</v>
+        <v>96515366.51190093</v>
       </c>
       <c r="M49">
-        <v>249372000.6116918</v>
+        <v>3216898807.890824</v>
       </c>
       <c r="N49">
-        <v>82112008.36370398</v>
+        <v>1059244907.891781</v>
       </c>
       <c r="O49">
-        <v>585727499.926525</v>
+        <v>7555884749.052173</v>
       </c>
       <c r="P49">
-        <v>895839861.1939508</v>
+        <v>11556334209.40197</v>
       </c>
       <c r="Q49">
-        <v>806246041.4727352</v>
+        <v>10400573934.99828</v>
       </c>
       <c r="R49">
-        <v>705013808.3984625</v>
+        <v>9094678128.340166</v>
       </c>
       <c r="S49">
-        <v>689150170.2846719</v>
+        <v>8890037196.672268</v>
       </c>
     </row>
     <row r="50">
@@ -13615,58 +13615,58 @@
         </is>
       </c>
       <c r="B50">
-        <v>96564880.25952157</v>
+        <v>1245686955.347828</v>
       </c>
       <c r="C50">
-        <v>1778532.56351978</v>
+        <v>22943070.06940516</v>
       </c>
       <c r="D50">
-        <v>135581883.2285733</v>
+        <v>1749006293.648596</v>
       </c>
       <c r="E50">
-        <v>5992061.13817651</v>
+        <v>77297588.68247698</v>
       </c>
       <c r="F50">
-        <v>62519223.61527222</v>
+        <v>806497984.6370116</v>
       </c>
       <c r="G50">
-        <v>205871700.5455418</v>
+        <v>2655744937.03749</v>
       </c>
       <c r="H50">
-        <v>169388265.3647152</v>
+        <v>2185108623.204826</v>
       </c>
       <c r="I50">
-        <v>46647542.68198633</v>
+        <v>601753300.5976237</v>
       </c>
       <c r="J50">
-        <v>17118270.66171902</v>
+        <v>220825691.5361754</v>
       </c>
       <c r="K50">
-        <v>15353561.87229379</v>
+        <v>198060948.1525899</v>
       </c>
       <c r="L50">
-        <v>7863807.27657432</v>
+        <v>101443113.8678087</v>
       </c>
       <c r="M50">
-        <v>250300117.7575739</v>
+        <v>3228871519.072703</v>
       </c>
       <c r="N50">
-        <v>81311555.93970537</v>
+        <v>1048919071.622199</v>
       </c>
       <c r="O50">
-        <v>587983121.5545678</v>
+        <v>7584982268.053925</v>
       </c>
       <c r="P50">
-        <v>890419702.3596313</v>
+        <v>11486414160.43924</v>
       </c>
       <c r="Q50">
-        <v>801244339.1433516</v>
+        <v>10336051974.94924</v>
       </c>
       <c r="R50">
-        <v>704679458.8838298</v>
+        <v>9090365019.601406</v>
       </c>
       <c r="S50">
-        <v>689325897.0115361</v>
+        <v>8892304071.448818</v>
       </c>
     </row>
     <row r="51">
@@ -13676,58 +13676,58 @@
         </is>
       </c>
       <c r="B51">
-        <v>91142905.83311483</v>
+        <v>1175743485.247181</v>
       </c>
       <c r="C51">
-        <v>1659178.24056388</v>
+        <v>21403399.30327405</v>
       </c>
       <c r="D51">
-        <v>135469732.2818689</v>
+        <v>1747559546.43611</v>
       </c>
       <c r="E51">
-        <v>5934509.49773185</v>
+        <v>76555172.52074087</v>
       </c>
       <c r="F51">
-        <v>60582080.95712794</v>
+        <v>781508844.3469504</v>
       </c>
       <c r="G51">
-        <v>203645500.9772926</v>
+        <v>2627026962.607075</v>
       </c>
       <c r="H51">
-        <v>170445107.531981</v>
+        <v>2198741887.162556</v>
       </c>
       <c r="I51">
-        <v>48078900.2179137</v>
+        <v>620217812.8110868</v>
       </c>
       <c r="J51">
-        <v>16722576.85564077</v>
+        <v>215721241.4377659</v>
       </c>
       <c r="K51">
-        <v>14473281.54721438</v>
+        <v>186705331.9590655</v>
       </c>
       <c r="L51">
-        <v>8148715.78863203</v>
+        <v>105118433.6733532</v>
       </c>
       <c r="M51">
-        <v>249410933.094195</v>
+        <v>3217401036.915116</v>
       </c>
       <c r="N51">
-        <v>81923746.02846102</v>
+        <v>1056816323.767147</v>
       </c>
       <c r="O51">
-        <v>589203261.0640379</v>
+        <v>7600722067.726089</v>
       </c>
       <c r="P51">
-        <v>883991667.8744454</v>
+        <v>11403492515.58035</v>
       </c>
       <c r="Q51">
-        <v>793919206.0573524</v>
+        <v>10241557758.13985</v>
       </c>
       <c r="R51">
-        <v>702776300.2242374</v>
+        <v>9065814272.892664</v>
       </c>
       <c r="S51">
-        <v>688303018.6770231</v>
+        <v>8879108940.933598</v>
       </c>
     </row>
     <row r="52">
@@ -13737,58 +13737,58 @@
         </is>
       </c>
       <c r="B52">
-        <v>90067055.03625967</v>
+        <v>1161865009.96775</v>
       </c>
       <c r="C52">
-        <v>1446959.05206259</v>
+        <v>18665771.77160741</v>
       </c>
       <c r="D52">
-        <v>136852902.4913732</v>
+        <v>1765402442.138714</v>
       </c>
       <c r="E52">
-        <v>5757945.63857217</v>
+        <v>74277498.737581</v>
       </c>
       <c r="F52">
-        <v>61904281.79411806</v>
+        <v>798565235.144123</v>
       </c>
       <c r="G52">
-        <v>205962088.976126</v>
+        <v>2656910947.792026</v>
       </c>
       <c r="H52">
-        <v>175792293.807584</v>
+        <v>2267720590.117834</v>
       </c>
       <c r="I52">
-        <v>50153612.74064702</v>
+        <v>646981604.3543466</v>
       </c>
       <c r="J52">
-        <v>16301575.22069297</v>
+        <v>210290320.3469393</v>
       </c>
       <c r="K52">
-        <v>13913689.67233853</v>
+        <v>179486596.773167</v>
       </c>
       <c r="L52">
-        <v>8303873.35282829</v>
+        <v>107119966.2514849</v>
       </c>
       <c r="M52">
-        <v>248821345.073581</v>
+        <v>3209795351.449195</v>
       </c>
       <c r="N52">
-        <v>83958168.29215103</v>
+        <v>1083060370.968748</v>
       </c>
       <c r="O52">
-        <v>597244558.1598228</v>
+        <v>7704454800.261714</v>
       </c>
       <c r="P52">
-        <v>893273702.1722085</v>
+        <v>11523230758.02149</v>
       </c>
       <c r="Q52">
-        <v>801011660.5272292</v>
+        <v>10333050420.80126</v>
       </c>
       <c r="R52">
-        <v>710944605.4909694</v>
+        <v>9171185410.833506</v>
       </c>
       <c r="S52">
-        <v>697030915.8186309</v>
+        <v>8991698814.060339</v>
       </c>
     </row>
     <row r="53">
@@ -13798,58 +13798,58 @@
         </is>
       </c>
       <c r="B53">
-        <v>89545485.64662015</v>
+        <v>1155136764.8414</v>
       </c>
       <c r="C53">
-        <v>1433761.68329197</v>
+        <v>18495525.71446642</v>
       </c>
       <c r="D53">
-        <v>140046494.3858328</v>
+        <v>1806599777.577244</v>
       </c>
       <c r="E53">
-        <v>5750695.30987495</v>
+        <v>74183969.49738686</v>
       </c>
       <c r="F53">
-        <v>61989119.40326769</v>
+        <v>799659640.3021532</v>
       </c>
       <c r="G53">
-        <v>209220070.7822675</v>
+        <v>2698938913.09125</v>
       </c>
       <c r="H53">
-        <v>178892393.9561905</v>
+        <v>2307711882.034858</v>
       </c>
       <c r="I53">
-        <v>52735402.32220194</v>
+        <v>680286689.956405</v>
       </c>
       <c r="J53">
-        <v>16486667.91601975</v>
+        <v>212678016.1166548</v>
       </c>
       <c r="K53">
-        <v>13162875.64112071</v>
+        <v>169801095.7704571</v>
       </c>
       <c r="L53">
-        <v>8643358.144868171</v>
+        <v>111499320.0687994</v>
       </c>
       <c r="M53">
-        <v>250041431.3837397</v>
+        <v>3225534464.850243</v>
       </c>
       <c r="N53">
-        <v>84654684.99089414</v>
+        <v>1092045436.382535</v>
       </c>
       <c r="O53">
-        <v>604616814.3550349</v>
+        <v>7799556905.179951</v>
       </c>
       <c r="P53">
-        <v>903382370.7839227</v>
+        <v>11653632583.1126</v>
       </c>
       <c r="Q53">
-        <v>810084327.6481602</v>
+        <v>10450087826.66127</v>
       </c>
       <c r="R53">
-        <v>720538842.0015402</v>
+        <v>9294951061.819868</v>
       </c>
       <c r="S53">
-        <v>707375966.3604194</v>
+        <v>9125149966.04941</v>
       </c>
     </row>
     <row r="54">
@@ -13859,58 +13859,58 @@
         </is>
       </c>
       <c r="B54">
-        <v>89016402.76416537</v>
+        <v>1148311595.657733</v>
       </c>
       <c r="C54">
-        <v>1223474.69848089</v>
+        <v>15782823.61040348</v>
       </c>
       <c r="D54">
-        <v>141580501.4137744</v>
+        <v>1826388468.23769</v>
       </c>
       <c r="E54">
-        <v>5806274.18716969</v>
+        <v>74900937.014489</v>
       </c>
       <c r="F54">
-        <v>60766308.18048114</v>
+        <v>783885375.5282067</v>
       </c>
       <c r="G54">
-        <v>209376558.4799061</v>
+        <v>2700957604.390789</v>
       </c>
       <c r="H54">
-        <v>180343713.1645305</v>
+        <v>2326433899.822443</v>
       </c>
       <c r="I54">
-        <v>54412304.53604599</v>
+        <v>701918728.5149933</v>
       </c>
       <c r="J54">
-        <v>16089772.11005716</v>
+        <v>207558060.2197374</v>
       </c>
       <c r="K54">
-        <v>13558602.23756825</v>
+        <v>174905968.8646304</v>
       </c>
       <c r="L54">
-        <v>8430691.65868159</v>
+        <v>108755922.3969925</v>
       </c>
       <c r="M54">
-        <v>251787235.371408</v>
+        <v>3248055336.291163</v>
       </c>
       <c r="N54">
-        <v>87200755.68586349</v>
+        <v>1124889748.347639</v>
       </c>
       <c r="O54">
-        <v>611823074.764155</v>
+        <v>7892517664.457601</v>
       </c>
       <c r="P54">
-        <v>910216036.0082265</v>
+        <v>11741786864.50612</v>
       </c>
       <c r="Q54">
-        <v>814584588.6636814</v>
+        <v>10508141193.76149</v>
       </c>
       <c r="R54">
-        <v>725568185.8995161</v>
+        <v>9359829598.103758</v>
       </c>
       <c r="S54">
-        <v>712009583.6619477</v>
+        <v>9184923629.239126</v>
       </c>
     </row>
     <row r="55">
@@ -13920,58 +13920,58 @@
         </is>
       </c>
       <c r="B55">
-        <v>89835430.07681568</v>
+        <v>1158877047.990922</v>
       </c>
       <c r="C55">
-        <v>1010311.70708011</v>
+        <v>13033021.02133342</v>
       </c>
       <c r="D55">
-        <v>142577271.4657385</v>
+        <v>1839246801.908027</v>
       </c>
       <c r="E55">
-        <v>5454418.9891126</v>
+        <v>70362004.95955254</v>
       </c>
       <c r="F55">
-        <v>60363578.50741995</v>
+        <v>778690162.7457174</v>
       </c>
       <c r="G55">
-        <v>209405580.6693512</v>
+        <v>2701331990.634631</v>
       </c>
       <c r="H55">
-        <v>181372289.8358208</v>
+        <v>2339702538.882089</v>
       </c>
       <c r="I55">
-        <v>55227790.05758968</v>
+        <v>712438491.7429069</v>
       </c>
       <c r="J55">
-        <v>15842418.1612474</v>
+        <v>204367194.2800915</v>
       </c>
       <c r="K55">
-        <v>14684188.47144348</v>
+        <v>189426031.2816209</v>
       </c>
       <c r="L55">
-        <v>8094039.48977271</v>
+        <v>104413109.418068</v>
       </c>
       <c r="M55">
-        <v>256882254.2118583</v>
+        <v>3313781079.332972</v>
       </c>
       <c r="N55">
-        <v>89119909.2411176</v>
+        <v>1149646829.210417</v>
       </c>
       <c r="O55">
-        <v>621222889.46885</v>
+        <v>8013775274.148166</v>
       </c>
       <c r="P55">
-        <v>920463900.2150168</v>
+        <v>11873984312.77372</v>
       </c>
       <c r="Q55">
-        <v>823249951.4841264</v>
+        <v>10619924374.14523</v>
       </c>
       <c r="R55">
-        <v>733414521.407311</v>
+        <v>9461047326.15431</v>
       </c>
       <c r="S55">
-        <v>718730332.9358674</v>
+        <v>9271621294.87269</v>
       </c>
     </row>
     <row r="56">
@@ -13981,58 +13981,58 @@
         </is>
       </c>
       <c r="B56">
-        <v>89488631.70902786</v>
+        <v>1154403349.046459</v>
       </c>
       <c r="C56">
-        <v>961124.44983533</v>
+        <v>12398505.40287576</v>
       </c>
       <c r="D56">
-        <v>144050023.0377032</v>
+        <v>1858245297.186371</v>
       </c>
       <c r="E56">
-        <v>5235577.19217297</v>
+        <v>67538945.77903131</v>
       </c>
       <c r="F56">
-        <v>60056138.42349985</v>
+        <v>774724185.663148</v>
       </c>
       <c r="G56">
-        <v>210302863.1032113</v>
+        <v>2712906934.031425</v>
       </c>
       <c r="H56">
-        <v>179620286.1782488</v>
+        <v>2317101691.69941</v>
       </c>
       <c r="I56">
-        <v>57493965.54716993</v>
+        <v>741672155.5584922</v>
       </c>
       <c r="J56">
-        <v>15770729.38246432</v>
+        <v>203442409.0337898</v>
       </c>
       <c r="K56">
-        <v>15956191.46991158</v>
+        <v>205834869.9618594</v>
       </c>
       <c r="L56">
-        <v>7626958.7049732</v>
+        <v>98387767.29415429</v>
       </c>
       <c r="M56">
-        <v>257178740.2812075</v>
+        <v>3317605749.627577</v>
       </c>
       <c r="N56">
-        <v>89508211.73355839</v>
+        <v>1154655931.362903</v>
       </c>
       <c r="O56">
-        <v>623155083.2975338</v>
+        <v>8038700574.538187</v>
       </c>
       <c r="P56">
-        <v>922946578.1097729</v>
+        <v>11906010857.61607</v>
       </c>
       <c r="Q56">
-        <v>825811407.6712413</v>
+        <v>10652967158.95901</v>
       </c>
       <c r="R56">
-        <v>736322775.9622136</v>
+        <v>9498563809.912556</v>
       </c>
       <c r="S56">
-        <v>720366584.4923019</v>
+        <v>9292728939.950695</v>
       </c>
     </row>
     <row r="57">
@@ -14042,58 +14042,58 @@
         </is>
       </c>
       <c r="B57">
-        <v>89185971.94965681</v>
+        <v>1150499038.150573</v>
       </c>
       <c r="C57">
-        <v>778653.68848437</v>
+        <v>10044632.58144837</v>
       </c>
       <c r="D57">
-        <v>143292694.0304983</v>
+        <v>1848475752.993428</v>
       </c>
       <c r="E57">
-        <v>5310291.672612879</v>
+        <v>68502762.57670616</v>
       </c>
       <c r="F57">
-        <v>59256171.99119566</v>
+        <v>764404618.686424</v>
       </c>
       <c r="G57">
-        <v>208637811.3827912</v>
+        <v>2691427766.838006</v>
       </c>
       <c r="H57">
-        <v>179038389.9015031</v>
+        <v>2309595229.72939</v>
       </c>
       <c r="I57">
-        <v>57033041.99843897</v>
+        <v>735726241.7798628</v>
       </c>
       <c r="J57">
-        <v>15677337.92515404</v>
+        <v>202237659.2344871</v>
       </c>
       <c r="K57">
-        <v>16479595.99329106</v>
+        <v>212586788.3134547</v>
       </c>
       <c r="L57">
-        <v>7338712.23102314</v>
+        <v>94669387.78019851</v>
       </c>
       <c r="M57">
-        <v>257933930.3835651</v>
+        <v>3327347701.94799</v>
       </c>
       <c r="N57">
-        <v>90085054.50662917</v>
+        <v>1162097203.135516</v>
       </c>
       <c r="O57">
-        <v>623586062.9396046</v>
+        <v>8044260211.9209</v>
       </c>
       <c r="P57">
-        <v>921409846.2720525</v>
+        <v>11886187016.90948</v>
       </c>
       <c r="Q57">
-        <v>823986079.5344002</v>
+        <v>10629420425.99376</v>
       </c>
       <c r="R57">
-        <v>734800107.5847435</v>
+        <v>9478921387.843191</v>
       </c>
       <c r="S57">
-        <v>718320511.5914524</v>
+        <v>9266334599.529736</v>
       </c>
     </row>
     <row r="58">
@@ -14103,58 +14103,58 @@
         </is>
       </c>
       <c r="B58">
-        <v>90772836.96114191</v>
+        <v>1170969596.798731</v>
       </c>
       <c r="C58">
-        <v>852079.5368943301</v>
+        <v>10991826.02593686</v>
       </c>
       <c r="D58">
-        <v>144868095.6170136</v>
+        <v>1868798433.459476</v>
       </c>
       <c r="E58">
-        <v>5667454.604316629</v>
+        <v>73110164.39568453</v>
       </c>
       <c r="F58">
-        <v>59922241.02367231</v>
+        <v>772996909.2053728</v>
       </c>
       <c r="G58">
-        <v>211309870.7818969</v>
+        <v>2725897333.08647</v>
       </c>
       <c r="H58">
-        <v>177929331.7969812</v>
+        <v>2295288380.181058</v>
       </c>
       <c r="I58">
-        <v>57805957.23867279</v>
+        <v>745696848.3788791</v>
       </c>
       <c r="J58">
-        <v>15917071.49975005</v>
+        <v>205330222.3467757</v>
       </c>
       <c r="K58">
-        <v>16970113.21546275</v>
+        <v>218914460.4794695</v>
       </c>
       <c r="L58">
-        <v>7592607.29968498</v>
+        <v>97944634.16593625</v>
       </c>
       <c r="M58">
-        <v>258121351.2285735</v>
+        <v>3329765430.848598</v>
       </c>
       <c r="N58">
-        <v>91509215.12103066</v>
+        <v>1180468875.061296</v>
       </c>
       <c r="O58">
-        <v>625845647.4001559</v>
+        <v>8073408851.462011</v>
       </c>
       <c r="P58">
-        <v>927928355.1431947</v>
+        <v>11970275781.34721</v>
       </c>
       <c r="Q58">
-        <v>828826532.722479</v>
+        <v>10691862272.11998</v>
       </c>
       <c r="R58">
-        <v>738053695.7613373</v>
+        <v>9520892675.321251</v>
       </c>
       <c r="S58">
-        <v>721083582.5458744</v>
+        <v>9301978214.84178</v>
       </c>
     </row>
   </sheetData>
